--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2168,10 +2168,57 @@
       <c r="L38" t="str">
         <v/>
       </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v/>
+      </c>
+      <c r="B39" t="str">
+        <v>home</v>
+      </c>
+      <c r="C39">
+        <v>10.760240950799044</v>
+      </c>
+      <c r="D39">
+        <v>106.61353282563975</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39">
+        <v>7</v>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O39"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O40"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2215,10 +2215,57 @@
       <c r="L39" t="str">
         <v/>
       </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v/>
+      </c>
+      <c r="B40" t="str">
+        <v>home11</v>
+      </c>
+      <c r="C40">
+        <v>10.760187558862727</v>
+      </c>
+      <c r="D40">
+        <v>106.61348686761437</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40">
+        <v>7</v>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
+      <c r="L40" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O40"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2262,10 +2262,57 @@
       <c r="L40" t="str">
         <v/>
       </c>
+      <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v/>
+      </c>
+      <c r="B41" t="str">
+        <v>Tru 1 test</v>
+      </c>
+      <c r="C41">
+        <v>10.760201091099338</v>
+      </c>
+      <c r="D41">
+        <v>106.61322250877839</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41">
+        <v>7</v>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
+      <c r="L41" t="str">
+        <v>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAASABIAAD/4QBMRXhpZgAATU0AKgAAAAgAAYdpAAQAAAABAAAAGgAAAAAAA6ABAAMAAAABAAEAAKACAAQAAAABAAABLKADAAQAAAABAAABkAAAAAD/7QA4UGhvdG9zaG9wIDMuMAA4QklNBAQAAAAAAAA4QklNBCUAAAAAABDUHYzZjwCyBOmACZjs+EJ+/8AAEQgBkAEsAwEiAAIRAQMRAf/EAB8AAAEFAQEBAQEBAAAAAAAAAAABAgMEBQYHCAkKC//EALUQAAIBAwMCBAMFBQQEAAABfQECAwAEEQUSITFBBhNRYQcicRQygZGhCCNCscEVUtHwJDNicoIJChYXGBkaJSYnKCkqNDU2Nzg5OkNERUZHSElKU1RVVldYWVpjZGVmZ2hpanN0dXZ3eHl6g4SFhoeIiYqSk5SVlpeYmZqio6Slpqeoqaqys7S1tre4ubrCw8TFxsfIycrS09TV1tfY2drh4uPk5ebn6Onq8fLz9PX29/j5+v/EAB8BAAMBAQEBAQEBAQEAAAAAAAABAgMEBQYHCAkKC//EALURAAIBAgQEAwQHBQQEAAECdwABAgMRBAUhMQYSQVEHYXETIjKBCBRCkaGxwQkjM1LwFWJy0QoWJDThJfEXGBkaJicoKSo1Njc4OTpDREVGR0hJSlNUVVZXWFlaY2RlZmdoaWpzdHV2d3h5eoKDhIWGh4iJipKTlJWWl5iZmqKjpKWmp6ipqrKztLW2t7i5usLDxMXGx8jJytLT1NXW19jZ2uLj5OXm5+jp6vLz9PX29/j5+v/bAEMAAwMDAwMDBgMDBggGBgYICwgICAgLDQsLCwsLDRANDQ0NDQ0QEBAQEBAQEBMTExMTExcXFxcXGhoaGhoaGhoaGv/bAEMBBAQEBgYGCwYGCxsSDxIbGxsbGxsbGxsbGxsbGxsbGxsbGxsbGxsbGxsbGxsbGxsbGxsbGxsbGxsbGxsbGxsbG//dAAQAE//aAAwDAQACEQMRAD8A/PjC5zznOR61bUbgAKgI59/Q9asR7dozXkHcPVcpjPIq7CDtxwf5frVVNpA6+vNXoRjJyaCS/AD/AJ49q67Tc/Z9q+p6+lclCDnbg8V1WkhgrDsOhqoPUJbGpjJwaUAUoBP49cU4DJ/nW5mKMZ9xW5oTbdQUN3B/UVihMjP41raM2NRiYcndjj3FAmcn8bow+h2Uhz+7mdR/wJc4/Sqvww/eaTqcJ6AJ19w3+Fb3xlh3eEoZjn93dL+OUb1rn/hMCbLUM/3I/wD2atfsma3PS7NLGLQJG1gB7UN84Klu4CjAyTyRjAzXe+Hxpn/CG3EejhFt0u4+EGAG2vuwPfvXD6OrT6fKtsQswJ2NICyA8EEjIz+YIru9Dgnt/DF4lx5TO9zE7NChjBJD9VLNz680uhTMybO9O+GH869P+Gy/8VQrLxi3uSPXPkP6f415pNnejH+8Ov1r0v4dKW8QsB1Npc8/9sH5qY7ky2Zy0i8Edql1eNRZ2JXPVmIPs3/1qJE3ZDVZ1pf9D02Pv5Tn/wAeb/Ct0YHFogMuCOay77Ju5MDo3StyNWacEeoGPxrAuzuuZT6tWdbY2pLUiyo7Co9oxnFShTjinbfSudM3YwKc5FTKM9Pypqj1+gqRVOTTTJJEyT6VOFyKbGuf8aljUkkUxWHR9x29anCgdOM9aYq4FWMZG09xQIeq/Lk1Kq/KDj3oQHaM81Mg/KgBEHGR+VWFH6+/aiNcKSaegIxu70EsUgg5zjsaexBGDzxT+GPHp6dKDjjAoENCnac8+9OYYzjp70o5GKdgZwefegBgz1/WjgdKcAp/z+GaqyyxB8ZXjjmmkB//0PgBlz05Oe/Gf50+PGMZ9vWlcAHcfWkTAyO3+ea8g7iZAw4ar8R+bJ/SqK5B57dauREbsYoEzVi610mlkiRoz0K5/wA/nXMw4UgV0GmnbN8voc0R+IJbHQkA89aBu6CjAIzTvumukyHLnPFaOlEjUIs8guBWcBxhqu2rqlzEzHow6fXvQJjfi/uPgz5Rn/SYznGcfKw/rXIfCTYPt6HqYVP6n/Gu4+KSbvBNy/ULJGT+LY5/GvPPhAd91coMsWtc/kwBrVfAR1PV9PSabRrnBcqd3ywDEvQfcOR83pXd+EhnwffAfawFuYv+PwfP909Pb0I75rz7S3mi026a02xSYO2V9oVeO5J/nxXe+EJNVl8IXx1c7pFmi2kmMttO7r5ZK/THakhshkHzIP8AaHH416R8PD/xPLhumLG7PPtA9ecS/eT/AHgOnvXqHw5UHVr09cafdds8mMjv0/ClDcU9jmgpzjBq5rIYpYq3GLZj+ZkNRbCDjpVrX1KG0Unn7Kvp3JP9a2OfqchbqGuEx/eGRXKStmRnIySe1dpZjbchjzjJ5+lcYxLsSOmTx+NZVtkb0t2CA444qVcfe7E8UxBzgVKoBJzz6/lXObjUU5p6gDilCZGMcVKq85POetAmh0aj04qdAdv+NMjX8qnVB1H86aZI9UPQ8d6mWPJAamqKsEYIwKYmKpXG31qVUIFIFGzgVKgwoY+lAiZVwoPpzzTlXgdOtAHy8VKgzk9M0AJgqxzj6fpUgzjp+VMKrnA5Gf8A9dSFeRTJYYx14oK5PI+pp4QgZPTNLgH8/b60CK8kiQoXcgBRkk9BivlHxV8Rtd1TWpZvD9zLBap+7QLj5tvVzwevb2xXonxJ8TXesahH8PfDG57mdgtyy9ApGdmR7csew47mvSfDHhPT/DOjRaVGgkZOZHI+856nvj2HpWsbRV2Fz//R+CWHGBjngimLwxz09qtOhX7wqAD5hx7V5B3DwoDZPOKspjPTvVQhhyOfc1YQ/KCeo/X1piZqoc8rkVt2L7ZVbPtVPSdFvdUTz4dqorbWJPK8ZropNFlsmDId3AOTxQoO9xXRfDFiCKkVj3/SosEHawpwPGa6DMnU5GP88VMpIdSDwCKrLk8jmpgcYGR1oEzf+IyGTwRfoBn5Yz6/8tU/xryf4QFl1OWPjm1b9HWvY/HCed4I1FT3gDD8HU14x8H2Ka15Z720g/HcO1bL4TPqexaO1pHZ3S6gyCEgl1kxtK45J9gM5rvPCw0QeFr6XQkijgkeIsIl2gsCRyB3HQ55rktBRJFnjdFaMnDhjnPUdPeu+0i2tLLQLuCyjSOImPhRxnceQfXrUFMxH5ZM9Nwr1H4ej/TdRz/0Drnn0+T/ACK8vlI3J/vD+deofD9nim1MqOmnTA9ehKjtRDcUtjn+QQT/AIVe8Sczwrn7lnFwO2cH+tZ+9CePqK0PE2BqDIT0toRj/gKGtjnOYtMK0jDtGx9shTXFDLNmuyhIEczdMRt19641QeprGt0Oil1JQowPX/PanqP4fwpoJFSDhgRzisDYlVemB1qVF5zUaj86nX0/zzSAfGo6mp1TAJX6UICDgdzz9KmALDGOlMhiIMDPHSpgvHFCqRg4zUoBA+bn2poQAYAxUuwkcCnEZwBzxjFP25GKdxDu+RnipVHy8dTg03GDiplHHHpxQAq8fNjninLu5H4UnXB/SpACQDxx/OmA0Ak/hXmvxC8c/wDCNQDR9KBl1O6G2JFG4pu4DfUn7oxyfauk8ZeJrbwnocurXADvwscecb3PQfTueOgrzr4c+Dr26uf+E58TkyXtyxkhV/4Aej4Pf+6OgGPbFxWnMyHvZG/8OvA6eG7RtU1H95qN0N0rsSxXdyVB7kn7x7n2r0vH93p7VLtJOBSDaeWxzzzUt3HY/9L4VkX1PSqmM+n4Vclyef8APFU8HPNeQdxIwUcj8P8A9dKhJXB4PSm53DilXgc0wZ0ehajJp92DExKtww9a9UgurW9Y26nLKA59weeK8VtG2uHXt1Fem+GYXV5bqTIXGxc9+a6lFezuYN+9Y3J7SEt05z29+1VXtVaPC/eHp0/rV27u4bZQ0zY3dPf3rOOpWssbMjbsdQOp+gpcrtcG1sUlYEZ/MVLuIXLcc0mn2U+zdcDaxJOM9AelaQWCWFoMAHoeeRRYR1HiCP7T4NvsHk2buT1Pypu/pXhXwmcJ4iAYnBjkA/n/AEr36/w/g+7PXNhLz/2zNfO3wsJfxLbhOjGUEf8AAScVpHYl7nvGl20VzJd2lwrFHJU45GDkEc+3tXd+FdDstB8NajZ2jMUYxP8AMFzu38/dAznk5/8ArAcPp0Us1xe2yyNCXyAyDoTnn8O1ehaDBLbaFfQPI8o8uL5mIOMMB1xk565JJpIbMaVTuj7Hev8AOvT/AAMYlh1h5QDiwcDPqXQD/P8APv5hMwDx+m8H9a9J8FuV0/WmHU2JHPvNHShuKexzSqfOAHHP86v+JGCanOc5/dxr6/wL/hWWoPmrggc/56U7xfcLFqN4542lF9uFx7elbnOlqYQuykFwAeSmP/HhXOA81QOqeY/kAZ38Z/Gr8fPXn6/lXPUOmGiNHTbG41G+hsLYAvM6ouenJxk45wO9e32nwYeGIzavqCfLyY7ZC5OPdtvP/ATXB/DS38/xZDIcEQK0hz9No/nX05v569O9KEE1dinNrRHg+o+ENDgPkW63IZc/O5GefbAHHSufHhZ1OY3+X6c19JzTh1CPhlHYjiq1vDp9vcLcPaxSFTna4O38R0q3CJKmz551Tw1c6ZDDKckzZOMDgcYz9axGt5owC6kA8c9OPSvo7UdDt9UlDmYxknJyARz9MfhxVe68M20NrHHZSLc9TKGULtOOAASc/X9K54Rnb3y3JdD588sBcnnPpTwBxXrp8JafcEmWMQZJ+YEj8h0rKttN8DQxme5vN6q7JiRhH8yMUYdAeGBHFVyjuedYAJ9PwqfygfvEAV6Ouu/DSEgboGx1zvf+hrTt9U+Ht4xEL2qse2dn88VapsnmR5UYWUZdSvp2pDlRwD/kV7PP4N8P6iguLSR0J5D7vMXHtnOPoDXHar4K1fTQZoVFxEOd8fUfVev5ZocWgujjyAOOv1qWPBPI9zTCGxz3qhq+oR6TpNzqsg3LbxM//fIyP8KkZ4pqe34g/E9NLILabpZPmA/dLL94fi2Fx6An1r31VAIUenHFeQ/BrTJU0CfX7klp9QlLucfeCk8/ixbNewgDGOOtVN62FHuMJyMN7ikZS3OTUvUbvelwB1FSM//T+HZAG5UYxVJ1+Yg1fK+veq0iDdg9MV5B3FYEZyeRmmqQcj9KecKOelRtndj8eapCN/w5Z/2jqsVl0ViS30HJr127sLuHbb6Wh2nksegz27CvN/h66DxIsZPLRvjPb5c/yr2G7vjCzwpwpGMg+1dCk1ZGbimcNeaDq0r75ELd+W6e3Wq+k2LJfFnBDopBjI7H+IZNdC810CNzcU1JmFwry87futjpnqPpW0qzlGxiqaTuaWwqCAOahuLaKddrcH+8pwfbnrWitxbMOSOawrrV7WIFpCqKM8sQP51gWd6IvO8PywHPz20iH8VIr5o+Fp2+KbWNR1eQcf8AXNq+nPD1zBf6RFLGdySBlypyOpH9K+XPho3leLbTd1849/VSK2jsyD6N0xm/tK6i3BCzEDI5OCc4+ma7DwuurRaPqketMjOQpjMZyNvmL/srj6Hcfc9uN09pP7auxGVBZieR3zx6V2PhZtXOk6ousiMOIkK+V93HnAYyTknABJwBzipsNsoygl4+P4h1r0zwUFOma4w/58uPxnjxXmczZeP2YV6b4LH/ABKNcbJx9mQEfWeOiG4p7HOLBKJFZl7jpWF42bzLq/SMHd5/QfUiu3iTfKq46kUpYJqd+w73DfntWtWYxPnSK3ulvULowAHUg4rpFGGz269a9SvfLJJkVTnuQDzXOeKILQaLpmp2cQRkeawufLXauS3nwSO3Qu4eRB/sxDsKxnF7m0JdDv8A4SWoDXuoEdAsYJ9Dyf6Zr2RrgZyPpXlvw9DWPhzf/wA9pC/5YX+ldabuTJYHoeaqK0REtzoPNDvgHp6VMsgzz0Jrnobn0yQRkVee8jgiMrnjH9KbBIvS3MECM8zYHavN/EPxAtdNDR2h3ydh/j6Vx/i7xlM8r2tq3ze3br0ryxstlm5J6k9alK+rLtY6TVvGev6qCkkzRISfljO38yK460VmjdGH/LRuv+8T/XrVnkEAnkdfwqvpZka6lH92bHr/AAg/1q0rDjqmOi+dyhHIwPQc+lSSDY3zcZq5dlTdMUXAHarSXPnMZJlGCCCvb/OaozYaXrOraPOJdNneEgg4Byp+oOQa9z8JfFeO8kjstf2wS5wJR9wkcfMP4f5V89AbfX/61W7OAXE+CcZPX2pkn1pr3hG11yI3enFY7nGQc4WQ+/oT69+9fJHxjluNK8Iz6dcKUkuJUtyMkMDnc36Lg/WvoHwr8QtKguLXw0EdIlXy1lY5y55GfTPrnr7VT+OXw1n8badZaxpuTPp8yvNF2lhOFY47tGOfdd3cCspRs7mkXfQ858KWDaT4dsdPcDMcCBsf3iMn9TW8CCfp+VNjRVHyDAH+R9KXay89PU1i3d3LQoxk1JuZeBn8MUxVAY59O1SfMOF2/jj+tAH/1Pim3gkviBZq0mSB8oyPzGQK76w+E/jvWAslnpl0ysPlKwyMD/wILtA9819M+G/ilruq2BsPBdu2jxIFPmRWEUEGD1VNw3E9eQMe/TMGrReOdYBW81y+cNwVaVlT2+VSBXAqaW50cz6HzdffA/4laeonvLFYVI5LzRIQPcMwb9K841TQtR0uVoLxDlMBih3L65BGRgV9PN8O9TZtzyxHPGWZi38jVa78AavEhMJilIz8qscn25AFVyR6BzM+YbG5uNNvYbyDIaNgw7Z9vxHFfRq2Y1a0S/ted6ggd+f6+tcbPAkkbo0QLcg5APNa/grVbu1tFt7oAKD8vPb0NOUbRugUtbMla0wxVxjFVpYR26V6DcJYXI83adx64/nWBNp4H3azUimjmo4BjjA+tc9N4Z0xrh55VMhJ3bWJxz2/Ou1e2kjOVHsQaqyIc5x1qrkWOw8IwxRaVFbxKERHYBRx15x+tfLHgxjD4ytxnlbtV4wOM4r6s8OZFkOOkh/kK+VNMiEHxFkgU4MeohfoBLgD8q2hsZy3PpKyQprlzsUHvz+Fdh4Xl1iXT9WGrwRQlEURtHJuDp5kfzYIBHPGP/rZ4i1bHiCdVUHC568Dp3rs/DdxqU2n6l/aMKQuLddojcuCPOj6kqvNOwXKMv8ArIwOfmFem+Dyf7B12Vv+eMK4A9Z09PTFeWSOPMjLf3h+VeoeEpNvhvXWGMmOAd/+ew6cY/HilFakzehUhmEcyN7j/wCtWVbX5uLu9k3ZL3D/ANAKZeSFFQZxyK5zRLppI5pMjJmkPHruIrRmSN+9mJG30rLlEF/oWpaXcgE+St5BuOFWazPm7vc+T5qAdy1SXMjbc+tZ0N21leRXqqshidX2MMq205wR3B7j0qGuha7ntWjbbbRbWJfl/dLlTkckZP61Zkmwfoa+dbfX/EGgvPpS3LzfZpiImnO8tE2HjY5yeUIrrbDxxftH/p0Kt6shI/nmi66Fcp7DbysrYBzXIeMfEP2OH7NCfnbIX2qfRtettShlljV18oAncB36cj6V5JrV9/aF+9wTxkhfoKjd2LWiuZrEsS5OSTkn60LjG0d6jz6dKkBwPm4NaEMQgYyOvT8KzrBjFfXar1JRh7ZXGR7cVptkjH+eKzIsnVZgeMxIR+Bagumt15GxbJG7nzW2574z1qxLabVzDOkg9BkfzFQRAHAb6ZPpTZQBK0fquR7HPI/AjNUZFN/Njl8toyRzyO1aMMpjhAj4J6/1olj3xs8nG8Yx/n/PFU1Q2SRRA53DIycnPXB70CLAyrYz05yK+vfh14iPiHw/HNKc3Ft+6l7k+jH/AHh+tfIJUKdw6GvY/g5qf2fxBJpsnK3ERx/vJyP0zTaA7+fwvY2/iOSyuoz9nnHmQ7WwAD24PQHIANW5PAelS8xSyJj3DD9Rn9aj+KOtXOgSaTqEYj8j7QYp2ZSWxlHUKwYAHG7GQa7wBhgf5x/nrWfKrFXZ5hJ4AcEG3ugevDKRx+dZ8vgbWA3ySREfU/8AxNd7d6/Ba3c8LggQoGJyMknGAB3zW5bziaISMuMjpipcUHMz/9XX8+9cAKeSeR/Suj0/wd4t1lR9msbiRWBxIUKIPfc20Y/GvRv+E6TTf+QBZ2dj6PBCu/Huz7s/pXNat4l1XWY2TU55Z0bBKO5KcdMJnA/AVwm9yqvgOz0w7/EOp29qyEB4YCbmcH0KRg4z65rNvJ7O0gMfhaxeKRuPtd+VeUDHPlxrlV6DDEk+1Y1xEtoM2SMp5HyHHtz61RW5uQnzk5zwDyfp0H50xFa4ttMuwy6haKzKOWK5J45IxzXNzeE/Dt0RFCWt84GF/l82fy/CumnF3K+9WKqOcc8/oeKa6osgERUKcbgDjB/ofwoA5CXwPqkJC2N1HOvOFf5GA/UH9Kzn8LeJImy1uWHqpVs/rXr1rp8STpLLIu7sBjn8T1rfWBRxijlHzHzrcabqFuha4gkQd2KkD8+lc3OyBC2QRjmvrVLcEgEE54wOa+Uv2nrL/hEtZ02DS/3F9e28ktzApIMagqInZeiliX/75o5LjUzW8PzJ9mZQwwJM/mMf0r5VvLxbD4q3CEYX+1W+bpyJzXqvwi1LULizvV1KUuyyIV3HPUHp9MV494zb7H8T7ubZz9v8wAe7BvTv1rohG2hhJ3dz6cVc+JZmVRyueTjHT0rrfD0upG11OPUYljC2qlSj7wSZkyvQdABntzXOvZL9uN8rAlhjB/xrovDzahJDqYvYY1VbbKtHIXyPOQDIKLt7dz6UhGa+PMjx/eFeoeExjwprjKerWw+o8wn+leTzOfMiH+1Xp3hN0XwjrO7qZLXHuNz8U0Etjl9UuChVB6/jXK+GZv8ARSfWST3/AIzWxrcgMgBrnvCx3aarD+JnP5uf6VT2M0dVcSkrg9TxWLLJt9q0pcY/OsiVSTk9/wDPWoLRFc2i3lxBdADkGF/UlOVJ6/wkAH2PpXRx6WnlADIGOP8A9Vc7HKkUb7+q4dfXKnn/AMdJzXVW+ooYN2KmxRrSKdG8LMP4p2JJ59MCvPXt2uLYlSRjqf8APrXeeK5Cuk2kajhlDHnpkZrhId7HywSQeaUO5cuxU2NGnmFsg9Bnn0p3nKBg1DfXEW7y4RwOM+/rWO8rlec4qyTqLCC51G6SyskaWV+FRBknufy9ak1nw7qfhzxIlpqSBHmtfNG1gw27yOo4GDkH/wDVWT4W1/U9E1tLnS7VruZkaNY1zn5h1GAe36V714fsofFniqy0rxTYOlw0M0cILKylnTzNvABJDqFyDhc7umaznJqxrSS1b7Hntl4U1rUNHm1uygMlvAMuw64H3iF6kL/ER0HXvjFSLcwLc4Oa+lvHmvN4J8zw7oUMLxy28sBKBwoiliCb14UYO9lBz1XkcjPzdI2wbI+p6mtIu6OdoikO87QOFHFRyxl83HpjPsDRjAB/yc9qa7tFC8ijdjjA7nFWIFBmXy+mOT/PNdp8OJzH4ssZYwf9ZtI5BO5SP61xSl1dd643Rhj7HuPwrvvhvbvceMbNYxwrFm7gAKf8KaBnq/x8Uf8ACDLKCMrexkZ7ZjkHFek2knnWcUvJ3Ip591Bry39oK4MfguG1X7018mPU7Uk/xFeo2ixwW8Vvu5RQn/fIxUdBmDqHh2C7lecNtd3DlsDI2rgbT1HrUaeHpFUKbyXjpk5/zzXVMwXHGMUwuAe/40guf//WmtfFnhyc83BiPfcen510UN1bXEY+zXUcn4/4V8ieJb7x/wCIHLXV4hUn7kUSIB9CF3frWD8Jobe58VzWd9J5hWN8FmIO/I4Bz2ANc7o6XNObWx92QpOR2PToev8An3qlLaTI+G3jcehXcB7cdq85Wz1O3fdY3TjHQE7v51uWuv8Ajmzwsd2Dj1RDz27elZpFM6xbFpEKERs2cjqCB/n2rTtPDmp3Eb/ZLKaTcPmMWX+mAV9e9cxb+OfH0eVTUdnThYoj/Navy+K/GGqRiG91m6QHr5L+Qfzj2n9arlJbO90P4baxrMvkzWVyrKMs1xGI8AdQGYAZ/GtHV9Q+Fvhe3Z/EGuW0DrlBBbuLyYuvXcsGQoPYMR7mvFbzwXo3iR1l8R3d5fMo+U3F1M+36b2NQy/C3wpLt8i6vIcfdEcvA/DaaV0h8rZreIPjZeWqm0+FOkPazsQiXuo7HmwVILJCDsV8kbclhgcjPT5N8QeHPEV3rc134nMt1qFy2+WSSQSuxxxkhjjjAAPQYFfVUvw8jmASHWr+PPJAdMn6nbn86dYfCLQra4N5dXM95OSCGnIwCO+FAB/HNHOrDUGfMHhfTbjTpJ1ETruwTwe2f8a8W+IlleJ48ub4xkqTC2e2PLT+tfpNc+E7OytnvpJUVYlLsx6YUZJ/KvhDxl40u/FN8zNH5UCsRCF4O3sW9Tj/AOtWlOTZE42PZEvEYnaR710Wi3WyC/jyPmtcf+RYz/Svl638VanbBVkcvs4UknOPf1/Gut07x3dwsxX7rqUdQM5BI9j3ANaOJnc9TkfMsQ77u1eneGX/AOKU1YnIHm2w/HMnX8q+b4vFsUzCZc/I24cY6V6x4O8Wm78J6sqw42PBM3P8KsYx655koUWTJ6FLX3VJ8seMdqy/DEynSodpzlfy6mo7+ObV1aSLMewcnr+HuTUGk6V9jiCRlxgbRycflTkraMSOyds9D2zWZKBnjvUBW7HPmEgDoQP/ANdVJH1Dk5Q/gR+uazLRU1NjHaM54HH6nHatCzmxbgDpjrXBeML/AFGLS2t0VUkkI2FWyTgjsQK89svF3jLTsLcAToOgdcH8CuP61cY3FKVj668WgyaXYyR/dMaY/wC+a4a5k+yW+wH53647Cu/0XXbHxD8M7TxFd2uySONlaPdu2tGxUckDqBn8a4nSfD2s+JmkvYUxCmWluJCViQDrlsds9Bk1ila6ZtJ3s0cyAZCSv4V6V4X+F+p64y3WpH7DbMQA0g+eTPQIvHXse/YGvQNE8O+GfDGpy6VCy3GrWhR5JZgdvlkbm+zRj77hcbTnGDuDYzVTxB4svNP8d6lpOrN/o1nqDCJghZ0a2kdYmAEiAkKxHPB4JB5p6sWxHLrWh+E9HtB4RsiyagZoGuOPPLRsFyu4HOcghSMZJGB1rz74pa81hrmlPpl7Ol/aibT7vDMrB4AqeYMHjeDsIH9zPU1pa94ymv3ltdIt47a1FxNJC7IpmVZX34B5CHpygBGBzxXjmvQk39pNNk7psFm5PJGSfWhrQ6sF71blfZ/kz628JfFfw74m0IeEPHAeLzkjhMxPEjg5DkqBswwB54PfjIpdP+DU4gv59ZvFjFvFLJEyZKsI0Lhn4JA45AGf6/PGkPb2Os22oX9v59vDKrtFnG8A9ORz7joelfSEvxv0ue5NpHp8rWsyNFK7ld4WRSrYT5lOAeMtVNPocXqeDMuBux1561EjR/aDDNkAjPTnkcH+VX757N72Y6f5n2cSHyfNxv2ZO3dt43Y644zVUZZ1kbkoMD+Q/KqEW79UjmWNOQqfzr1b4L6YZddudQYZWGHaCT/ExH9Aa8hYs8p8w/Mf6f8A1q+rfhr4fk0Lwuss3yy3J8589gR8ufov9aLiOG+KgXWfHfhvwlGx2rIbuVeD8u7g/gI27Vv3VxqsF5JKUba9wX2oTu2I2xF54wxNc18PwfF3jjWPiA2DAr/ZLM88ooxkZOR8gUntljjFe1soznGT3/z9also4fVvEbR6al0ivHmTaWZTlQOpPUd6SyvfEN3aR3MCKVZRgsDk9j3HeuvuLaK5jMdyoZeuDyOOR+tZMkUtsRDZRbUA6LtAz+NK4H//1/nKLWJNXkk+xCaxjzhQ6NucH1ddwFc3D4WubO+a9tmWJ925PLkXKnsACQeh717defEn4faETC97ESoziFTJn8VG39awZ/j/AOALVysFldXLZ6lI0U/+PE/gcVHM9h8q3MNJvFttErPdysTyf3CsOenKuKh/4SfxjbtlJYnx1Dxuv8iareJf2hNJ1KyNrpujJA7ZAmco5UeygLg+hya8VPiZbycyG9uImbk/Mygf98nimrdR27Hu48d+LYAFKQtz2Zv6inj4la+nMlocf7Lg/wCFeRx3mttH5lrfNKDyeQ38waifWvEkQAWXPPUxoeP++apSh1RNme2p8X72Fg01lMCBzjB/HrWonxpiUDzoZUP+4T/KvM9BsPEuqwJdyz2axSdNy5fgkfdUD09a7pPDkRhCzyxs/cqu1fyyf50P2fVDvJdTqrX426Q5X53TkcMrf4V1ll8XtHY7ftA4Hc9q8buPDJU7ohHJ369PyBpIdOngjkWW0LlhgGNh369QOtS4UhqUz2rXPiZo2ueHL/SrW7jZ7i2kiTkfedCB+HNfCK6hIZTHIMFcg57EV6zd6ZCXYS2Eqn1Crj/x01yFzo0CzM0hCck/NHJx+SHFVGEFsyZSk9zn1mJHSpFm54A96vDTY2bYkkeT6sF/9CxWpa+Ery84imtlHcvcRKP1aqcfMkv+HDbXejarAqDzooo5lPPCiVVf8fmHWuy8C3N3brdIOIJ4wkrnsoOcD1JI4HtWXpXhyy0lXmh1OGc3K+TNFEk+fLyrHBaNFZsjK/NjIOcDBPUNYi8iW3gBgij/ANXGp6dst6sR1P5ADACTsS9TqPNYJshTEa8Dv+JP61ehm3Ljb71rafrJtfDA0E28JYgq05XMxBOeW+nHTpWXEgVahjRKyq3Qe/0rPvGFuhlk6D0rQIBpDCZ/3ITeW424zmoaKR55HpkurXP2u4BwOFFareGo9uWXP1rqLjRPEtp4hhWGJPsBi+cDGc4PrznOOnaugltiMZHbmjmsXyjPAsKjTrrw3Io2P+9jA45Iww/IA/nWt4d1grcSeCvGN0Y9ImRYi4T/AFPlsHSVVRSS3VScEkNzmsW3llsLuO8h+/EwI9PcH2PQ11viPRYNW09Ne0wZDZ3AdR6qfcVm3rdmiWljltY8SjVtPsIIbcQ3VgWBvAR5sqKFWEEqoK+WiY4JySTWHO9xeXEl7eSPLNMxd3kJZmZuSSTyST60iqq+3qPpUnzRqT7gY781ZkRrAHbGOe/4fSqV9p9reMkcq7jEwYHpz2rfKmC3Vv4pP0rO8p4n8uXrnt6dv/r0DjJxfNEaIwMHAzTlQf8A6qlAHXrR9KZIwIoqRQFXn8cUdeR3ro/DfhnUfE9+LOyBCA/vJMZVR3/H0FAGx8PvCsniHWUknT/RbchpD2JHIX8TyR6V6n8W/EdxBp0XgfQfn1HVgIVRMfLCTh2PXAYZXOOm49q2dU1bw/8ACvwrvP8ACCI4xw80h/Dqe5xwPwFc58PPDN/LezePvF4/4md+CY4z0giPRQDyDjgDOQOvOaLhY7/wv4etPDGgWuiWigiBMM395jyzd+p5ra46dsninnIOBzxULtjGenp71ACEg4DfnUJYpgYP5VBeXUdpEZJDgdu/PbAHU01L2NkDn+IZ7UAf/9D81ZCqAqD09e3rVVjgZIOO9aAFrJwr1KmnbxvRs985ArnRtcy9/GU4NRgMRtXnPHArsbTwsZF86dgkY6ncrdfoev41cPhy0sUDMTKQOB6D6DP8+aqxLkjE0ie5sSXjbYCct7Z4496970CDStaU2F1hLtVzk4Ak/wB3nr7d/wAwPmm8mdpTFGMDIOF7Vdsr/U7K6S8t5iJYz8rHnn8R2quUi59Dar4Xtog3levGK5Kewu7dtkEsidhhiPyqbTvimkqFdctCDwN8HI5P91jnj6/hW/cXmheILPFhdKrk7lI4cEcH5Tg/5FZzUrPl3NIuN1zHnV5qWp2m4C7nV1GQu9+e1JofjzXNEvPNmladZBsaOVmPBIJIOSQfQ9q19Ua/fw9/Ysqo80cpdZsjlccDpnPWuEbw5fm0XUfNjcM6xkI+SrsOAwOPTmsITU4OGIVr6HRKm4y5qOp7fq/xO0nUNOB0qW/sL5F24CQTQMccbmJRxn1AP0NYNh8QPE8sUlzOttcLGCzx7Dvx6jnBHrXIXHhjUNH0ganM0UsO9UYqejEEgc/jWnoD2kMEl+EbI3R7cDZswOWJ7g571jSdOlRvQk2r9Xf5HpZfgni8W6OIVtG77fPzO00Tx3Y6tcpaahBYw+ZNFGDKpHyu2GbdjaNnU7iOM9TxU+o63a6VqEljqOhIWjON8NwskbAhSCrxbkIww6MRz15r5+065Bu8TH5CxY5H617F4Zu7y8uHkuJmmiAjg2yNuYJtKqFDHcFVV6KMAAdOK73e10eJZXszqbbxb4YBH/Etuoz1+Qq38zXTWPi7wu74Md1H7uq/0zWungp06xjj2p7eEZVH3APpV3MrFyLWPDE0Yma6ZADjlDnnocYzWla6z4FYn7RqDgDoFjOT69RivPdY8H3YHmLnb+Vc2fDV2jDOfxqkKx7dFrXg9pT9lW4uB2DlVB+u3muq0rxPoONtpAkQJ28AsTntuPUV82R2V3abiu7gckZ4962NOtbyxs7aWFmiBkIDSHYm4fMBkgc/RuvvUSaRSjc+mX8U+GZ7l7C7njimhZo2VjtwynBGSAOvvU0+iWl/GJ7JlYN90rgg/Tsa8X0L/hH7lri/8S2l06Bsq1vIEG84OCzrJktnOMg9+nNdb4Tt7Vtdjl8Npew2qlzKLhw4K/wg7EQZ9+/XApbjtY1NQ8OXsSb1Tdz/AA81W0HXrnwzdtHdx+ZaS8SxdD/vLn+IfrXsZOflHPtVCfRbK9U/aIlYdB61LiUpHK654L0/W7X+3vCsqyo3JCjpgZKsOoPtivLZ7S5tW+z3UbRt6MMV7Pp/hjUtDvDe+GbprdiQWjkw0TgZ4YcZ+vUdiK6jzbTVIPI8VaWFfHM8AEkZIHXHDjPYAN9alXRTsz5sExDIsnO3jmlc+axc4yf84r6Al+Hvg7UX3afdeWzfwhgGGfRGGR+IpD8INOXO65l/DH9BT5iOU8AAOM8CnxwSTyCKBS7ngKoyT+Ar6Ah+GvhXTlabUpsquNxlcIo+p4q6niX4Y+G7YmymhmYfw2gErEjtuX5c/VhTuKx5x4c+Gmqam4m1bNtD1KY+c/XsP88V6frPifwx8NNOXTLdd90wAhsoTmWRjwCepAJ/iPXtk8V5x4g+MGqXim28OwiyTkea+HlI9QPur9OT6GvEL2Ge7ma8mkkMzNvMpY7y3ruPOapLuI+kfDXhLV9Z1keNfiAVe762tn/yzt1PQlc/e9ux5OT09F1SPUpLgXNo2VCkFQcEk+vrg44r47s/FnjnSTutdTmcZB2z4lBxjjLhiB9CK7Sw+NniezkP9rWEFwCQcws0bD1678/pQ4PoHMfRD6jqGnoFmiMoVMtIvTPfgegqSw8QRX2UdSsqqXK4OOOuDXl2mfHDwpdAR6mtxaMRz5ke5T7Axlj+Yrv9L8VeFdbffpt3bzSFeVDrv2n1UnI/GlysfMiTUb201a3KwZMifMoHBHocHrWYvh+WQeZcuu88ncpJ/PNaDaFYm6S5jcoVxhRx0Ax9OlU7vw9LcTtL57YJOOP060rDP//R/MVoZ4JMOjg+4rUtbrCrGyAlTnce/wBa+jriwtp1ImRXU9iAf51jyeFdEuDva3RSf7vH8q5vaXNXBnn8uo29zpSW8yrFglxt4OCAME98Y4z0rnbPW7nTpQpIuIG6ox5xn+H0Ir1QfDvT7qYR2jSbyMAEbv8AD+dQXfhXS/C0cmm6jZLezXCK8c5Zk8rk5AUHByMg556EEdDamiOU8r1qeyutQe5so/KQ8lep/wCBHABPrgCs4bRgk4H0ruf+EaidiQg9qgfwoYyQrHBP+SBVcwrM5JjxtHB/OpFG5twO0juDg/mOa9Lg+DvjK50SLxBZxJ9kuJGiR2nhViyjcRsZw445BIwe1cZ/wj+pRj5kyR6UlK4NDoNUv1OHfzB338//AF6kW8jeKTfHtbIYEHjI9sf1qobW/i+V4XGPbjH+fak+RTuZSozyMf40OMXuiozktmX3v5rixW0uXdYWkDMFJOSOMhc4yM17FoN18LYNPOmXMSSTP92a7e4AAPXCptAJ4+9xXhpkBc45A6fh2xUqkffz83b/ACamNGC0SK9vNPmT1PYotM8CNMbmzmtk29+MZP8AsyYP6V6P4C0O18Q6nNdyqlusc4u5fsYVIZiOVCxx4jUA8hVUAA/KFr5aSMEZU5PSpxujCxoSCat076Iz9pbdH6E6LrGj6xcvZ2xy8bFT0PI5KnBOD7V1DaVGRtXivzv0KDVdU1KOwsZ5Y3nbDuHK9jlmOeRXrHjT4feB/DHhRtat7+8kviyRxLuQK8h68BCQAoLfe7YzUQjKKtUdypyjJ3grI+mNS8PyMuUwRjNcLdaekZ5UA9+K6f4favcaf8PrB/F9yTdSoSDI2X2MxMe485IQgnPToeayta1fSYIHljkWY8/KhBP8yB+NWxHn+papNpFvfQadCk09xZyQ4bHyh8DeMnAK9R/kU3SNW0nUdd8P6TeWrW9rBbE306klppf4Tu9d3X5uhwMCqWLi61BTBK0i3Fu4aJBlXDggqzAMQfXkYqvp9nfXlpZ2sUcTFZWANuNo8sn5jISxJIwcZ554FZ8qbKcmWH0618W3zokRFvJKJQORwCdrEfxA9BnnH1r3LR1NjbLbRjCjpiqnh/QWtIhGAN2ATjHYYrphEIzgjH/1q20SsZ6sljv3TH0qyurSgkEish9pbK/Su/8AAnhAa9cG/vwTaRHGBxvb+7nqB3JqGOxFoun65rhLWMbbM4Mh+VB+J6/hXpun+CzCoa/naRjg4jG0fTJyT+ldykUUYFtCu1VACqowFX0AHYVYWPAwahjOcTw3ou3bNaxyL3EihwfwbirsGladaDy7W3iiX0jRVH6CtnZnjHJpCAeSMZoSBsoiFFBKqoJ9RVObTrSfiaGJx6FAen1rTc5XIGD/AJ5qHBJp2Fc5a68F+EbxcXGmWhJHJEKAn8QM1xl38GfAc6EQW0tsWO7dFK/H0Dl0x/wGvXs5GenakJBwTzgcUxXPnPVfgJp7ZfTb5l9p4wxJ/wB5NgH/AHya811b4MeLtPjYrCtwoXcWt3DjjttYI5P0U19q7V6n1/pSbCTkZH0p3A/Na+0G5tpmtbqPZKODG42v+KMA36VhXOjIvyMhU59MV+l2q6NpGt2ptdZt47qMHO2RQwz7Z6GvHPEPwP0e7QyeGrmSxcf8spcyxd+PmO5c+uT9KakFj5DsNZ8V6Iw/sjUbiJUGFRm3p/3w2V/Suqt/ix8QYIxFJ9lnI43vEdx+u1lH5Crfijwb4l8KNnXLPEO7Czxcxt2+8OmewYA1xLSWWcNuUjtVXJtY/9LkJ9BtJhho1JNY1x4Xtd/yKydvlOT+ua0IfENrJ8rrj/dJH8sVoi8t5hmKYgHGA2Mf0P618xCVWD1PoJRpyH2GjW2mRgRAlj1c9fzrh/HmkNdC3uYyPl3KR0JyR1/Wu5n1IRIGnIfAH3eBx0P1ridZ1f7YDGeR14r24zvFNHiSi1JpnnMel7eRyaXyAjYxk16NpfiDw5p2iTWt1pkVxfOQyXExZgozyoTdtwR3xuB744qjaN4R1bxI11qqnTNOklDGC3LO6pkZVGk3kfU7sehobYzk4km2+WHYLnO3OACfQVKtqmM4Fdd4kbwda6m1v4eFx5GBt+0SIz46ZJRQBz/sAjuM1Q0bQ9Z8RCV9Es550hG6QqhIjXOAzsPlUHsSQDS1AxFs4+gUY+ma6xrbwE/hyOzbS5H1DcWkuXlbHK8BEXCjB9QTz1xWZLZ3VlKba8jaOQclWGDz0/AinqgzmncLHHS+DtJlYmSJeevaqrfD/T5AVTcvpjivREjHpVtEH0FWpMhpHnC/BnW5bFdVtI7hreRiqS+UxjJUfMoYDBI788Vy178Ptfto/MhZZRycdMV9Ei/1CW1i09ppPJhZmRAxCgsAGOBwSQAM09VXG5h0FWpMmyPmTw9da7oWps9tbI8yAjbKDgdRkEMvP4118eleIPFF5Z/200QijclYiQC24gnPUAHGMluB0FdZrFu89w92wCLnCrwM4HfH60+28M3F1ALy6kZC/KjnaB2PWm33BI7S80y8WATXE8DkYG1JY2IHoEVsgD6VgPZbwznoOpPT6mss6BqVoPtNvl0T5iy/wgdz6D61ma54vu7g2unWkYaOLhmUY8xsnLsep64AGABzjJOZUW9ijora1hu50tbeEuysCGPAHHH5V7ToegxabEowDIxyzdK8a0DxW1jMqXMKbfUdf/r16tZeM9NlKqx5YAjBB/P0PtWiskQ02d+irGuF4yMZ/nWbcSBTjpj19TVe212wuUVkkHJwAfbrSXE0bfxAnr2qWy0is85DEccV9c+CLWG28JWCpgh4RIT15f5jn8TivjeVq+q/hHq8GqeEI7In97ZMYmGecHLKfpjj8Ki5Tjpc9GWIbuAQScVY25xnk5/D9alVCx4HPQ0oQDjrg+tBBGyALzVaVCoIXjNX3+U561Tzk4PU4poTKoQ4HvzUbKF61cyNo46f1ppXJBBpiKoXJ/X/AD9KTZjGOMj07e9XUVEZXwCO4yeR6cf4V4TceKvi9bassd5odu8O7B+yhirAEchzI+3P+0BQ3Yai3seykFOTwf8ACmtJg7R6mpiWmhDyKVPp3HfGR1qN1Y8jOT/OmIj8zcnIxj9KhYJkOpyaXgHOck00gL0oAqSxrIrJIAytkFTggg8YP9a8k1X4L+C9TvGu4kltN33o7d9iZzkkLtYD6DA9q9mKZXB7VXIRSQ3X2pAf/9PwFXZTgHv/AJNTR3bxc5J9qrhXxg9KZg5rzrI7Ls6SG11y9tWura2mlhBw0iIzICPVgMA/WuZmk3Nx9PSu3u/iB4ovdPstLmnYQ6e8jWygkBBJt3Lj+6NoIHbn1rh3G872Jz/OqtbYzlrqyqcZ56UpUEYx9fepj15rsfCXgu/8XTTJaTQWywRtI0ly5RflXcQAqsxOPRcDqcCqRJw6QRKxYDn+ldBpeqarYW81rZStHHOpWRFOAytjIP5VNqujvpNyIZZYp1YZDwsWX0IyQDn8KpKpUjFNMGi5vmlbdOxYgbQT2AqdFKnJ4qGFt5wK6G1tI5o9znDfrQA/RLO0u9RitdSuBaQuwEkpXdtU9SFyuSOwyPrWjrNlo9ndy2+l3RuhHM6eZ5ewOqnCuPnbg9QO1UjpkoX5Bu+lRrCUyG6j1qkS2SRxYI28npWlNbMqsH4SMbpG7Af/AK677wB4Om1eZdQuVIQNiMHjJH8R9h1r3l/h1o0ulvZMgKuTuyOWPv1rRLqZt9D4X1OY3hNvbgCEEkcckev865TTl8QaPMy6PcDYzbmikAZDngnnkfga+sfEHwViYs1i5jHZVO7p9cVw1x8K9QtXWUYztxg7h7delS7mqs0eLTax4mutOuNKnjgje4ZQ0sYZcxg7ig57kLz6DnOayRp+owLHAXjKpnBI6A+pAyeffivU7zwfrFtcKs0ThRkEjkDp0Nc7d6PdRJI+1j5TYBIwSM46U41GtBuC3TPOrgtp8uwqrAnAMZPf61oQuyEFeADkAdBWvLYLJOC6DkcHHPvVeWwdE3ryAcN9PWrckxKI6W5lYh4yQc54PQ16j4Turu600PcOZMMdpJyR7EmvKFieJwsnXHHvXs/hWFhpiB12MM5A/MGoewzoTEqxMrZzgbceuR1/DNb3grxjceEPEK3n3reX5Jl7Yzwfwqg8P7rdmuY1FSkbuATxgfjxWTZpBc2h+iWm39pqVnHfWbiSKQAqw9D/AJ5rQABHy8H/AD9a+H/hz8RLzwW0emXhaSzOAQf4f8BX2Po2t6frcC3NjKGDDsc9fp2/Q1UZXMpw5WbZVWGWH+c+tUvIyMj8/wD69WmdUGTk+gqPfuHI7/T3qiCoInDHdyOnBpm0E4b8avKQD+ePegqjfe/SncVjPOOxOaVlJBXoe/P86sGNW98VCUIyT2ppisViATs/z71ARzj86s5bqvHT26U04Ix/npTApGMA85/CovLG7C5q02S2AOfXFIQSSR1HFICq3I745/XiqjuM5BPIq5KyqpGPaq4dHG4UAf/U8HlWSF/LcYP9Ki69a2tW1q/1kRfb3L+UCFJJY884zWNjnNeedbEKg/SmFT3p5GDXTW/gvxXdabHq8VhOLaY7YpnXYkhBwfLLY39Oducd6aJZyhTnJ5qeJ5kBRGYLnOAe/rTzFJFK0MylGUlWVhggjqCPakU9BVIgcAxGWJPYZNTqM459qaMngDpUyLk5PSmBahUZXoOx9BXp17F4GtrGBNIuLqe88tvPZwiRiQE4CqATgjB+8evUdB5tGi/XFbltEAOlPoI3IXO37xFb/hzw2/iDUcSAiGI5kb1/2R7/AMqzdF0m71i8WxtBkn7zEZCjuff2r6p8IeGYNLtoxAAFT7nue7n+nvWkY3M5O2h0GiaHBplqINgUgben3R/d/qcd/pWnPPkcVamkWMeWOAOlYM7MTu6dqtkpEMrZ5bnnn0qoyrj5h/8ArqUngkjBHekODgmpLKM1layn5416emP5VkT+GNLuBjYBkYI+tdCUZup96jw2OOf8/SgDzaf4Z6J9+FE9emea5PVPhlYzZPlbT7fpivdjlTzzmmuqsdp79PxNAHydqHwymXiFmwpPXnGf/wBVdLp2jtYwpbyZJjGCx9h15r36fT43yoHXjFcjrOmTQxmSEEgDJI7fjSaKT7nGXFmy2aMwILcj6VxWoWZknjtx0J3sPZef54r6R1jwHLZ6Nb3bySFnjV8yEEHeoONueB6frXH2Xw+N5F/atxNtkYeUFVdwAznJOR1+lZSRvSkk7nis9nl8AdBXV+ENb1bw3d7oZWEXXZ2BPp1x79jW/N4O1CPXU0eRGO6Mz71Ut+6GRux16gjHrRd+EdYsrJL+8i8uORgqbmTLE+i5z+lQykz6A8PfEaxv0CXmFY9x0/LtXoont7uISQMGBHBHIr4p+w3VrIOGRxzgZFdbpHivXdKICOXX64P49jTjN9TOVNdD6vSMyQjPUcc0xULggdeOnSvMdE+I9pdKsd2Nr9PQ/kev516HZapY3CEwuM44Hf8AKtVJMycWi045JPUdR1oCB149OR0FDqrYdSPU0v3RuHTtTJDyYycgdaqvAO3H8qteauQPWoy4zxk4oAoNCRyR0qLZg/NirjkADPSqrnHLdqdxWInUHqO/+fxqiLZBnyiMHmrrMCCMZ5qLcfSi4WP/1fCOCMmkx2pdpB5pMZ4NeedQ3ao4NdZc+MNdvLGPTrp98VvJ50G4Z8tmAVtpPQEKPl6cdK5jAzkdacCegHTtVLQh2YSvJNK00x3OxyT6/lTVBzipQoI7fWpAp7dqaEOigeaVYIFLu7BVUDkk8AAetdzqvgDXNA8q31M28dxNH5yW4nRpCmN24bSVwR2DE+tcdAz28qTxHDKQyn0I5rZm1fUb4xm7kMjQx+Ujn7ypz8o5wByelUIoxR4Pz9cYrp7Fbi5nSys0LyOdqqPU/wCfoKw4lB6D6V9FeAPB0tiEurpB9rmHAY8Rr1/P19OnrVqNyXKyudb4L8KQ6db+SwyzYad16seyj/PHWvYwot49i8HjIH6AD2FVLC3js4ht/h+7nqc9z7mo7iYkVpsZLV3IriXccE+9ZjEk8cUryA9O9REg8nrUmg5fbtwKUcYHXjt70cfeGeP89abxzn6etAAcdjmotuB/nmpDuP60mNueg+vvQBFjnd2FLlcbqftwM0beMt+NADAO36mlOMbvwyaeV6H8aBx1xQAl4TqMRhu2LdAOea3PBMttoF0RdZlhI47nrxnPGfyrEGO/XqKd05X059qTQ0+h1/iPVbDXbqeGeMKkiCIkABtikkKWHPUk8etcRdeEdH1aazLzSKsJ+cA5ZkB4Az0PbPPXNSMuQQOKgIlXlDWbj1LUiuuhahNqqw6pbBdNjBeKCA7y7jgB2JVjkEkn8vSuX8VabHpUsX7h4ZGUySxkEeWhIVMjtk+vt613MOqXcDDJyB2PSr0mq217G9tqEKyCUAOGH3gCCAe+MgGs+UtSPM7DRpr2y/tCFCI8MVZuN20ZbaDgnA6kdKuWb3Nuu+3lKrzxnK/rmvVJ57LWLyG7lkCImEMexdoTGCFAA7Vxel6Fr2im8MISeJYnePbh2LthEAB+YYzuIHXFA7lmx8XanaAJMokXgcHBx+OQf0rrbTx7pEn7u+3REn+IEfy3VwmgWialpd19qjdbm1QZbOFJZwFXBGc4yT7CsyW3PO7rVpszaPd7bVtBvUCxXMYLdiwz/PNbJ03eA0MisCf72OPxr5ia1A5jyp9avaaWt7xWmJ2A5O3qKtENH0edEvWXCBTn/aUcdOKY3hzVCp+TJ9mX/GvOPFXiqK4jt7LRJJYo4EO5gSrMx9cHPHbnvXmGpa14ikUiPULtR6CZ/wDGqsTc+lU8JaoxLMUjHbLH9cZrJul8OWExtdQ1iwhlX7yPMgI/BjmvgvxhFqE0rNczSyMOcuxY+o6mrdjpJ1ixh1KEY81BuAJHzDhv1FaKmhXP/9bk9H8G6BdeF59e1XVBHdRMuLKNMuVboS5IG7qdoU8dweK47WbKysLwRWEpmjZVcbxhlz2ODjIrP3yYPzE5AB59OlMHznNcLt0OjXZht+WnqjE9KfEqg4OTV6OME8jpQSVkhxyasKgIG6vQvCPgyx8R2V5f6jqMdkltE0ixlS8khHtlVC9idxIOPlNYGq2NpYRwS2k3nLKG6rtxjA655z+FVa24LW9jAWMdO49KsqgA6/59KjHHGOa9C8EeED4huzeXgIsoCN56b27RqevuxHQehIqokyOk+HvhNiyeINRQFf8Al3jPJJz9/HoP4fU89hX0zo2mCKEzTYLHG4nsf7v+Pv8AhWJoenGdxKqhVXiNQMKoHGcdsdv/ANVdlM6xDyl4AGOBg1stDFu5RS+upJJI7mLywpwhBDBlI68dPTFUpp2LYH+NSzTHO2s7ORnNSWkSDBbdnGeMdv8A61OwO/SowcHilzzxQMnyo44oOCMGoc8Aj9KfnFAA3oKFyTn9abhT0/xpenAoAQYzjvxgfpUmSMk0z5ieOp5pwwVAoAQY/PpTeMYp/IGT6c008mgAH3844pQT0IppHPPX6UvTlj3oAc2V6Hr3p2A33uDUaAZ6ZqUH5QB+P9aVgIHt1PI4GTUBhdTgj/Gr/AOCe9JlXGAM/wCfelYaZm/MnSrEV5cW/MTEHHXNWDHHkbj9agaAj8KTiO5uxa8zRm2vBvR8bumTjOD+GawdXisBev8A2buMPGN3XOPm/DPT2qPy3HQcelRsDjI7/SlyhzGeY1J6U5F2glegq26f/rqN488VVhXMuQMxJ9aoTR5H1rbdBjBH86qSR44xkdKaJZ5z4l07zbbzccpxn61w+jeMLvwnDLpqQLKrymUFuo3ADHT2r2bU7Xz7V4164yM+1eQX2kpNcFyB+laxYrH/1/D8bjnrUig9etMAwevXpUigdDXCbkqdeauJuOBiqyg9RVxW44poRJulKiMOyqM8A44PUfT2piLgBRnHvmpAFByOtXbOzuNQu47GzUyTSsFVR3JqgNDw54evPEmqLp1p8o+9JJjIRM8sfzwB3PFfVGi6RBDBHpdgpW2gABA6se+cdWbqT/8AWrF8N+HoPD2nro1iVadvmuZhn5m+pGdq9B789TXqul2cdpGrEHOOAf5mtoqxjKVy8mLKIRjGeh/piqE8rEF/U1JcTbskEHFZE0+4EjNJsEgkkJOB/wDrqMOM7f1qISZX3NAO7p+tJFE+4Af56U/du5FQP8ylXxggg5NOBwcfpTAmHXHTinHGfc1EzA4x+P6d6fk4BNACkktntTt65I74FQhfWlzzsPvigCVSB27U7PQ+lQluPenk55XkfyoAkUkDLf5zR2CnjvUO48EU8ONvGMY/WgBcADIxTDz16UrNxnORSJz+NACh2zgU9Se3b8/aomABJGB9KUNjJPfFAD92fb6UoY5yvP1qLdgc8c0oOAcE8dqAJcgcHnHFP3E8cVWLN3J/H680ob0oAsAqRg1GEQDHWoi4J4NKz8D19frQK4YU9KjaPBxxSh2yQOtRl36E/wCfegVyJogwBP5dKgaEY2jtVx2YMRwR0pjEEZPrTsBQeBSpFeeanpZhvGQLkdRzjg16W7DBZcfjWZPDHK+5wCcd6a0A/9DxEA8Yq1FGZGCICxPQDP41AA3TrxXrmn/EyHwx4MvPB9hBGhuxG/nKB8zKefMJBLeiDICHkdxXElc2Z5gY3iYrKMY6gjFToMY+lX9Q1ufWYLcTpteJWBPrk9/pVKNCenNCv1G7dCYDb0719CeB/DR8PWa6heJ/xMLlfkXHzRRt0Hs7d+4GBxzXM/D7wogiXxVq65RG/wBGiPHmOP4z6qp6epHoOfbtKtZbu5M85Jdvm644Pf6mtoLqYzl0Rs6JpojTzZh7sffPQe1bc0x3YGcDj/P4U12SKJY0wFHYVmTTnscVTZKQk0zZ29hnpVIknk849OaieTnBz7imqWxkZ5qCyQckClPBJHWmbl3YHOelKpOORjqKaAs7sjHal3E8npVfcSB69KUyYPPXAPNMCcg54Hc//WpyEEYxUOSDz0HFO3IM46+tAFlT2JPHNA9zVcudx560b2GAp570ATkjPrij3NQK27tx3qbcMe2f5+9ADmJbAJ9qbvwABTSw60gIJ49O9ADsZODxTgR94c03tg9BRuI5/KgCTcffOf8APSonJPvjr9aQnoRjP1prNt6UAP3DHFHygE59etMBO6jcO3+f/r0CuKSWycdvWk3Hp+VMJbrjOKbn1/CmIk3FQD0pd46Z6f5xULMQMCmEjbjHakBPlvWozKwOFPXmonft68H0puQR2xTAcWwcj3pjS9h3pjsG/D/JqHd7+tAEkjY4xzVV3jVsc/r/AEp2QB8x4ph255I/GgD/0fGQrAZNToiZqAZ3cVbAHQVxmxIACOK73wN4UXxHfG4vcrYW2GnccFvSNfdv0HNc/wCHfD994l1OPStOHzNy7n7qIOrsewH+etfSUNtaWltD4c0fKWkH8RHLMR80j+pPb2q4oiUraGjEDqM6BVCQxgJHGvChV6Ko9AK722gW0gx3YZJ9qxdHs1hTz34xlVUjoPWtGedTkHp+taGSQ2abqCc+vvWXLMFGSfr9aWeUL0+X61m7skvz/L15qDQmLYJGcnpxTkc44NVt3fpTwxH6UAToW3Z7VKWBXr161VWT5cEVKfl78H/OaaAm54xz/n/OKeCOh5x6d6rDsMdRjmpgc9e+cZpgWNxIJxzSkg8HpUIfru7YxSq56A98/WgCTPNAOOKYTu5GaA5XA9DQA/dg/SnlgRt74qA/PkYPH+TxTg3X2HNAEh64z160Ljlfrj/P0qPIxg07zMErjGR1oAl3A59f/r//AKqQtx6+mfpUW75ewobHQf55/wAaBXJN2Pu5yKXrx2qBWO3aOlKH47YoETKw+96j/PSj3B4/wqMOD/n60Fl2YJ6A/h/jQAuQ3GcUMQDzTMk4xzimeYT1HJH9aAHsRnnI+tRO2eeMU0tnnFMLfLgfj3oAlLtj0qPIGcfiKjLjIx6U1nz0/wDr00A4gkkDH86ibIXaD39qaDgH3/Wmn0zmnYAOcEjt1qszkcAn8qczYH15qMsfp+Bp2A//0vHupxVy0t57y4SztUMksrBERRkkngAD1zVNAD05xX0Z4I8PR+DtLj8T6gMajeJm1U9YY2/5aH0Zh09Aa5ErmknY3dH0aPwZpP8AYVqRJfXWGvJFOeeqxL7L3Pck5rq9HsUGGcg9z7n/AA9KxdOspLi4zJne3PPYHn8zXZLtgjEacCtTLcttKqDYegH/ANaqE8+0ZH0qrLMiqSec9fyrOmn3DGeT296lspIledn4P40m7nj8Mf8A6qrZVRweo/z3pCSOO1Ay0GAPXj+lO471VDdvap43yf0oAlznp/n8qlQsw46j0qHvg9amUkAcjnvQBMMbs4HtR1HvTAcDI/H2pBjdjj6fjTQEitzxUgck5PSocHdk9vSpIwcbc+gpgSAjrz604HHP5VFnnAPIHFLyT8vegVyUHPU0cAYPfr7VGpAz2zkUrMS3Bz2/OgQ8N/doLbeMd6YpxnnntS7+T69BQBJg52+/ahj0U+oH/wBao94Ix1/GjJ4bPqevIoAXgDn09KBkeue//wBemMRzihjnjpx/OgA3ZHp3zSbxnj8aRmOSfemMB0z+BoAk3gDk9e1QySqG2jq1NZ8AnmqbSDzSR2woB7UAXSxIx25NN8w9VyAeuPeoNxYbRnA/wpVbjvx/SgCQk9VqM4B3U7du/wDrVDznJ5q4q4ErYDflTW6cH60gGFyfSoXPGAOtdHs1YVxGORk8VXfbn5+vv/8AqqRiB7896rtsJ5rFoZ//05fhv4Mt5Ld/GXiJB9it2xbxN/y3mByBg9UXv78eteiXEt1rd42o3rbmc4Qfw5HT6BT+Gahv9RTVXjtbNPs1laqI4Y0GAqfwjvlm7k1vaXb7P30uMgAKPQDoKwWgm7mpptoun2YhfJY5LHqQTyeeuM1LLMuSzY9s1DLKTkDAH5VRllwBzSbKSJJZd3eq247t1VzIDwTTWkycnr61IyYy7s46df61Ln/9dVFPI4we1TBh1FNASqwXnnn8KlTkD0qruxwPpUw4OKYFtGGcH2PFTLIo5weeAao7vTjmpFkOQD2x1oAuFwDgfT8aTPAz2qIP2alBGdwqgLBY5x6dKkAcLluv4frUCbs7m/zmpYzzj36j9fWgCUZ6L0Izz/TtTsjHPeow4AGe4wetL3AJFBJL8xwTx/T8fSmE/MQvA6ik3ADaP8/5NOJOCBxnuaAFDFTjt0pu4L15/wA+lBPG3HWk7gHp/ntQA7nbwM/0oB2jaBTByOODjtTm6cdBz/n8BQAgw33O9KzHPHf19qbu43evr3+lREgH2PagCUlcDbwefw9KY7NyQME8CmEgnA/z/OkxznpQAksqqvPGB29qorjZ83U+x696mm+ZCnfBFVd/lqZD0A5oAsA/Lk8n2qQHkk/rTEIK7vUUwkdR0IoAkJByT0pAS569PrUWecfhTCRVwdmBMSW4FRMxBxj+f400yBhzUTMe/St5TFYRmHfmq7ODg5QcfxU5s4x+FViJG5Xtxxn+lYNjP//U9F06yjLApnYp6n+I92+npXR5VE2r71Uj2xqsadunSoJJicEHnuPr/wDXrnBFhnKgk8479+f/ANdUpJSxBzzUTyknvURc9/fH+RUlE5kPf0oD+3OKqsx6Djj/AOvSBqALnIOalDYGMdRVVWIHTA61IvXAPX9KAJ1JPXmrKNnlqpK+f89alViq8n8KoC2ecCnrIAfWq24E8nOBn/OKkBUEZ4/CgC2GycdqlVgcen+eaqBgD27nP+RT0bJ5xx+vpTQFvcSxxUoxt7HHAqmr85btjtVgHGT0xTJJcnHofanhhnLflUWQBu/Knl/lP0547mgB+cnJ/wA+lBJUHj35qMOQdpP0/wAKTeMYFAEgkydpzg/0pA539PamgkNyOtNUg/MR06596AJicHOMEdu9BJ+6Op9Peo8926Y+v50Fiw2jj1JoAeWz97qT9OKjJzgvQzEYC+v6VGXwNoHXtQA7JOc9M0MwOAen/wBamgkHj8KjBUck57UABOR6YOOarFVB9Qf/ANVTs+/kDHp3qMfN+X1oAf0/z6U3p1/Wgt8oUDrxmmMwJJ7UABOOOg61C3Bz+IqQgYqM4JIFACE8cVExOMilIzk9B61XJXdTuA8tt4HFQF2BwuTQxy3NML89cf5+lAH/1fUnkDHIOPpVOSXGQBUcs+0YWqcku85B68VzNjSJzKcnJ696buPfkGqhdd3FODHp1/lU3LsWQ7MeKkByMdqrhsnOaeG7k9aYi0DgHJ5FShztwe/NVQ+BwR1qUPkgkAUIRYBP609W9TVYSKDkdKUtuPPeqAueZk47fnUvmZ5HU9apgt944qVWyCf6UAWwSQOv0qQMSOmeOAP8+tV1IOeee2afvDEkYznH0FAFpMEZPfAxVgNyD2zVVTyAeewqVTuxg/8A6qokslixAycY4Huacpz1Gf8AH271FyDtPXPfv6U4EAZoAlyPvE8jikOADg+/TgU3JJyRjpTCQeST36+tAEuRu/zmjgDk4I9ajJOdueo/Sm5O3nqRQBKWOfQZzSF93zCo15/LJx/KlDDOT1NAEgP+f5VHIecnB5607LY2jvULHGCT16UAKzEH5eB/9amuQQG/zikAB5b/AD7/AEqMkE4oAk3DHH1pC/POOOPxqM46HoKQnPyj17UASEqDgdKiL/LuPQcf4UxmI96YevOTQBITkYPpSFj1x2qLcc5PWkzng4oAGOfQd6hJznFPY88n1qJmUg96AG4GDnp9arMmW47e1Th8HOOtQsAxyw/rQJn/1uvll+XBz6dqrmQFjjvULOGYYIpFYDr1rjZaLG/FWFJY5zVAMSOOanVgDx6UFXLOcdO1SA5yT1Wqm8hs1MMDr2NUSyyJCoyKcJPx/SqqsR9etTbiABQIs53fd9etPU5JBquGzyeuMZHH8qlDA8dhVAWt4AIz1oDjP+cVASMYz+lHGMZPHegC8mcfWpt4Gcd6ph+cH1/z/OrCtkAt9f8A9dAFsOxPHXr+PvUyYGCvAPQD9apo3PXjpn61KH2sPQD+VUhMuBtw5xyP8ml3DOB0qsrhgKC2fr1/L0oEXN65yOp5/H600EbRj0/DAqAsR85OMcZpjMOR69vfigC0rf3efX8KTdyB6Hmq3J7/AI0ZAAzx/higC3kBckg55/pTcEHgdKhViD9entQrAHimBZDKRkHmmOcdOv41HuxkkfSo2c9R2HbFADido700kHnt/jTQ2T1/zimbgTwM9v8A9dAD8+mMDgelIzHp3qNjuHv2703cRz7UgHAjAJ6Y/wA96jJ7dfb1pCe5pjYwfXPagCUsBzjv0qIkjkdelNyMelNY7h/nmgAYkD6cZpuQT8tIzYHbFR5ANAmPbAA5HNQtuycf5/WguGGDx0pmV/iOPzoEf//X1ww/h7U8NnvVQDBweOBUwkUgc9+lcZRbwvbnvj1p3XHaqoPJP+fpUhIzhu9MCwrHrUm/BAGeP51V5B5PenBs/MP8mmBaVs8+1TKxI4HvVNSMYA69RUobbntQBcDE5x0/OpVPOPQYqkhK9uKkLAjH4VSAtlwRgVKCBxVLOOT0HHXP61IrDaB1JoAvK4yTnk9fx/yakyTjPA6+9VBnqf07U7cc/N0HFAF5GyMZPIycHtUysMZ4P+e9ZyuRnPGeuKl8wHgc+tAF4OFAFO8zHI+n4VRMmOvU84p2807klvzCR196QHnn8arA9RyacW3Djv8A0pgX84UAmmsdzBR0HSqisVGSc07eB16nr6UAWVbHHSlZjnAqoCCf504udvWmBZLc46+lQs2BtBzxTUYcY445ppfgkEg+tADy2P60u7C4/XvVYvk9fwpdwbBoAm3g5Y03IIqMsAATz7e9ML84oAnJAG7PHpUOeOabklTzioiQBk0gJSQ3QdeKp3V5FZIJJjhSevpU3mZ9+KjZRINrDI70AOLgqCDnPOfrTGbOAOtIxwcLTC3fp9M0CY4kdetM3beCeaTI6YzQD6UCP//Z</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O40"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O41"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O42"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2309,10 +2309,57 @@
       <c r="L41" t="str">
         <v>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAASABIAAD/4QBMRXhpZgAATU0AKgAAAAgAAYdpAAQAAAABAAAAGgAAAAAAA6ABAAMAAAABAAEAAKACAAQAAAABAAABLKADAAQAAAABAAABkAAAAAD/7QA4UGhvdG9zaG9wIDMuMAA4QklNBAQAAAAAAAA4QklNBCUAAAAAABDUHYzZjwCyBOmACZjs+EJ+/8AAEQgBkAEsAwEiAAIRAQMRAf/EAB8AAAEFAQEBAQEBAAAAAAAAAAABAgMEBQYHCAkKC//EALUQAAIBAwMCBAMFBQQEAAABfQECAwAEEQUSITFBBhNRYQcicRQygZGhCCNCscEVUtHwJDNicoIJChYXGBkaJSYnKCkqNDU2Nzg5OkNERUZHSElKU1RVVldYWVpjZGVmZ2hpanN0dXZ3eHl6g4SFhoeIiYqSk5SVlpeYmZqio6Slpqeoqaqys7S1tre4ubrCw8TFxsfIycrS09TV1tfY2drh4uPk5ebn6Onq8fLz9PX29/j5+v/EAB8BAAMBAQEBAQEBAQEAAAAAAAABAgMEBQYHCAkKC//EALURAAIBAgQEAwQHBQQEAAECdwABAgMRBAUhMQYSQVEHYXETIjKBCBRCkaGxwQkjM1LwFWJy0QoWJDThJfEXGBkaJicoKSo1Njc4OTpDREVGR0hJSlNUVVZXWFlaY2RlZmdoaWpzdHV2d3h5eoKDhIWGh4iJipKTlJWWl5iZmqKjpKWmp6ipqrKztLW2t7i5usLDxMXGx8jJytLT1NXW19jZ2uLj5OXm5+jp6vLz9PX29/j5+v/bAEMAAwMDAwMDBgMDBggGBgYICwgICAgLDQsLCwsLDRANDQ0NDQ0QEBAQEBAQEBMTExMTExcXFxcXGhoaGhoaGhoaGv/bAEMBBAQEBgYGCwYGCxsSDxIbGxsbGxsbGxsbGxsbGxsbGxsbGxsbGxsbGxsbGxsbGxsbGxsbGxsbGxsbGxsbGxsbG//dAAQAE//aAAwDAQACEQMRAD8A/PjC5zznOR61bUbgAKgI59/Q9asR7dozXkHcPVcpjPIq7CDtxwf5frVVNpA6+vNXoRjJyaCS/AD/AJ49q67Tc/Z9q+p6+lclCDnbg8V1WkhgrDsOhqoPUJbGpjJwaUAUoBP49cU4DJ/nW5mKMZ9xW5oTbdQUN3B/UVihMjP41raM2NRiYcndjj3FAmcn8bow+h2Uhz+7mdR/wJc4/Sqvww/eaTqcJ6AJ19w3+Fb3xlh3eEoZjn93dL+OUb1rn/hMCbLUM/3I/wD2atfsma3PS7NLGLQJG1gB7UN84Klu4CjAyTyRjAzXe+Hxpn/CG3EejhFt0u4+EGAG2vuwPfvXD6OrT6fKtsQswJ2NICyA8EEjIz+YIru9Dgnt/DF4lx5TO9zE7NChjBJD9VLNz680uhTMybO9O+GH869P+Gy/8VQrLxi3uSPXPkP6f415pNnejH+8Ov1r0v4dKW8QsB1Npc8/9sH5qY7ky2Zy0i8Edql1eNRZ2JXPVmIPs3/1qJE3ZDVZ1pf9D02Pv5Tn/wAeb/Ct0YHFogMuCOay77Ju5MDo3StyNWacEeoGPxrAuzuuZT6tWdbY2pLUiyo7Co9oxnFShTjinbfSudM3YwKc5FTKM9Pypqj1+gqRVOTTTJJEyT6VOFyKbGuf8aljUkkUxWHR9x29anCgdOM9aYq4FWMZG09xQIeq/Lk1Kq/KDj3oQHaM81Mg/KgBEHGR+VWFH6+/aiNcKSaegIxu70EsUgg5zjsaexBGDzxT+GPHp6dKDjjAoENCnac8+9OYYzjp70o5GKdgZwefegBgz1/WjgdKcAp/z+GaqyyxB8ZXjjmmkB//0PgBlz05Oe/Gf50+PGMZ9vWlcAHcfWkTAyO3+ea8g7iZAw4ar8R+bJ/SqK5B57dauREbsYoEzVi610mlkiRoz0K5/wA/nXMw4UgV0GmnbN8voc0R+IJbHQkA89aBu6CjAIzTvumukyHLnPFaOlEjUIs8guBWcBxhqu2rqlzEzHow6fXvQJjfi/uPgz5Rn/SYznGcfKw/rXIfCTYPt6HqYVP6n/Gu4+KSbvBNy/ULJGT+LY5/GvPPhAd91coMsWtc/kwBrVfAR1PV9PSabRrnBcqd3ywDEvQfcOR83pXd+EhnwffAfawFuYv+PwfP909Pb0I75rz7S3mi026a02xSYO2V9oVeO5J/nxXe+EJNVl8IXx1c7pFmi2kmMttO7r5ZK/THakhshkHzIP8AaHH416R8PD/xPLhumLG7PPtA9ecS/eT/AHgOnvXqHw5UHVr09cafdds8mMjv0/ClDcU9jmgpzjBq5rIYpYq3GLZj+ZkNRbCDjpVrX1KG0Unn7Kvp3JP9a2OfqchbqGuEx/eGRXKStmRnIySe1dpZjbchjzjJ5+lcYxLsSOmTx+NZVtkb0t2CA444qVcfe7E8UxBzgVKoBJzz6/lXObjUU5p6gDilCZGMcVKq85POetAmh0aj04qdAdv+NMjX8qnVB1H86aZI9UPQ8d6mWPJAamqKsEYIwKYmKpXG31qVUIFIFGzgVKgwoY+lAiZVwoPpzzTlXgdOtAHy8VKgzk9M0AJgqxzj6fpUgzjp+VMKrnA5Gf8A9dSFeRTJYYx14oK5PI+pp4QgZPTNLgH8/b60CK8kiQoXcgBRkk9BivlHxV8Rtd1TWpZvD9zLBap+7QLj5tvVzwevb2xXonxJ8TXesahH8PfDG57mdgtyy9ApGdmR7csew47mvSfDHhPT/DOjRaVGgkZOZHI+856nvj2HpWsbRV2Fz//R+CWHGBjngimLwxz09qtOhX7wqAD5hx7V5B3DwoDZPOKspjPTvVQhhyOfc1YQ/KCeo/X1piZqoc8rkVt2L7ZVbPtVPSdFvdUTz4dqorbWJPK8ZropNFlsmDId3AOTxQoO9xXRfDFiCKkVj3/SosEHawpwPGa6DMnU5GP88VMpIdSDwCKrLk8jmpgcYGR1oEzf+IyGTwRfoBn5Yz6/8tU/xryf4QFl1OWPjm1b9HWvY/HCed4I1FT3gDD8HU14x8H2Ka15Z720g/HcO1bL4TPqexaO1pHZ3S6gyCEgl1kxtK45J9gM5rvPCw0QeFr6XQkijgkeIsIl2gsCRyB3HQ55rktBRJFnjdFaMnDhjnPUdPeu+0i2tLLQLuCyjSOImPhRxnceQfXrUFMxH5ZM9Nwr1H4ej/TdRz/0Drnn0+T/ACK8vlI3J/vD+deofD9nim1MqOmnTA9ehKjtRDcUtjn+QQT/AIVe8Sczwrn7lnFwO2cH+tZ+9CePqK0PE2BqDIT0toRj/gKGtjnOYtMK0jDtGx9shTXFDLNmuyhIEczdMRt19641QeprGt0Oil1JQowPX/PanqP4fwpoJFSDhgRzisDYlVemB1qVF5zUaj86nX0/zzSAfGo6mp1TAJX6UICDgdzz9KmALDGOlMhiIMDPHSpgvHFCqRg4zUoBA+bn2poQAYAxUuwkcCnEZwBzxjFP25GKdxDu+RnipVHy8dTg03GDiplHHHpxQAq8fNjninLu5H4UnXB/SpACQDxx/OmA0Ak/hXmvxC8c/wDCNQDR9KBl1O6G2JFG4pu4DfUn7oxyfauk8ZeJrbwnocurXADvwscecb3PQfTueOgrzr4c+Dr26uf+E58TkyXtyxkhV/4Aej4Pf+6OgGPbFxWnMyHvZG/8OvA6eG7RtU1H95qN0N0rsSxXdyVB7kn7x7n2r0vH93p7VLtJOBSDaeWxzzzUt3HY/9L4VkX1PSqmM+n4Vclyef8APFU8HPNeQdxIwUcj8P8A9dKhJXB4PSm53DilXgc0wZ0ehajJp92DExKtww9a9UgurW9Y26nLKA59weeK8VtG2uHXt1Fem+GYXV5bqTIXGxc9+a6lFezuYN+9Y3J7SEt05z29+1VXtVaPC/eHp0/rV27u4bZQ0zY3dPf3rOOpWssbMjbsdQOp+gpcrtcG1sUlYEZ/MVLuIXLcc0mn2U+zdcDaxJOM9AelaQWCWFoMAHoeeRRYR1HiCP7T4NvsHk2buT1Pypu/pXhXwmcJ4iAYnBjkA/n/AEr36/w/g+7PXNhLz/2zNfO3wsJfxLbhOjGUEf8AAScVpHYl7nvGl20VzJd2lwrFHJU45GDkEc+3tXd+FdDstB8NajZ2jMUYxP8AMFzu38/dAznk5/8ArAcPp0Us1xe2yyNCXyAyDoTnn8O1ehaDBLbaFfQPI8o8uL5mIOMMB1xk565JJpIbMaVTuj7Hev8AOvT/AAMYlh1h5QDiwcDPqXQD/P8APv5hMwDx+m8H9a9J8FuV0/WmHU2JHPvNHShuKexzSqfOAHHP86v+JGCanOc5/dxr6/wL/hWWoPmrggc/56U7xfcLFqN4542lF9uFx7elbnOlqYQuykFwAeSmP/HhXOA81QOqeY/kAZ38Z/Gr8fPXn6/lXPUOmGiNHTbG41G+hsLYAvM6ouenJxk45wO9e32nwYeGIzavqCfLyY7ZC5OPdtvP/ATXB/DS38/xZDIcEQK0hz9No/nX05v569O9KEE1dinNrRHg+o+ENDgPkW63IZc/O5GefbAHHSufHhZ1OY3+X6c19JzTh1CPhlHYjiq1vDp9vcLcPaxSFTna4O38R0q3CJKmz551Tw1c6ZDDKckzZOMDgcYz9axGt5owC6kA8c9OPSvo7UdDt9UlDmYxknJyARz9MfhxVe68M20NrHHZSLc9TKGULtOOAASc/X9K54Rnb3y3JdD588sBcnnPpTwBxXrp8JafcEmWMQZJ+YEj8h0rKttN8DQxme5vN6q7JiRhH8yMUYdAeGBHFVyjuedYAJ9PwqfygfvEAV6Ouu/DSEgboGx1zvf+hrTt9U+Ht4xEL2qse2dn88VapsnmR5UYWUZdSvp2pDlRwD/kV7PP4N8P6iguLSR0J5D7vMXHtnOPoDXHar4K1fTQZoVFxEOd8fUfVev5ZocWgujjyAOOv1qWPBPI9zTCGxz3qhq+oR6TpNzqsg3LbxM//fIyP8KkZ4pqe34g/E9NLILabpZPmA/dLL94fi2Fx6An1r31VAIUenHFeQ/BrTJU0CfX7klp9QlLucfeCk8/ixbNewgDGOOtVN62FHuMJyMN7ikZS3OTUvUbvelwB1FSM//T+HZAG5UYxVJ1+Yg1fK+veq0iDdg9MV5B3FYEZyeRmmqQcj9KecKOelRtndj8eapCN/w5Z/2jqsVl0ViS30HJr127sLuHbb6Wh2nksegz27CvN/h66DxIsZPLRvjPb5c/yr2G7vjCzwpwpGMg+1dCk1ZGbimcNeaDq0r75ELd+W6e3Wq+k2LJfFnBDopBjI7H+IZNdC810CNzcU1JmFwry87futjpnqPpW0qzlGxiqaTuaWwqCAOahuLaKddrcH+8pwfbnrWitxbMOSOawrrV7WIFpCqKM8sQP51gWd6IvO8PywHPz20iH8VIr5o+Fp2+KbWNR1eQcf8AXNq+nPD1zBf6RFLGdySBlypyOpH9K+XPho3leLbTd1849/VSK2jsyD6N0xm/tK6i3BCzEDI5OCc4+ma7DwuurRaPqketMjOQpjMZyNvmL/srj6Hcfc9uN09pP7auxGVBZieR3zx6V2PhZtXOk6ousiMOIkK+V93HnAYyTknABJwBzipsNsoygl4+P4h1r0zwUFOma4w/58uPxnjxXmczZeP2YV6b4LH/ABKNcbJx9mQEfWeOiG4p7HOLBKJFZl7jpWF42bzLq/SMHd5/QfUiu3iTfKq46kUpYJqd+w73DfntWtWYxPnSK3ulvULowAHUg4rpFGGz269a9SvfLJJkVTnuQDzXOeKILQaLpmp2cQRkeawufLXauS3nwSO3Qu4eRB/sxDsKxnF7m0JdDv8A4SWoDXuoEdAsYJ9Dyf6Zr2RrgZyPpXlvw9DWPhzf/wA9pC/5YX+ldabuTJYHoeaqK0REtzoPNDvgHp6VMsgzz0Jrnobn0yQRkVee8jgiMrnjH9KbBIvS3MECM8zYHavN/EPxAtdNDR2h3ydh/j6Vx/i7xlM8r2tq3ze3br0ryxstlm5J6k9alK+rLtY6TVvGev6qCkkzRISfljO38yK460VmjdGH/LRuv+8T/XrVnkEAnkdfwqvpZka6lH92bHr/AAg/1q0rDjqmOi+dyhHIwPQc+lSSDY3zcZq5dlTdMUXAHarSXPnMZJlGCCCvb/OaozYaXrOraPOJdNneEgg4Byp+oOQa9z8JfFeO8kjstf2wS5wJR9wkcfMP4f5V89AbfX/61W7OAXE+CcZPX2pkn1pr3hG11yI3enFY7nGQc4WQ+/oT69+9fJHxjluNK8Iz6dcKUkuJUtyMkMDnc36Lg/WvoHwr8QtKguLXw0EdIlXy1lY5y55GfTPrnr7VT+OXw1n8badZaxpuTPp8yvNF2lhOFY47tGOfdd3cCspRs7mkXfQ858KWDaT4dsdPcDMcCBsf3iMn9TW8CCfp+VNjRVHyDAH+R9KXay89PU1i3d3LQoxk1JuZeBn8MUxVAY59O1SfMOF2/jj+tAH/1Pim3gkviBZq0mSB8oyPzGQK76w+E/jvWAslnpl0ysPlKwyMD/wILtA9819M+G/ilruq2BsPBdu2jxIFPmRWEUEGD1VNw3E9eQMe/TMGrReOdYBW81y+cNwVaVlT2+VSBXAqaW50cz6HzdffA/4laeonvLFYVI5LzRIQPcMwb9K841TQtR0uVoLxDlMBih3L65BGRgV9PN8O9TZtzyxHPGWZi38jVa78AavEhMJilIz8qscn25AFVyR6BzM+YbG5uNNvYbyDIaNgw7Z9vxHFfRq2Y1a0S/ted6ggd+f6+tcbPAkkbo0QLcg5APNa/grVbu1tFt7oAKD8vPb0NOUbRugUtbMla0wxVxjFVpYR26V6DcJYXI83adx64/nWBNp4H3azUimjmo4BjjA+tc9N4Z0xrh55VMhJ3bWJxz2/Ou1e2kjOVHsQaqyIc5x1qrkWOw8IwxRaVFbxKERHYBRx15x+tfLHgxjD4ytxnlbtV4wOM4r6s8OZFkOOkh/kK+VNMiEHxFkgU4MeohfoBLgD8q2hsZy3PpKyQprlzsUHvz+Fdh4Xl1iXT9WGrwRQlEURtHJuDp5kfzYIBHPGP/rZ4i1bHiCdVUHC568Dp3rs/DdxqU2n6l/aMKQuLddojcuCPOj6kqvNOwXKMv8ArIwOfmFem+Dyf7B12Vv+eMK4A9Z09PTFeWSOPMjLf3h+VeoeEpNvhvXWGMmOAd/+ew6cY/HilFakzehUhmEcyN7j/wCtWVbX5uLu9k3ZL3D/ANAKZeSFFQZxyK5zRLppI5pMjJmkPHruIrRmSN+9mJG30rLlEF/oWpaXcgE+St5BuOFWazPm7vc+T5qAdy1SXMjbc+tZ0N21leRXqqshidX2MMq205wR3B7j0qGuha7ntWjbbbRbWJfl/dLlTkckZP61Zkmwfoa+dbfX/EGgvPpS3LzfZpiImnO8tE2HjY5yeUIrrbDxxftH/p0Kt6shI/nmi66Fcp7DbysrYBzXIeMfEP2OH7NCfnbIX2qfRtettShlljV18oAncB36cj6V5JrV9/aF+9wTxkhfoKjd2LWiuZrEsS5OSTkn60LjG0d6jz6dKkBwPm4NaEMQgYyOvT8KzrBjFfXar1JRh7ZXGR7cVptkjH+eKzIsnVZgeMxIR+Bagumt15GxbJG7nzW2574z1qxLabVzDOkg9BkfzFQRAHAb6ZPpTZQBK0fquR7HPI/AjNUZFN/Njl8toyRzyO1aMMpjhAj4J6/1olj3xs8nG8Yx/n/PFU1Q2SRRA53DIycnPXB70CLAyrYz05yK+vfh14iPiHw/HNKc3Ft+6l7k+jH/AHh+tfIJUKdw6GvY/g5qf2fxBJpsnK3ERx/vJyP0zTaA7+fwvY2/iOSyuoz9nnHmQ7WwAD24PQHIANW5PAelS8xSyJj3DD9Rn9aj+KOtXOgSaTqEYj8j7QYp2ZSWxlHUKwYAHG7GQa7wBhgf5x/nrWfKrFXZ5hJ4AcEG3ugevDKRx+dZ8vgbWA3ySREfU/8AxNd7d6/Ba3c8LggQoGJyMknGAB3zW5bziaISMuMjpipcUHMz/9XX8+9cAKeSeR/Suj0/wd4t1lR9msbiRWBxIUKIPfc20Y/GvRv+E6TTf+QBZ2dj6PBCu/Huz7s/pXNat4l1XWY2TU55Z0bBKO5KcdMJnA/AVwm9yqvgOz0w7/EOp29qyEB4YCbmcH0KRg4z65rNvJ7O0gMfhaxeKRuPtd+VeUDHPlxrlV6DDEk+1Y1xEtoM2SMp5HyHHtz61RW5uQnzk5zwDyfp0H50xFa4ttMuwy6haKzKOWK5J45IxzXNzeE/Dt0RFCWt84GF/l82fy/CumnF3K+9WKqOcc8/oeKa6osgERUKcbgDjB/ofwoA5CXwPqkJC2N1HOvOFf5GA/UH9Kzn8LeJImy1uWHqpVs/rXr1rp8STpLLIu7sBjn8T1rfWBRxijlHzHzrcabqFuha4gkQd2KkD8+lc3OyBC2QRjmvrVLcEgEE54wOa+Uv2nrL/hEtZ02DS/3F9e28ktzApIMagqInZeiliX/75o5LjUzW8PzJ9mZQwwJM/mMf0r5VvLxbD4q3CEYX+1W+bpyJzXqvwi1LULizvV1KUuyyIV3HPUHp9MV494zb7H8T7ubZz9v8wAe7BvTv1rohG2hhJ3dz6cVc+JZmVRyueTjHT0rrfD0upG11OPUYljC2qlSj7wSZkyvQdABntzXOvZL9uN8rAlhjB/xrovDzahJDqYvYY1VbbKtHIXyPOQDIKLt7dz6UhGa+PMjx/eFeoeExjwprjKerWw+o8wn+leTzOfMiH+1Xp3hN0XwjrO7qZLXHuNz8U0Etjl9UuChVB6/jXK+GZv8ARSfWST3/AIzWxrcgMgBrnvCx3aarD+JnP5uf6VT2M0dVcSkrg9TxWLLJt9q0pcY/OsiVSTk9/wDPWoLRFc2i3lxBdADkGF/UlOVJ6/wkAH2PpXRx6WnlADIGOP8A9Vc7HKkUb7+q4dfXKnn/AMdJzXVW+ooYN2KmxRrSKdG8LMP4p2JJ59MCvPXt2uLYlSRjqf8APrXeeK5Cuk2kajhlDHnpkZrhId7HywSQeaUO5cuxU2NGnmFsg9Bnn0p3nKBg1DfXEW7y4RwOM+/rWO8rlec4qyTqLCC51G6SyskaWV+FRBknufy9ak1nw7qfhzxIlpqSBHmtfNG1gw27yOo4GDkH/wDVWT4W1/U9E1tLnS7VruZkaNY1zn5h1GAe36V714fsofFniqy0rxTYOlw0M0cILKylnTzNvABJDqFyDhc7umaznJqxrSS1b7Hntl4U1rUNHm1uygMlvAMuw64H3iF6kL/ER0HXvjFSLcwLc4Oa+lvHmvN4J8zw7oUMLxy28sBKBwoiliCb14UYO9lBz1XkcjPzdI2wbI+p6mtIu6OdoikO87QOFHFRyxl83HpjPsDRjAB/yc9qa7tFC8ijdjjA7nFWIFBmXy+mOT/PNdp8OJzH4ssZYwf9ZtI5BO5SP61xSl1dd643Rhj7HuPwrvvhvbvceMbNYxwrFm7gAKf8KaBnq/x8Uf8ACDLKCMrexkZ7ZjkHFek2knnWcUvJ3Ip591Bry39oK4MfguG1X7018mPU7Uk/xFeo2ixwW8Vvu5RQn/fIxUdBmDqHh2C7lecNtd3DlsDI2rgbT1HrUaeHpFUKbyXjpk5/zzXVMwXHGMUwuAe/40guf//WmtfFnhyc83BiPfcen510UN1bXEY+zXUcn4/4V8ieJb7x/wCIHLXV4hUn7kUSIB9CF3frWD8Jobe58VzWd9J5hWN8FmIO/I4Bz2ANc7o6XNObWx92QpOR2PToev8An3qlLaTI+G3jcehXcB7cdq85Wz1O3fdY3TjHQE7v51uWuv8Ajmzwsd2Dj1RDz27elZpFM6xbFpEKERs2cjqCB/n2rTtPDmp3Eb/ZLKaTcPmMWX+mAV9e9cxb+OfH0eVTUdnThYoj/Navy+K/GGqRiG91m6QHr5L+Qfzj2n9arlJbO90P4baxrMvkzWVyrKMs1xGI8AdQGYAZ/GtHV9Q+Fvhe3Z/EGuW0DrlBBbuLyYuvXcsGQoPYMR7mvFbzwXo3iR1l8R3d5fMo+U3F1M+36b2NQy/C3wpLt8i6vIcfdEcvA/DaaV0h8rZreIPjZeWqm0+FOkPazsQiXuo7HmwVILJCDsV8kbclhgcjPT5N8QeHPEV3rc134nMt1qFy2+WSSQSuxxxkhjjjAAPQYFfVUvw8jmASHWr+PPJAdMn6nbn86dYfCLQra4N5dXM95OSCGnIwCO+FAB/HNHOrDUGfMHhfTbjTpJ1ETruwTwe2f8a8W+IlleJ48ub4xkqTC2e2PLT+tfpNc+E7OytnvpJUVYlLsx6YUZJ/KvhDxl40u/FN8zNH5UCsRCF4O3sW9Tj/AOtWlOTZE42PZEvEYnaR710Wi3WyC/jyPmtcf+RYz/Svl638VanbBVkcvs4UknOPf1/Gut07x3dwsxX7rqUdQM5BI9j3ANaOJnc9TkfMsQ77u1eneGX/AOKU1YnIHm2w/HMnX8q+b4vFsUzCZc/I24cY6V6x4O8Wm78J6sqw42PBM3P8KsYx655koUWTJ6FLX3VJ8seMdqy/DEynSodpzlfy6mo7+ObV1aSLMewcnr+HuTUGk6V9jiCRlxgbRycflTkraMSOyds9D2zWZKBnjvUBW7HPmEgDoQP/ANdVJH1Dk5Q/gR+uazLRU1NjHaM54HH6nHatCzmxbgDpjrXBeML/AFGLS2t0VUkkI2FWyTgjsQK89svF3jLTsLcAToOgdcH8CuP61cY3FKVj668WgyaXYyR/dMaY/wC+a4a5k+yW+wH53647Cu/0XXbHxD8M7TxFd2uySONlaPdu2tGxUckDqBn8a4nSfD2s+JmkvYUxCmWluJCViQDrlsds9Bk1ila6ZtJ3s0cyAZCSv4V6V4X+F+p64y3WpH7DbMQA0g+eTPQIvHXse/YGvQNE8O+GfDGpy6VCy3GrWhR5JZgdvlkbm+zRj77hcbTnGDuDYzVTxB4svNP8d6lpOrN/o1nqDCJghZ0a2kdYmAEiAkKxHPB4JB5p6sWxHLrWh+E9HtB4RsiyagZoGuOPPLRsFyu4HOcghSMZJGB1rz74pa81hrmlPpl7Ol/aibT7vDMrB4AqeYMHjeDsIH9zPU1pa94ymv3ltdIt47a1FxNJC7IpmVZX34B5CHpygBGBzxXjmvQk39pNNk7psFm5PJGSfWhrQ6sF71blfZ/kz628JfFfw74m0IeEPHAeLzkjhMxPEjg5DkqBswwB54PfjIpdP+DU4gv59ZvFjFvFLJEyZKsI0Lhn4JA45AGf6/PGkPb2Os22oX9v59vDKrtFnG8A9ORz7joelfSEvxv0ue5NpHp8rWsyNFK7ld4WRSrYT5lOAeMtVNPocXqeDMuBux1561EjR/aDDNkAjPTnkcH+VX757N72Y6f5n2cSHyfNxv2ZO3dt43Y644zVUZZ1kbkoMD+Q/KqEW79UjmWNOQqfzr1b4L6YZddudQYZWGHaCT/ExH9Aa8hYs8p8w/Mf6f8A1q+rfhr4fk0Lwuss3yy3J8589gR8ufov9aLiOG+KgXWfHfhvwlGx2rIbuVeD8u7g/gI27Vv3VxqsF5JKUba9wX2oTu2I2xF54wxNc18PwfF3jjWPiA2DAr/ZLM88ooxkZOR8gUntljjFe1soznGT3/z9also4fVvEbR6al0ivHmTaWZTlQOpPUd6SyvfEN3aR3MCKVZRgsDk9j3HeuvuLaK5jMdyoZeuDyOOR+tZMkUtsRDZRbUA6LtAz+NK4H//1/nKLWJNXkk+xCaxjzhQ6NucH1ddwFc3D4WubO+a9tmWJ925PLkXKnsACQeh717defEn4faETC97ESoziFTJn8VG39awZ/j/AOALVysFldXLZ6lI0U/+PE/gcVHM9h8q3MNJvFttErPdysTyf3CsOenKuKh/4SfxjbtlJYnx1Dxuv8iareJf2hNJ1KyNrpujJA7ZAmco5UeygLg+hya8VPiZbycyG9uImbk/Mygf98nimrdR27Hu48d+LYAFKQtz2Zv6inj4la+nMlocf7Lg/wCFeRx3mttH5lrfNKDyeQ38waifWvEkQAWXPPUxoeP++apSh1RNme2p8X72Fg01lMCBzjB/HrWonxpiUDzoZUP+4T/KvM9BsPEuqwJdyz2axSdNy5fgkfdUD09a7pPDkRhCzyxs/cqu1fyyf50P2fVDvJdTqrX426Q5X53TkcMrf4V1ll8XtHY7ftA4Hc9q8buPDJU7ohHJ369PyBpIdOngjkWW0LlhgGNh369QOtS4UhqUz2rXPiZo2ueHL/SrW7jZ7i2kiTkfedCB+HNfCK6hIZTHIMFcg57EV6zd6ZCXYS2Eqn1Crj/x01yFzo0CzM0hCck/NHJx+SHFVGEFsyZSk9zn1mJHSpFm54A96vDTY2bYkkeT6sF/9CxWpa+Ery84imtlHcvcRKP1aqcfMkv+HDbXejarAqDzooo5lPPCiVVf8fmHWuy8C3N3brdIOIJ4wkrnsoOcD1JI4HtWXpXhyy0lXmh1OGc3K+TNFEk+fLyrHBaNFZsjK/NjIOcDBPUNYi8iW3gBgij/ANXGp6dst6sR1P5ADACTsS9TqPNYJshTEa8Dv+JP61ehm3Ljb71rafrJtfDA0E28JYgq05XMxBOeW+nHTpWXEgVahjRKyq3Qe/0rPvGFuhlk6D0rQIBpDCZ/3ITeW424zmoaKR55HpkurXP2u4BwOFFareGo9uWXP1rqLjRPEtp4hhWGJPsBi+cDGc4PrznOOnaugltiMZHbmjmsXyjPAsKjTrrw3Io2P+9jA45Iww/IA/nWt4d1grcSeCvGN0Y9ImRYi4T/AFPlsHSVVRSS3VScEkNzmsW3llsLuO8h+/EwI9PcH2PQ11viPRYNW09Ne0wZDZ3AdR6qfcVm3rdmiWljltY8SjVtPsIIbcQ3VgWBvAR5sqKFWEEqoK+WiY4JySTWHO9xeXEl7eSPLNMxd3kJZmZuSSTyST60iqq+3qPpUnzRqT7gY781ZkRrAHbGOe/4fSqV9p9reMkcq7jEwYHpz2rfKmC3Vv4pP0rO8p4n8uXrnt6dv/r0DjJxfNEaIwMHAzTlQf8A6qlAHXrR9KZIwIoqRQFXn8cUdeR3ro/DfhnUfE9+LOyBCA/vJMZVR3/H0FAGx8PvCsniHWUknT/RbchpD2JHIX8TyR6V6n8W/EdxBp0XgfQfn1HVgIVRMfLCTh2PXAYZXOOm49q2dU1bw/8ACvwrvP8ACCI4xw80h/Dqe5xwPwFc58PPDN/LezePvF4/4md+CY4z0giPRQDyDjgDOQOvOaLhY7/wv4etPDGgWuiWigiBMM395jyzd+p5ra46dsninnIOBzxULtjGenp71ACEg4DfnUJYpgYP5VBeXUdpEZJDgdu/PbAHU01L2NkDn+IZ7UAf/9D81ZCqAqD09e3rVVjgZIOO9aAFrJwr1KmnbxvRs985ArnRtcy9/GU4NRgMRtXnPHArsbTwsZF86dgkY6ncrdfoev41cPhy0sUDMTKQOB6D6DP8+aqxLkjE0ie5sSXjbYCct7Z4496970CDStaU2F1hLtVzk4Ak/wB3nr7d/wAwPmm8mdpTFGMDIOF7Vdsr/U7K6S8t5iJYz8rHnn8R2quUi59Dar4Xtog3levGK5Kewu7dtkEsidhhiPyqbTvimkqFdctCDwN8HI5P91jnj6/hW/cXmheILPFhdKrk7lI4cEcH5Tg/5FZzUrPl3NIuN1zHnV5qWp2m4C7nV1GQu9+e1JofjzXNEvPNmladZBsaOVmPBIJIOSQfQ9q19Ua/fw9/Ysqo80cpdZsjlccDpnPWuEbw5fm0XUfNjcM6xkI+SrsOAwOPTmsITU4OGIVr6HRKm4y5qOp7fq/xO0nUNOB0qW/sL5F24CQTQMccbmJRxn1AP0NYNh8QPE8sUlzOttcLGCzx7Dvx6jnBHrXIXHhjUNH0ganM0UsO9UYqejEEgc/jWnoD2kMEl+EbI3R7cDZswOWJ7g571jSdOlRvQk2r9Xf5HpZfgni8W6OIVtG77fPzO00Tx3Y6tcpaahBYw+ZNFGDKpHyu2GbdjaNnU7iOM9TxU+o63a6VqEljqOhIWjON8NwskbAhSCrxbkIww6MRz15r5+065Bu8TH5CxY5H617F4Zu7y8uHkuJmmiAjg2yNuYJtKqFDHcFVV6KMAAdOK73e10eJZXszqbbxb4YBH/Etuoz1+Qq38zXTWPi7wu74Md1H7uq/0zWungp06xjj2p7eEZVH3APpV3MrFyLWPDE0Yma6ZADjlDnnocYzWla6z4FYn7RqDgDoFjOT69RivPdY8H3YHmLnb+Vc2fDV2jDOfxqkKx7dFrXg9pT9lW4uB2DlVB+u3muq0rxPoONtpAkQJ28AsTntuPUV82R2V3abiu7gckZ4962NOtbyxs7aWFmiBkIDSHYm4fMBkgc/RuvvUSaRSjc+mX8U+GZ7l7C7njimhZo2VjtwynBGSAOvvU0+iWl/GJ7JlYN90rgg/Tsa8X0L/hH7lri/8S2l06Bsq1vIEG84OCzrJktnOMg9+nNdb4Tt7Vtdjl8Npew2qlzKLhw4K/wg7EQZ9+/XApbjtY1NQ8OXsSb1Tdz/AA81W0HXrnwzdtHdx+ZaS8SxdD/vLn+IfrXsZOflHPtVCfRbK9U/aIlYdB61LiUpHK654L0/W7X+3vCsqyo3JCjpgZKsOoPtivLZ7S5tW+z3UbRt6MMV7Pp/hjUtDvDe+GbprdiQWjkw0TgZ4YcZ+vUdiK6jzbTVIPI8VaWFfHM8AEkZIHXHDjPYAN9alXRTsz5sExDIsnO3jmlc+axc4yf84r6Al+Hvg7UX3afdeWzfwhgGGfRGGR+IpD8INOXO65l/DH9BT5iOU8AAOM8CnxwSTyCKBS7ngKoyT+Ar6Ah+GvhXTlabUpsquNxlcIo+p4q6niX4Y+G7YmymhmYfw2gErEjtuX5c/VhTuKx5x4c+Gmqam4m1bNtD1KY+c/XsP88V6frPifwx8NNOXTLdd90wAhsoTmWRjwCepAJ/iPXtk8V5x4g+MGqXim28OwiyTkea+HlI9QPur9OT6GvEL2Ge7ma8mkkMzNvMpY7y3ruPOapLuI+kfDXhLV9Z1keNfiAVe762tn/yzt1PQlc/e9ux5OT09F1SPUpLgXNo2VCkFQcEk+vrg44r47s/FnjnSTutdTmcZB2z4lBxjjLhiB9CK7Sw+NniezkP9rWEFwCQcws0bD1678/pQ4PoHMfRD6jqGnoFmiMoVMtIvTPfgegqSw8QRX2UdSsqqXK4OOOuDXl2mfHDwpdAR6mtxaMRz5ke5T7Axlj+Yrv9L8VeFdbffpt3bzSFeVDrv2n1UnI/GlysfMiTUb201a3KwZMifMoHBHocHrWYvh+WQeZcuu88ncpJ/PNaDaFYm6S5jcoVxhRx0Ax9OlU7vw9LcTtL57YJOOP060rDP//R/MVoZ4JMOjg+4rUtbrCrGyAlTnce/wBa+jriwtp1ImRXU9iAf51jyeFdEuDva3RSf7vH8q5vaXNXBnn8uo29zpSW8yrFglxt4OCAME98Y4z0rnbPW7nTpQpIuIG6ox5xn+H0Ir1QfDvT7qYR2jSbyMAEbv8AD+dQXfhXS/C0cmm6jZLezXCK8c5Zk8rk5AUHByMg556EEdDamiOU8r1qeyutQe5so/KQ8lep/wCBHABPrgCs4bRgk4H0ruf+EaidiQg9qgfwoYyQrHBP+SBVcwrM5JjxtHB/OpFG5twO0juDg/mOa9Lg+DvjK50SLxBZxJ9kuJGiR2nhViyjcRsZw445BIwe1cZ/wj+pRj5kyR6UlK4NDoNUv1OHfzB338//AF6kW8jeKTfHtbIYEHjI9sf1qobW/i+V4XGPbjH+fak+RTuZSozyMf40OMXuiozktmX3v5rixW0uXdYWkDMFJOSOMhc4yM17FoN18LYNPOmXMSSTP92a7e4AAPXCptAJ4+9xXhpkBc45A6fh2xUqkffz83b/ACamNGC0SK9vNPmT1PYotM8CNMbmzmtk29+MZP8AsyYP6V6P4C0O18Q6nNdyqlusc4u5fsYVIZiOVCxx4jUA8hVUAA/KFr5aSMEZU5PSpxujCxoSCat076Iz9pbdH6E6LrGj6xcvZ2xy8bFT0PI5KnBOD7V1DaVGRtXivzv0KDVdU1KOwsZ5Y3nbDuHK9jlmOeRXrHjT4feB/DHhRtat7+8kviyRxLuQK8h68BCQAoLfe7YzUQjKKtUdypyjJ3grI+mNS8PyMuUwRjNcLdaekZ5UA9+K6f4favcaf8PrB/F9yTdSoSDI2X2MxMe485IQgnPToeayta1fSYIHljkWY8/KhBP8yB+NWxHn+papNpFvfQadCk09xZyQ4bHyh8DeMnAK9R/kU3SNW0nUdd8P6TeWrW9rBbE306klppf4Tu9d3X5uhwMCqWLi61BTBK0i3Fu4aJBlXDggqzAMQfXkYqvp9nfXlpZ2sUcTFZWANuNo8sn5jISxJIwcZ554FZ8qbKcmWH0618W3zokRFvJKJQORwCdrEfxA9BnnH1r3LR1NjbLbRjCjpiqnh/QWtIhGAN2ATjHYYrphEIzgjH/1q20SsZ6sljv3TH0qyurSgkEish9pbK/Su/8AAnhAa9cG/vwTaRHGBxvb+7nqB3JqGOxFoun65rhLWMbbM4Mh+VB+J6/hXpun+CzCoa/naRjg4jG0fTJyT+ldykUUYFtCu1VACqowFX0AHYVYWPAwahjOcTw3ou3bNaxyL3EihwfwbirsGladaDy7W3iiX0jRVH6CtnZnjHJpCAeSMZoSBsoiFFBKqoJ9RVObTrSfiaGJx6FAen1rTc5XIGD/AJ5qHBJp2Fc5a68F+EbxcXGmWhJHJEKAn8QM1xl38GfAc6EQW0tsWO7dFK/H0Dl0x/wGvXs5GenakJBwTzgcUxXPnPVfgJp7ZfTb5l9p4wxJ/wB5NgH/AHya811b4MeLtPjYrCtwoXcWt3DjjttYI5P0U19q7V6n1/pSbCTkZH0p3A/Na+0G5tpmtbqPZKODG42v+KMA36VhXOjIvyMhU59MV+l2q6NpGt2ptdZt47qMHO2RQwz7Z6GvHPEPwP0e7QyeGrmSxcf8spcyxd+PmO5c+uT9KakFj5DsNZ8V6Iw/sjUbiJUGFRm3p/3w2V/Suqt/ix8QYIxFJ9lnI43vEdx+u1lH5Crfijwb4l8KNnXLPEO7Czxcxt2+8OmewYA1xLSWWcNuUjtVXJtY/9LkJ9BtJhho1JNY1x4Xtd/yKydvlOT+ua0IfENrJ8rrj/dJH8sVoi8t5hmKYgHGA2Mf0P618xCVWD1PoJRpyH2GjW2mRgRAlj1c9fzrh/HmkNdC3uYyPl3KR0JyR1/Wu5n1IRIGnIfAH3eBx0P1ridZ1f7YDGeR14r24zvFNHiSi1JpnnMel7eRyaXyAjYxk16NpfiDw5p2iTWt1pkVxfOQyXExZgozyoTdtwR3xuB744qjaN4R1bxI11qqnTNOklDGC3LO6pkZVGk3kfU7sehobYzk4km2+WHYLnO3OACfQVKtqmM4Fdd4kbwda6m1v4eFx5GBt+0SIz46ZJRQBz/sAjuM1Q0bQ9Z8RCV9Es550hG6QqhIjXOAzsPlUHsSQDS1AxFs4+gUY+ma6xrbwE/hyOzbS5H1DcWkuXlbHK8BEXCjB9QTz1xWZLZ3VlKba8jaOQclWGDz0/AinqgzmncLHHS+DtJlYmSJeevaqrfD/T5AVTcvpjivREjHpVtEH0FWpMhpHnC/BnW5bFdVtI7hreRiqS+UxjJUfMoYDBI788Vy178Ptfto/MhZZRycdMV9Ei/1CW1i09ppPJhZmRAxCgsAGOBwSQAM09VXG5h0FWpMmyPmTw9da7oWps9tbI8yAjbKDgdRkEMvP4118eleIPFF5Z/200QijclYiQC24gnPUAHGMluB0FdZrFu89w92wCLnCrwM4HfH60+28M3F1ALy6kZC/KjnaB2PWm33BI7S80y8WATXE8DkYG1JY2IHoEVsgD6VgPZbwznoOpPT6mss6BqVoPtNvl0T5iy/wgdz6D61ma54vu7g2unWkYaOLhmUY8xsnLsep64AGABzjJOZUW9ijora1hu50tbeEuysCGPAHHH5V7ToegxabEowDIxyzdK8a0DxW1jMqXMKbfUdf/r16tZeM9NlKqx5YAjBB/P0PtWiskQ02d+irGuF4yMZ/nWbcSBTjpj19TVe212wuUVkkHJwAfbrSXE0bfxAnr2qWy0is85DEccV9c+CLWG28JWCpgh4RIT15f5jn8TivjeVq+q/hHq8GqeEI7In97ZMYmGecHLKfpjj8Ki5Tjpc9GWIbuAQScVY25xnk5/D9alVCx4HPQ0oQDjrg+tBBGyALzVaVCoIXjNX3+U561Tzk4PU4poTKoQ4HvzUbKF61cyNo46f1ppXJBBpiKoXJ/X/AD9KTZjGOMj07e9XUVEZXwCO4yeR6cf4V4TceKvi9bassd5odu8O7B+yhirAEchzI+3P+0BQ3Yai3seykFOTwf8ACmtJg7R6mpiWmhDyKVPp3HfGR1qN1Y8jOT/OmIj8zcnIxj9KhYJkOpyaXgHOck00gL0oAqSxrIrJIAytkFTggg8YP9a8k1X4L+C9TvGu4kltN33o7d9iZzkkLtYD6DA9q9mKZXB7VXIRSQ3X2pAf/9PwFXZTgHv/AJNTR3bxc5J9qrhXxg9KZg5rzrI7Ls6SG11y9tWura2mlhBw0iIzICPVgMA/WuZmk3Nx9PSu3u/iB4ovdPstLmnYQ6e8jWygkBBJt3Lj+6NoIHbn1rh3G872Jz/OqtbYzlrqyqcZ56UpUEYx9fepj15rsfCXgu/8XTTJaTQWywRtI0ly5RflXcQAqsxOPRcDqcCqRJw6QRKxYDn+ldBpeqarYW81rZStHHOpWRFOAytjIP5VNqujvpNyIZZYp1YZDwsWX0IyQDn8KpKpUjFNMGi5vmlbdOxYgbQT2AqdFKnJ4qGFt5wK6G1tI5o9znDfrQA/RLO0u9RitdSuBaQuwEkpXdtU9SFyuSOwyPrWjrNlo9ndy2+l3RuhHM6eZ5ewOqnCuPnbg9QO1UjpkoX5Bu+lRrCUyG6j1qkS2SRxYI28npWlNbMqsH4SMbpG7Af/AK677wB4Om1eZdQuVIQNiMHjJH8R9h1r3l/h1o0ulvZMgKuTuyOWPv1rRLqZt9D4X1OY3hNvbgCEEkcckev865TTl8QaPMy6PcDYzbmikAZDngnnkfga+sfEHwViYs1i5jHZVO7p9cVw1x8K9QtXWUYztxg7h7delS7mqs0eLTax4mutOuNKnjgje4ZQ0sYZcxg7ig57kLz6DnOayRp+owLHAXjKpnBI6A+pAyeffivU7zwfrFtcKs0ThRkEjkDp0Nc7d6PdRJI+1j5TYBIwSM46U41GtBuC3TPOrgtp8uwqrAnAMZPf61oQuyEFeADkAdBWvLYLJOC6DkcHHPvVeWwdE3ryAcN9PWrckxKI6W5lYh4yQc54PQ16j4Turu600PcOZMMdpJyR7EmvKFieJwsnXHHvXs/hWFhpiB12MM5A/MGoewzoTEqxMrZzgbceuR1/DNb3grxjceEPEK3n3reX5Jl7Yzwfwqg8P7rdmuY1FSkbuATxgfjxWTZpBc2h+iWm39pqVnHfWbiSKQAqw9D/AJ5rQABHy8H/AD9a+H/hz8RLzwW0emXhaSzOAQf4f8BX2Po2t6frcC3NjKGDDsc9fp2/Q1UZXMpw5WbZVWGWH+c+tUvIyMj8/wD69WmdUGTk+gqPfuHI7/T3qiCoInDHdyOnBpm0E4b8avKQD+ePegqjfe/SncVjPOOxOaVlJBXoe/P86sGNW98VCUIyT2ppisViATs/z71ARzj86s5bqvHT26U04Ix/npTApGMA85/CovLG7C5q02S2AOfXFIQSSR1HFICq3I745/XiqjuM5BPIq5KyqpGPaq4dHG4UAf/U8HlWSF/LcYP9Ki69a2tW1q/1kRfb3L+UCFJJY884zWNjnNeedbEKg/SmFT3p5GDXTW/gvxXdabHq8VhOLaY7YpnXYkhBwfLLY39Oducd6aJZyhTnJ5qeJ5kBRGYLnOAe/rTzFJFK0MylGUlWVhggjqCPakU9BVIgcAxGWJPYZNTqM459qaMngDpUyLk5PSmBahUZXoOx9BXp17F4GtrGBNIuLqe88tvPZwiRiQE4CqATgjB+8evUdB5tGi/XFbltEAOlPoI3IXO37xFb/hzw2/iDUcSAiGI5kb1/2R7/AMqzdF0m71i8WxtBkn7zEZCjuff2r6p8IeGYNLtoxAAFT7nue7n+nvWkY3M5O2h0GiaHBplqINgUgben3R/d/qcd/pWnPPkcVamkWMeWOAOlYM7MTu6dqtkpEMrZ5bnnn0qoyrj5h/8ArqUngkjBHekODgmpLKM1layn5416emP5VkT+GNLuBjYBkYI+tdCUZup96jw2OOf8/SgDzaf4Z6J9+FE9emea5PVPhlYzZPlbT7fpivdjlTzzmmuqsdp79PxNAHydqHwymXiFmwpPXnGf/wBVdLp2jtYwpbyZJjGCx9h15r36fT43yoHXjFcjrOmTQxmSEEgDJI7fjSaKT7nGXFmy2aMwILcj6VxWoWZknjtx0J3sPZef54r6R1jwHLZ6Nb3bySFnjV8yEEHeoONueB6frXH2Xw+N5F/atxNtkYeUFVdwAznJOR1+lZSRvSkk7nis9nl8AdBXV+ENb1bw3d7oZWEXXZ2BPp1x79jW/N4O1CPXU0eRGO6Mz71Ut+6GRux16gjHrRd+EdYsrJL+8i8uORgqbmTLE+i5z+lQykz6A8PfEaxv0CXmFY9x0/LtXoont7uISQMGBHBHIr4p+w3VrIOGRxzgZFdbpHivXdKICOXX64P49jTjN9TOVNdD6vSMyQjPUcc0xULggdeOnSvMdE+I9pdKsd2Nr9PQ/kev516HZapY3CEwuM44Hf8AKtVJMycWi045JPUdR1oCB149OR0FDqrYdSPU0v3RuHTtTJDyYycgdaqvAO3H8qteauQPWoy4zxk4oAoNCRyR0qLZg/NirjkADPSqrnHLdqdxWInUHqO/+fxqiLZBnyiMHmrrMCCMZ5qLcfSi4WP/1fCOCMmkx2pdpB5pMZ4NeedQ3ao4NdZc+MNdvLGPTrp98VvJ50G4Z8tmAVtpPQEKPl6cdK5jAzkdacCegHTtVLQh2YSvJNK00x3OxyT6/lTVBzipQoI7fWpAp7dqaEOigeaVYIFLu7BVUDkk8AAetdzqvgDXNA8q31M28dxNH5yW4nRpCmN24bSVwR2DE+tcdAz28qTxHDKQyn0I5rZm1fUb4xm7kMjQx+Ujn7ypz8o5wByelUIoxR4Pz9cYrp7Fbi5nSys0LyOdqqPU/wCfoKw4lB6D6V9FeAPB0tiEurpB9rmHAY8Rr1/P19OnrVqNyXKyudb4L8KQ6db+SwyzYad16seyj/PHWvYwot49i8HjIH6AD2FVLC3js4ht/h+7nqc9z7mo7iYkVpsZLV3IriXccE+9ZjEk8cUryA9O9REg8nrUmg5fbtwKUcYHXjt70cfeGeP89abxzn6etAAcdjmotuB/nmpDuP60mNueg+vvQBFjnd2FLlcbqftwM0beMt+NADAO36mlOMbvwyaeV6H8aBx1xQAl4TqMRhu2LdAOea3PBMttoF0RdZlhI47nrxnPGfyrEGO/XqKd05X059qTQ0+h1/iPVbDXbqeGeMKkiCIkABtikkKWHPUk8etcRdeEdH1aazLzSKsJ+cA5ZkB4Az0PbPPXNSMuQQOKgIlXlDWbj1LUiuuhahNqqw6pbBdNjBeKCA7y7jgB2JVjkEkn8vSuX8VabHpUsX7h4ZGUySxkEeWhIVMjtk+vt613MOqXcDDJyB2PSr0mq217G9tqEKyCUAOGH3gCCAe+MgGs+UtSPM7DRpr2y/tCFCI8MVZuN20ZbaDgnA6kdKuWb3Nuu+3lKrzxnK/rmvVJ57LWLyG7lkCImEMexdoTGCFAA7Vxel6Fr2im8MISeJYnePbh2LthEAB+YYzuIHXFA7lmx8XanaAJMokXgcHBx+OQf0rrbTx7pEn7u+3REn+IEfy3VwmgWialpd19qjdbm1QZbOFJZwFXBGc4yT7CsyW3PO7rVpszaPd7bVtBvUCxXMYLdiwz/PNbJ03eA0MisCf72OPxr5ia1A5jyp9avaaWt7xWmJ2A5O3qKtENH0edEvWXCBTn/aUcdOKY3hzVCp+TJ9mX/GvOPFXiqK4jt7LRJJYo4EO5gSrMx9cHPHbnvXmGpa14ikUiPULtR6CZ/wDGqsTc+lU8JaoxLMUjHbLH9cZrJul8OWExtdQ1iwhlX7yPMgI/BjmvgvxhFqE0rNczSyMOcuxY+o6mrdjpJ1ixh1KEY81BuAJHzDhv1FaKmhXP/9bk9H8G6BdeF59e1XVBHdRMuLKNMuVboS5IG7qdoU8dweK47WbKysLwRWEpmjZVcbxhlz2ODjIrP3yYPzE5AB59OlMHznNcLt0OjXZht+WnqjE9KfEqg4OTV6OME8jpQSVkhxyasKgIG6vQvCPgyx8R2V5f6jqMdkltE0ixlS8khHtlVC9idxIOPlNYGq2NpYRwS2k3nLKG6rtxjA655z+FVa24LW9jAWMdO49KsqgA6/59KjHHGOa9C8EeED4huzeXgIsoCN56b27RqevuxHQehIqokyOk+HvhNiyeINRQFf8Al3jPJJz9/HoP4fU89hX0zo2mCKEzTYLHG4nsf7v+Pv8AhWJoenGdxKqhVXiNQMKoHGcdsdv/ANVdlM6xDyl4AGOBg1stDFu5RS+upJJI7mLywpwhBDBlI68dPTFUpp2LYH+NSzTHO2s7ORnNSWkSDBbdnGeMdv8A61OwO/SowcHilzzxQMnyo44oOCMGoc8Aj9KfnFAA3oKFyTn9abhT0/xpenAoAQYzjvxgfpUmSMk0z5ieOp5pwwVAoAQY/PpTeMYp/IGT6c008mgAH3844pQT0IppHPPX6UvTlj3oAc2V6Hr3p2A33uDUaAZ6ZqUH5QB+P9aVgIHt1PI4GTUBhdTgj/Gr/AOCe9JlXGAM/wCfelYaZm/MnSrEV5cW/MTEHHXNWDHHkbj9agaAj8KTiO5uxa8zRm2vBvR8bumTjOD+GawdXisBev8A2buMPGN3XOPm/DPT2qPy3HQcelRsDjI7/SlyhzGeY1J6U5F2glegq26f/rqN488VVhXMuQMxJ9aoTR5H1rbdBjBH86qSR44xkdKaJZ5z4l07zbbzccpxn61w+jeMLvwnDLpqQLKrymUFuo3ADHT2r2bU7Xz7V4164yM+1eQX2kpNcFyB+laxYrH/1/D8bjnrUig9etMAwevXpUigdDXCbkqdeauJuOBiqyg9RVxW44poRJulKiMOyqM8A44PUfT2piLgBRnHvmpAFByOtXbOzuNQu47GzUyTSsFVR3JqgNDw54evPEmqLp1p8o+9JJjIRM8sfzwB3PFfVGi6RBDBHpdgpW2gABA6se+cdWbqT/8AWrF8N+HoPD2nro1iVadvmuZhn5m+pGdq9B789TXqul2cdpGrEHOOAf5mtoqxjKVy8mLKIRjGeh/piqE8rEF/U1JcTbskEHFZE0+4EjNJsEgkkJOB/wDrqMOM7f1qISZX3NAO7p+tJFE+4Af56U/du5FQP8ylXxggg5NOBwcfpTAmHXHTinHGfc1EzA4x+P6d6fk4BNACkktntTt65I74FQhfWlzzsPvigCVSB27U7PQ+lQluPenk55XkfyoAkUkDLf5zR2CnjvUO48EU8ONvGMY/WgBcADIxTDz16UrNxnORSJz+NACh2zgU9Se3b8/aomABJGB9KUNjJPfFAD92fb6UoY5yvP1qLdgc8c0oOAcE8dqAJcgcHnHFP3E8cVWLN3J/H680ob0oAsAqRg1GEQDHWoi4J4NKz8D19frQK4YU9KjaPBxxSh2yQOtRl36E/wCfegVyJogwBP5dKgaEY2jtVx2YMRwR0pjEEZPrTsBQeBSpFeeanpZhvGQLkdRzjg16W7DBZcfjWZPDHK+5wCcd6a0A/9DxEA8Yq1FGZGCICxPQDP41AA3TrxXrmn/EyHwx4MvPB9hBGhuxG/nKB8zKefMJBLeiDICHkdxXElc2Z5gY3iYrKMY6gjFToMY+lX9Q1ufWYLcTpteJWBPrk9/pVKNCenNCv1G7dCYDb0719CeB/DR8PWa6heJ/xMLlfkXHzRRt0Hs7d+4GBxzXM/D7wogiXxVq65RG/wBGiPHmOP4z6qp6epHoOfbtKtZbu5M85Jdvm644Pf6mtoLqYzl0Rs6JpojTzZh7sffPQe1bc0x3YGcDj/P4U12SKJY0wFHYVmTTnscVTZKQk0zZ29hnpVIknk849OaieTnBz7imqWxkZ5qCyQckClPBJHWmbl3YHOelKpOORjqKaAs7sjHal3E8npVfcSB69KUyYPPXAPNMCcg54Hc//WpyEEYxUOSDz0HFO3IM46+tAFlT2JPHNA9zVcudx560b2GAp570ATkjPrij3NQK27tx3qbcMe2f5+9ADmJbAJ9qbvwABTSw60gIJ49O9ADsZODxTgR94c03tg9BRuI5/KgCTcffOf8APSonJPvjr9aQnoRjP1prNt6UAP3DHFHygE59etMBO6jcO3+f/r0CuKSWycdvWk3Hp+VMJbrjOKbn1/CmIk3FQD0pd46Z6f5xULMQMCmEjbjHakBPlvWozKwOFPXmonft68H0puQR2xTAcWwcj3pjS9h3pjsG/D/JqHd7+tAEkjY4xzVV3jVsc/r/AEp2QB8x4ph255I/GgD/0fGQrAZNToiZqAZ3cVbAHQVxmxIACOK73wN4UXxHfG4vcrYW2GnccFvSNfdv0HNc/wCHfD994l1OPStOHzNy7n7qIOrsewH+etfSUNtaWltD4c0fKWkH8RHLMR80j+pPb2q4oiUraGjEDqM6BVCQxgJHGvChV6Ko9AK722gW0gx3YZJ9qxdHs1hTz34xlVUjoPWtGedTkHp+taGSQ2abqCc+vvWXLMFGSfr9aWeUL0+X61m7skvz/L15qDQmLYJGcnpxTkc44NVt3fpTwxH6UAToW3Z7VKWBXr161VWT5cEVKfl78H/OaaAm54xz/n/OKeCOh5x6d6rDsMdRjmpgc9e+cZpgWNxIJxzSkg8HpUIfru7YxSq56A98/WgCTPNAOOKYTu5GaA5XA9DQA/dg/SnlgRt74qA/PkYPH+TxTg3X2HNAEh64z160Ljlfrj/P0qPIxg07zMErjGR1oAl3A59f/r//AKqQtx6+mfpUW75ewobHQf55/wAaBXJN2Pu5yKXrx2qBWO3aOlKH47YoETKw+96j/PSj3B4/wqMOD/n60Fl2YJ6A/h/jQAuQ3GcUMQDzTMk4xzimeYT1HJH9aAHsRnnI+tRO2eeMU0tnnFMLfLgfj3oAlLtj0qPIGcfiKjLjIx6U1nz0/wDr00A4gkkDH86ibIXaD39qaDgH3/Wmn0zmnYAOcEjt1qszkcAn8qczYH15qMsfp+Bp2A//0vHupxVy0t57y4SztUMksrBERRkkngAD1zVNAD05xX0Z4I8PR+DtLj8T6gMajeJm1U9YY2/5aH0Zh09Aa5ErmknY3dH0aPwZpP8AYVqRJfXWGvJFOeeqxL7L3Pck5rq9HsUGGcg9z7n/AA9KxdOspLi4zJne3PPYHn8zXZLtgjEacCtTLcttKqDYegH/ANaqE8+0ZH0qrLMiqSec9fyrOmn3DGeT296lspIledn4P40m7nj8Mf8A6qrZVRweo/z3pCSOO1Ay0GAPXj+lO471VDdvap43yf0oAlznp/n8qlQsw46j0qHvg9amUkAcjnvQBMMbs4HtR1HvTAcDI/H2pBjdjj6fjTQEitzxUgck5PSocHdk9vSpIwcbc+gpgSAjrz604HHP5VFnnAPIHFLyT8vegVyUHPU0cAYPfr7VGpAz2zkUrMS3Bz2/OgQ8N/doLbeMd6YpxnnntS7+T69BQBJg52+/ahj0U+oH/wBao94Ix1/GjJ4bPqevIoAXgDn09KBkeue//wBemMRzihjnjpx/OgA3ZHp3zSbxnj8aRmOSfemMB0z+BoAk3gDk9e1QySqG2jq1NZ8AnmqbSDzSR2woB7UAXSxIx25NN8w9VyAeuPeoNxYbRnA/wpVbjvx/SgCQk9VqM4B3U7du/wDrVDznJ5q4q4ErYDflTW6cH60gGFyfSoXPGAOtdHs1YVxGORk8VXfbn5+vv/8AqqRiB7896rtsJ5rFoZ//05fhv4Mt5Ld/GXiJB9it2xbxN/y3mByBg9UXv78eteiXEt1rd42o3rbmc4Qfw5HT6BT+Gahv9RTVXjtbNPs1laqI4Y0GAqfwjvlm7k1vaXb7P30uMgAKPQDoKwWgm7mpptoun2YhfJY5LHqQTyeeuM1LLMuSzY9s1DLKTkDAH5VRllwBzSbKSJJZd3eq247t1VzIDwTTWkycnr61IyYy7s46df61Ln/9dVFPI4we1TBh1FNASqwXnnn8KlTkD0qruxwPpUw4OKYFtGGcH2PFTLIo5weeAao7vTjmpFkOQD2x1oAuFwDgfT8aTPAz2qIP2alBGdwqgLBY5x6dKkAcLluv4frUCbs7m/zmpYzzj36j9fWgCUZ6L0Izz/TtTsjHPeow4AGe4wetL3AJFBJL8xwTx/T8fSmE/MQvA6ik3ADaP8/5NOJOCBxnuaAFDFTjt0pu4L15/wA+lBPG3HWk7gHp/ntQA7nbwM/0oB2jaBTByOODjtTm6cdBz/n8BQAgw33O9KzHPHf19qbu43evr3+lREgH2PagCUlcDbwefw9KY7NyQME8CmEgnA/z/OkxznpQAksqqvPGB29qorjZ83U+x696mm+ZCnfBFVd/lqZD0A5oAsA/Lk8n2qQHkk/rTEIK7vUUwkdR0IoAkJByT0pAS569PrUWecfhTCRVwdmBMSW4FRMxBxj+f400yBhzUTMe/St5TFYRmHfmq7ODg5QcfxU5s4x+FViJG5Xtxxn+lYNjP//U9F06yjLApnYp6n+I92+npXR5VE2r71Uj2xqsadunSoJJicEHnuPr/wDXrnBFhnKgk8479+f/ANdUpJSxBzzUTyknvURc9/fH+RUlE5kPf0oD+3OKqsx6Djj/AOvSBqALnIOalDYGMdRVVWIHTA61IvXAPX9KAJ1JPXmrKNnlqpK+f89alViq8n8KoC2ecCnrIAfWq24E8nOBn/OKkBUEZ4/CgC2GycdqlVgcen+eaqBgD27nP+RT0bJ5xx+vpTQFvcSxxUoxt7HHAqmr85btjtVgHGT0xTJJcnHofanhhnLflUWQBu/Knl/lP0547mgB+cnJ/wA+lBJUHj35qMOQdpP0/wAKTeMYFAEgkydpzg/0pA539PamgkNyOtNUg/MR06596AJicHOMEdu9BJ+6Op9Peo8926Y+v50Fiw2jj1JoAeWz97qT9OKjJzgvQzEYC+v6VGXwNoHXtQA7JOc9M0MwOAen/wBamgkHj8KjBUck57UABOR6YOOarFVB9Qf/ANVTs+/kDHp3qMfN+X1oAf0/z6U3p1/Wgt8oUDrxmmMwJJ7UABOOOg61C3Bz+IqQgYqM4JIFACE8cVExOMilIzk9B61XJXdTuA8tt4HFQF2BwuTQxy3NML89cf5+lAH/1fUnkDHIOPpVOSXGQBUcs+0YWqcku85B68VzNjSJzKcnJ696buPfkGqhdd3FODHp1/lU3LsWQ7MeKkByMdqrhsnOaeG7k9aYi0DgHJ5FShztwe/NVQ+BwR1qUPkgkAUIRYBP609W9TVYSKDkdKUtuPPeqAueZk47fnUvmZ5HU9apgt944qVWyCf6UAWwSQOv0qQMSOmeOAP8+tV1IOeee2afvDEkYznH0FAFpMEZPfAxVgNyD2zVVTyAeewqVTuxg/8A6qokslixAycY4Huacpz1Gf8AH271FyDtPXPfv6U4EAZoAlyPvE8jikOADg+/TgU3JJyRjpTCQeST36+tAEuRu/zmjgDk4I9ajJOdueo/Sm5O3nqRQBKWOfQZzSF93zCo15/LJx/KlDDOT1NAEgP+f5VHIecnB5607LY2jvULHGCT16UAKzEH5eB/9amuQQG/zikAB5b/AD7/AEqMkE4oAk3DHH1pC/POOOPxqM46HoKQnPyj17UASEqDgdKiL/LuPQcf4UxmI96YevOTQBITkYPpSFj1x2qLcc5PWkzng4oAGOfQd6hJznFPY88n1qJmUg96AG4GDnp9arMmW47e1Th8HOOtQsAxyw/rQJn/1uvll+XBz6dqrmQFjjvULOGYYIpFYDr1rjZaLG/FWFJY5zVAMSOOanVgDx6UFXLOcdO1SA5yT1Wqm8hs1MMDr2NUSyyJCoyKcJPx/SqqsR9etTbiABQIs53fd9etPU5JBquGzyeuMZHH8qlDA8dhVAWt4AIz1oDjP+cVASMYz+lHGMZPHegC8mcfWpt4Gcd6ph+cH1/z/OrCtkAt9f8A9dAFsOxPHXr+PvUyYGCvAPQD9apo3PXjpn61KH2sPQD+VUhMuBtw5xyP8ml3DOB0qsrhgKC2fr1/L0oEXN65yOp5/H600EbRj0/DAqAsR85OMcZpjMOR69vfigC0rf3efX8KTdyB6Hmq3J7/AI0ZAAzx/higC3kBckg55/pTcEHgdKhViD9entQrAHimBZDKRkHmmOcdOv41HuxkkfSo2c9R2HbFADido700kHnt/jTQ2T1/zimbgTwM9v8A9dAD8+mMDgelIzHp3qNjuHv2703cRz7UgHAjAJ6Y/wA96jJ7dfb1pCe5pjYwfXPagCUsBzjv0qIkjkdelNyMelNY7h/nmgAYkD6cZpuQT8tIzYHbFR5ANAmPbAA5HNQtuycf5/WguGGDx0pmV/iOPzoEf//X1ww/h7U8NnvVQDBweOBUwkUgc9+lcZRbwvbnvj1p3XHaqoPJP+fpUhIzhu9MCwrHrUm/BAGeP51V5B5PenBs/MP8mmBaVs8+1TKxI4HvVNSMYA69RUobbntQBcDE5x0/OpVPOPQYqkhK9uKkLAjH4VSAtlwRgVKCBxVLOOT0HHXP61IrDaB1JoAvK4yTnk9fx/yakyTjPA6+9VBnqf07U7cc/N0HFAF5GyMZPIycHtUysMZ4P+e9ZyuRnPGeuKl8wHgc+tAF4OFAFO8zHI+n4VRMmOvU84p2807klvzCR196QHnn8arA9RyacW3Djv8A0pgX84UAmmsdzBR0HSqisVGSc07eB16nr6UAWVbHHSlZjnAqoCCf504udvWmBZLc46+lQs2BtBzxTUYcY445ppfgkEg+tADy2P60u7C4/XvVYvk9fwpdwbBoAm3g5Y03IIqMsAATz7e9ML84oAnJAG7PHpUOeOabklTzioiQBk0gJSQ3QdeKp3V5FZIJJjhSevpU3mZ9+KjZRINrDI70AOLgqCDnPOfrTGbOAOtIxwcLTC3fp9M0CY4kdetM3beCeaTI6YzQD6UCP//Z</v>
       </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v/>
+      </c>
+      <c r="B42" t="str">
+        <v>wergwergwr</v>
+      </c>
+      <c r="C42">
+        <v>10.760209955969543</v>
+      </c>
+      <c r="D42">
+        <v>106.61351658980168</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42">
+        <v>7</v>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O42"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O44"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2356,10 +2356,95 @@
       <c r="L42" t="str">
         <v/>
       </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v/>
+      </c>
+      <c r="B43" t="str">
+        <v>T1</v>
+      </c>
+      <c r="C43">
+        <v>10.76059473694789</v>
+      </c>
+      <c r="D43">
+        <v>106.61356395288789</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43">
+        <v>7</v>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v/>
+      </c>
+      <c r="B44" t="str">
+        <v>T2</v>
+      </c>
+      <c r="C44">
+        <v>10.760969567023023</v>
+      </c>
+      <c r="D44">
+        <v>106.61358587853535</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44">
+        <v>7</v>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="L44" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O42"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O44"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O46"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,6 +436,9 @@
       <c r="L1" t="str">
         <v>Ảnh Base64</v>
       </c>
+      <c r="M1" t="str">
+        <v>Thời gian cập nhật</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -2495,10 +2498,60 @@
       <c r="L45" t="str">
         <v/>
       </c>
+      <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v/>
+      </c>
+      <c r="B46" t="str">
+        <v>My home</v>
+      </c>
+      <c r="C46">
+        <v>10.7852</v>
+      </c>
+      <c r="D46">
+        <v>106.6065</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46">
+        <v>7</v>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v>17:58:53 11/4/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O46"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O50"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2548,10 +2548,180 @@
       <c r="M46" t="str">
         <v>17:58:53 11/4/2026</v>
       </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v/>
+      </c>
+      <c r="B47" t="str">
+        <v>1</v>
+      </c>
+      <c r="C47">
+        <v>10.784576030449708</v>
+      </c>
+      <c r="D47">
+        <v>106.60733968019488</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47">
+        <v>7</v>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
+        <v/>
+      </c>
+      <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
+        <v>17:59:53 11/4/2026</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v/>
+      </c>
+      <c r="B48" t="str">
+        <v>2</v>
+      </c>
+      <c r="C48">
+        <v>10.784151821728125</v>
+      </c>
+      <c r="D48">
+        <v>106.60722702741626</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48">
+        <v>7</v>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
+        <v>17:59:56 11/4/2026</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v/>
+      </c>
+      <c r="B49" t="str">
+        <v>3</v>
+      </c>
+      <c r="C49">
+        <v>10.783827736401111</v>
+      </c>
+      <c r="D49">
+        <v>106.60704195499422</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49">
+        <v>7</v>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+      <c r="K49" t="str">
+        <v/>
+      </c>
+      <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
+        <v>18:00:00 11/4/2026</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v/>
+      </c>
+      <c r="B50" t="str">
+        <v>4</v>
+      </c>
+      <c r="C50">
+        <v>10.783522094634566</v>
+      </c>
+      <c r="D50">
+        <v>106.60688370466235</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50">
+        <v>7</v>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
+        <v/>
+      </c>
+      <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v>18:00:04 11/4/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O50"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O60"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2595,6 +2595,12 @@
       <c r="M47" t="str">
         <v>17:59:53 11/4/2026</v>
       </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -2636,6 +2642,12 @@
       <c r="M48" t="str">
         <v>17:59:56 11/4/2026</v>
       </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -2677,6 +2689,12 @@
       <c r="M49" t="str">
         <v>18:00:00 11/4/2026</v>
       </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -2718,10 +2736,426 @@
       <c r="M50" t="str">
         <v>18:00:04 11/4/2026</v>
       </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v/>
+      </c>
+      <c r="B51" t="str">
+        <v>htlt</v>
+      </c>
+      <c r="C51">
+        <v>10.898800703481468</v>
+      </c>
+      <c r="D51">
+        <v>106.70990467071535</v>
+      </c>
+      <c r="E51" t="str">
+        <v>trụ hạ thé</v>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51">
+        <v>7</v>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+      <c r="K51" t="str">
+        <v/>
+      </c>
+      <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v>18:07:30 11/4/2026</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v/>
+      </c>
+      <c r="B52" t="str">
+        <v>htlt 1</v>
+      </c>
+      <c r="C52">
+        <v>10.899385412973253</v>
+      </c>
+      <c r="D52">
+        <v>106.71037673950197</v>
+      </c>
+      <c r="E52" t="str">
+        <v>trụ hạ thé</v>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52">
+        <v>7</v>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
+        <v/>
+      </c>
+      <c r="L52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
+        <v>18:07:45 11/4/2026</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v/>
+      </c>
+      <c r="B53" t="str">
+        <v>htlt 2</v>
+      </c>
+      <c r="C53">
+        <v>10.900091276955056</v>
+      </c>
+      <c r="D53">
+        <v>106.71080589294434</v>
+      </c>
+      <c r="E53" t="str">
+        <v>trụ hạ thé</v>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53">
+        <v>7</v>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
+        <v/>
+      </c>
+      <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v>18:07:50 11/4/2026</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v/>
+      </c>
+      <c r="B54" t="str">
+        <v>htlt 3</v>
+      </c>
+      <c r="C54">
+        <v>10.900765533523117</v>
+      </c>
+      <c r="D54">
+        <v>106.71120822429658</v>
+      </c>
+      <c r="E54" t="str">
+        <v>trụ hạ thé</v>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54">
+        <v>7</v>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
+        <v/>
+      </c>
+      <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v>18:07:53 11/4/2026</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v/>
+      </c>
+      <c r="B55" t="str">
+        <v>htlt 4</v>
+      </c>
+      <c r="C55">
+        <v>10.901392380055551</v>
+      </c>
+      <c r="D55">
+        <v>106.71159982681276</v>
+      </c>
+      <c r="E55" t="str">
+        <v>trụ hạ thé</v>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55">
+        <v>7</v>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
+        <v/>
+      </c>
+      <c r="L55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
+        <v>18:07:58 11/4/2026</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v/>
+      </c>
+      <c r="B56" t="str">
+        <v>htlt 5</v>
+      </c>
+      <c r="C56">
+        <v>10.902085070275763</v>
+      </c>
+      <c r="D56">
+        <v>106.7119860649109</v>
+      </c>
+      <c r="E56" t="str">
+        <v>trụ hạ thé</v>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56">
+        <v>7</v>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
+        <v/>
+      </c>
+      <c r="L56" t="str">
+        <v/>
+      </c>
+      <c r="M56" t="str">
+        <v>18:08:01 11/4/2026</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v/>
+      </c>
+      <c r="B57" t="str">
+        <v>htlt 6</v>
+      </c>
+      <c r="C57">
+        <v>10.902817265789174</v>
+      </c>
+      <c r="D57">
+        <v>106.71225160360339</v>
+      </c>
+      <c r="E57" t="str">
+        <v>trụ hạ thé</v>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57">
+        <v>7</v>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
+        <v/>
+      </c>
+      <c r="L57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
+        <v>18:08:06 11/4/2026</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v/>
+      </c>
+      <c r="B58" t="str">
+        <v>htlt 7</v>
+      </c>
+      <c r="C58">
+        <v>10.903639008247684</v>
+      </c>
+      <c r="D58">
+        <v>106.7124366760254</v>
+      </c>
+      <c r="E58" t="str">
+        <v>trụ hạ thé</v>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58">
+        <v>7</v>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
+        <v/>
+      </c>
+      <c r="L58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
+        <v>18:08:10 11/4/2026</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v/>
+      </c>
+      <c r="B59" t="str">
+        <v>htlt 8</v>
+      </c>
+      <c r="C59">
+        <v>10.905053348124103</v>
+      </c>
+      <c r="D59">
+        <v>106.71253859996797</v>
+      </c>
+      <c r="E59" t="str">
+        <v>trụ hạ thé</v>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59">
+        <v>7</v>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
+        <v/>
+      </c>
+      <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v>18:08:15 11/4/2026</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v/>
+      </c>
+      <c r="B60" t="str">
+        <v>htlt 9</v>
+      </c>
+      <c r="C60">
+        <v>10.906723156004887</v>
+      </c>
+      <c r="D60">
+        <v>106.71262979507448</v>
+      </c>
+      <c r="E60" t="str">
+        <v>trụ hạ thé</v>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60">
+        <v>7</v>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
+        <v/>
+      </c>
+      <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v>18:09:22 11/4/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O60"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O67"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2783,6 +2783,12 @@
       <c r="M51" t="str">
         <v>18:07:30 11/4/2026</v>
       </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -2824,6 +2830,12 @@
       <c r="M52" t="str">
         <v>18:07:45 11/4/2026</v>
       </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -2865,6 +2877,12 @@
       <c r="M53" t="str">
         <v>18:07:50 11/4/2026</v>
       </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -2906,6 +2924,12 @@
       <c r="M54" t="str">
         <v>18:07:53 11/4/2026</v>
       </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -2947,6 +2971,12 @@
       <c r="M55" t="str">
         <v>18:07:58 11/4/2026</v>
       </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -2988,6 +3018,12 @@
       <c r="M56" t="str">
         <v>18:08:01 11/4/2026</v>
       </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -3029,6 +3065,12 @@
       <c r="M57" t="str">
         <v>18:08:06 11/4/2026</v>
       </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -3070,6 +3112,12 @@
       <c r="M58" t="str">
         <v>18:08:10 11/4/2026</v>
       </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -3111,6 +3159,12 @@
       <c r="M59" t="str">
         <v>18:08:15 11/4/2026</v>
       </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -3152,10 +3206,303 @@
       <c r="M60" t="str">
         <v>18:09:22 11/4/2026</v>
       </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v/>
+      </c>
+      <c r="B61" t="str">
+        <v>tru tên 1</v>
+      </c>
+      <c r="C61">
+        <v>10.83591930409522</v>
+      </c>
+      <c r="D61">
+        <v>106.60729408264162</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61">
+        <v>7</v>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
+        <v>18:30:03 11/4/2026</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v/>
+      </c>
+      <c r="B62" t="str">
+        <v>tru tên 2</v>
+      </c>
+      <c r="C62">
+        <v>10.83644881483479</v>
+      </c>
+      <c r="D62">
+        <v>106.60821139812471</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62">
+        <v>7</v>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+      <c r="K62" t="str">
+        <v/>
+      </c>
+      <c r="L62" t="str">
+        <v/>
+      </c>
+      <c r="M62" t="str">
+        <v>18:30:07 11/4/2026</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v/>
+      </c>
+      <c r="B63" t="str">
+        <v>tru tên 3</v>
+      </c>
+      <c r="C63">
+        <v>10.837117946469373</v>
+      </c>
+      <c r="D63">
+        <v>106.60888999700548</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63">
+        <v>7</v>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
+        <v/>
+      </c>
+      <c r="L63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
+        <v>18:30:16 11/4/2026</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v/>
+      </c>
+      <c r="B64" t="str">
+        <v>tru tên 4</v>
+      </c>
+      <c r="C64">
+        <v>10.836772843332824</v>
+      </c>
+      <c r="D64">
+        <v>106.60933792591096</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64">
+        <v>7</v>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
+      <c r="K64" t="str">
+        <v/>
+      </c>
+      <c r="L64" t="str">
+        <v/>
+      </c>
+      <c r="M64" t="str">
+        <v>18:30:29 11/4/2026</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v/>
+      </c>
+      <c r="B65" t="str">
+        <v>tru tên 5</v>
+      </c>
+      <c r="C65">
+        <v>10.836277580120997</v>
+      </c>
+      <c r="D65">
+        <v>106.60890877246858</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65">
+        <v>7</v>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+      <c r="K65" t="str">
+        <v/>
+      </c>
+      <c r="L65" t="str">
+        <v/>
+      </c>
+      <c r="M65" t="str">
+        <v>18:30:36 11/4/2026</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v/>
+      </c>
+      <c r="B66" t="str">
+        <v>tru tên 6</v>
+      </c>
+      <c r="C66">
+        <v>10.835840272561223</v>
+      </c>
+      <c r="D66">
+        <v>106.60845816135408</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66">
+        <v>7</v>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+      <c r="K66" t="str">
+        <v/>
+      </c>
+      <c r="L66" t="str">
+        <v/>
+      </c>
+      <c r="M66" t="str">
+        <v>18:30:40 11/4/2026</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v/>
+      </c>
+      <c r="B67" t="str">
+        <v>tru tên 7</v>
+      </c>
+      <c r="C67">
+        <v>10.835645328021462</v>
+      </c>
+      <c r="D67">
+        <v>106.60796463489534</v>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67">
+        <v>7</v>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+      <c r="K67" t="str">
+        <v/>
+      </c>
+      <c r="L67" t="str">
+        <v/>
+      </c>
+      <c r="M67" t="str">
+        <v>18:30:42 11/4/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O67"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:O71"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3253,6 +3253,12 @@
       <c r="M61" t="str">
         <v>18:30:03 11/4/2026</v>
       </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -3294,6 +3300,12 @@
       <c r="M62" t="str">
         <v>18:30:07 11/4/2026</v>
       </c>
+      <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -3335,6 +3347,12 @@
       <c r="M63" t="str">
         <v>18:30:16 11/4/2026</v>
       </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -3376,6 +3394,12 @@
       <c r="M64" t="str">
         <v>18:30:29 11/4/2026</v>
       </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -3417,6 +3441,12 @@
       <c r="M65" t="str">
         <v>18:30:36 11/4/2026</v>
       </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -3458,6 +3488,12 @@
       <c r="M66" t="str">
         <v>18:30:40 11/4/2026</v>
       </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -3499,10 +3535,180 @@
       <c r="M67" t="str">
         <v>18:30:42 11/4/2026</v>
       </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v/>
+      </c>
+      <c r="B68" t="str">
+        <v>fdsf1</v>
+      </c>
+      <c r="C68">
+        <v>10.946585056517058</v>
+      </c>
+      <c r="D68">
+        <v>106.44172668457033</v>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68">
+        <v>7</v>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+      <c r="K68" t="str">
+        <v/>
+      </c>
+      <c r="L68" t="str">
+        <v/>
+      </c>
+      <c r="M68" t="str">
+        <v>19:46:16 11/4/2026</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v/>
+      </c>
+      <c r="B69" t="str">
+        <v>fdsf2</v>
+      </c>
+      <c r="C69">
+        <v>10.94641125171887</v>
+      </c>
+      <c r="D69">
+        <v>106.44202440977098</v>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69">
+        <v>7</v>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+      <c r="K69" t="str">
+        <v/>
+      </c>
+      <c r="L69" t="str">
+        <v/>
+      </c>
+      <c r="M69" t="str">
+        <v>19:46:19 11/4/2026</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v/>
+      </c>
+      <c r="B70" t="str">
+        <v>fdsf3</v>
+      </c>
+      <c r="C70">
+        <v>10.945963572223603</v>
+      </c>
+      <c r="D70">
+        <v>106.44274592399599</v>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70">
+        <v>7</v>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
+      <c r="K70" t="str">
+        <v/>
+      </c>
+      <c r="L70" t="str">
+        <v/>
+      </c>
+      <c r="M70" t="str">
+        <v>19:46:21 11/4/2026</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v/>
+      </c>
+      <c r="B71" t="str">
+        <v>fdsf4</v>
+      </c>
+      <c r="C71">
+        <v>10.94512087957377</v>
+      </c>
+      <c r="D71">
+        <v>106.44431233406068</v>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71">
+        <v>7</v>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
+      <c r="J71" t="str">
+        <v/>
+      </c>
+      <c r="K71" t="str">
+        <v/>
+      </c>
+      <c r="L71" t="str">
+        <v/>
+      </c>
+      <c r="M71" t="str">
+        <v>19:46:25 11/4/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O67"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O71"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:O64"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2172,6 +2172,12 @@
       <c r="M38" t="str">
         <v>21:46:57 11/4/2026</v>
       </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -2213,6 +2219,12 @@
       <c r="M39" t="str">
         <v>21:47:11 11/4/2026</v>
       </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -2254,6 +2266,12 @@
       <c r="M40" t="str">
         <v>21:47:15 11/4/2026</v>
       </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -2295,6 +2313,12 @@
       <c r="M41" t="str">
         <v>21:47:19 11/4/2026</v>
       </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -2336,6 +2360,12 @@
       <c r="M42" t="str">
         <v>21:47:29 11/4/2026</v>
       </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -2377,6 +2407,12 @@
       <c r="M43" t="str">
         <v>21:47:33 11/4/2026</v>
       </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -2418,6 +2454,12 @@
       <c r="M44" t="str">
         <v>21:47:39 11/4/2026</v>
       </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -2459,6 +2501,12 @@
       <c r="M45" t="str">
         <v>21:47:46 11/4/2026</v>
       </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -2500,6 +2548,12 @@
       <c r="M46" t="str">
         <v>21:47:49 11/4/2026</v>
       </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -2541,6 +2595,12 @@
       <c r="M47" t="str">
         <v>21:47:54 11/4/2026</v>
       </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -2582,6 +2642,12 @@
       <c r="M48" t="str">
         <v>21:47:57 11/4/2026</v>
       </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -2623,6 +2689,12 @@
       <c r="M49" t="str">
         <v>21:47:59 11/4/2026</v>
       </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -2664,6 +2736,12 @@
       <c r="M50" t="str">
         <v>21:48:02 11/4/2026</v>
       </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -2705,6 +2783,12 @@
       <c r="M51" t="str">
         <v>21:48:05 11/4/2026</v>
       </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -2746,6 +2830,12 @@
       <c r="M52" t="str">
         <v>21:48:07 11/4/2026</v>
       </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -2787,6 +2877,12 @@
       <c r="M53" t="str">
         <v>21:48:10 11/4/2026</v>
       </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -2828,6 +2924,12 @@
       <c r="M54" t="str">
         <v>21:48:13 11/4/2026</v>
       </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -2869,10 +2971,385 @@
       <c r="M55" t="str">
         <v>21:48:16 11/4/2026</v>
       </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v/>
+      </c>
+      <c r="B56" t="str">
+        <v>N1kkkk</v>
+      </c>
+      <c r="C56">
+        <v>10.760201091099338</v>
+      </c>
+      <c r="D56">
+        <v>106.61322250877839</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56">
+        <v>7</v>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
+        <v/>
+      </c>
+      <c r="L56" t="str">
+        <v/>
+      </c>
+      <c r="M56" t="str">
+        <v>22:23:07 11/4/2026</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v/>
+      </c>
+      <c r="B57" t="str">
+        <v>N1kkkk</v>
+      </c>
+      <c r="C57">
+        <v>10.760201091099338</v>
+      </c>
+      <c r="D57">
+        <v>106.61322250877839</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57">
+        <v>7</v>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
+        <v/>
+      </c>
+      <c r="L57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
+        <v>22:25:29 11/4/2026</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v/>
+      </c>
+      <c r="B58" t="str">
+        <v>N1kkkk</v>
+      </c>
+      <c r="C58">
+        <v>10.759810179861683</v>
+      </c>
+      <c r="D58">
+        <v>106.61340951919557</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58">
+        <v>7</v>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
+        <v/>
+      </c>
+      <c r="L58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
+        <v>22:26:15 11/4/2026</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v/>
+      </c>
+      <c r="B59" t="str">
+        <v>N1kkkk1</v>
+      </c>
+      <c r="C59">
+        <v>10.760224470516196</v>
+      </c>
+      <c r="D59">
+        <v>106.61320956070797</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59">
+        <v>7</v>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
+        <v/>
+      </c>
+      <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v>22:45:41 11/4/2026</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v/>
+      </c>
+      <c r="B60" t="str">
+        <v>N1kkkk2</v>
+      </c>
+      <c r="C60">
+        <v>10.75975220730571</v>
+      </c>
+      <c r="D60">
+        <v>106.6138717532158</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60">
+        <v>7</v>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
+        <v/>
+      </c>
+      <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v>22:46:01 11/4/2026</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v/>
+      </c>
+      <c r="B61" t="str">
+        <v>N1kkkk3</v>
+      </c>
+      <c r="C61">
+        <v>10.759632304490403</v>
+      </c>
+      <c r="D61">
+        <v>106.61424281241086</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61">
+        <v>7</v>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
+        <v>22:46:10 11/4/2026</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v/>
+      </c>
+      <c r="B62" t="str">
+        <v>N1kkkk4</v>
+      </c>
+      <c r="C62">
+        <v>10.759553698691473</v>
+      </c>
+      <c r="D62">
+        <v>106.61492854356764</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62">
+        <v>7</v>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+      <c r="K62" t="str">
+        <v/>
+      </c>
+      <c r="L62" t="str">
+        <v/>
+      </c>
+      <c r="M62" t="str">
+        <v>22:46:41 11/4/2026</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v/>
+      </c>
+      <c r="B63" t="str">
+        <v>N1kkkk5</v>
+      </c>
+      <c r="C63">
+        <v>10.759489192626395</v>
+      </c>
+      <c r="D63">
+        <v>106.61525834203896</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63">
+        <v>7</v>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
+        <v/>
+      </c>
+      <c r="L63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
+        <v>22:46:54 11/4/2026</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v/>
+      </c>
+      <c r="B64" t="str">
+        <v>N1kkkk6</v>
+      </c>
+      <c r="C64">
+        <v>10.760250235235263</v>
+      </c>
+      <c r="D64">
+        <v>106.61560893058778</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64">
+        <v>7</v>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
+      <c r="K64" t="str">
+        <v/>
+      </c>
+      <c r="L64" t="str">
+        <v/>
+      </c>
+      <c r="M64" t="str">
+        <v>22:47:37 11/4/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O64"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:O68"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3018,6 +3018,12 @@
       <c r="M56" t="str">
         <v>22:23:07 11/4/2026</v>
       </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -3059,6 +3065,12 @@
       <c r="M57" t="str">
         <v>22:25:29 11/4/2026</v>
       </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -3100,6 +3112,12 @@
       <c r="M58" t="str">
         <v>22:26:15 11/4/2026</v>
       </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -3141,6 +3159,12 @@
       <c r="M59" t="str">
         <v>22:45:41 11/4/2026</v>
       </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -3182,6 +3206,12 @@
       <c r="M60" t="str">
         <v>22:46:01 11/4/2026</v>
       </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -3223,6 +3253,12 @@
       <c r="M61" t="str">
         <v>22:46:10 11/4/2026</v>
       </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -3264,6 +3300,12 @@
       <c r="M62" t="str">
         <v>22:46:41 11/4/2026</v>
       </c>
+      <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -3305,6 +3347,12 @@
       <c r="M63" t="str">
         <v>22:46:54 11/4/2026</v>
       </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -3346,10 +3394,180 @@
       <c r="M64" t="str">
         <v>22:47:37 11/4/2026</v>
       </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v/>
+      </c>
+      <c r="B65" t="str">
+        <v>n1</v>
+      </c>
+      <c r="C65">
+        <v>10.7852</v>
+      </c>
+      <c r="D65">
+        <v>106.6065</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65">
+        <v>7</v>
+      </c>
+      <c r="H65" t="str">
+        <v>Nguyen Van Qua</v>
+      </c>
+      <c r="I65" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+      <c r="K65" t="str">
+        <v/>
+      </c>
+      <c r="L65" t="str">
+        <v/>
+      </c>
+      <c r="M65" t="str">
+        <v>23:01:31 11/4/2026</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v/>
+      </c>
+      <c r="B66" t="str">
+        <v>n2</v>
+      </c>
+      <c r="C66">
+        <v>10.785311148494626</v>
+      </c>
+      <c r="D66">
+        <v>106.60728871822359</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66">
+        <v>7</v>
+      </c>
+      <c r="H66" t="str">
+        <v>Nguyen Van Qua</v>
+      </c>
+      <c r="I66" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+      <c r="K66" t="str">
+        <v/>
+      </c>
+      <c r="L66" t="str">
+        <v/>
+      </c>
+      <c r="M66" t="str">
+        <v>23:01:50 11/4/2026</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v/>
+      </c>
+      <c r="B67" t="str">
+        <v>n3</v>
+      </c>
+      <c r="C67">
+        <v>10.785110901463296</v>
+      </c>
+      <c r="D67">
+        <v>106.60791367292407</v>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67">
+        <v>7</v>
+      </c>
+      <c r="H67" t="str">
+        <v>Nguyen Van Qua</v>
+      </c>
+      <c r="I67" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+      <c r="K67" t="str">
+        <v/>
+      </c>
+      <c r="L67" t="str">
+        <v/>
+      </c>
+      <c r="M67" t="str">
+        <v>23:01:55 11/4/2026</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v/>
+      </c>
+      <c r="B68" t="str">
+        <v>n4</v>
+      </c>
+      <c r="C68">
+        <v>10.785709007332331</v>
+      </c>
+      <c r="D68">
+        <v>106.60853058099748</v>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68">
+        <v>7</v>
+      </c>
+      <c r="H68" t="str">
+        <v>Nguyen Van Qua</v>
+      </c>
+      <c r="I68" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+      <c r="K68" t="str">
+        <v/>
+      </c>
+      <c r="L68" t="str">
+        <v/>
+      </c>
+      <c r="M68" t="str">
+        <v>23:02:04 11/4/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O64"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O68"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O40"/>
   <cols>
     <col min="12" max="12" width="23.33203125" customWidth="1"/>
   </cols>
@@ -2135,7 +2135,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="120" customHeight="1">
+    <row r="38">
       <c r="A38" t="str">
         <v/>
       </c>
@@ -2175,6 +2175,12 @@
       <c r="M38" t="str">
         <v>11:27:46 12/4/2026</v>
       </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -2216,10 +2222,57 @@
       <c r="M39" t="str">
         <v>11:27:57 12/4/2026</v>
       </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="120" customHeight="1">
+      <c r="A40" t="str">
+        <v/>
+      </c>
+      <c r="B40" t="str">
+        <v>Al66-ts1</v>
+      </c>
+      <c r="C40">
+        <v>11.1628938</v>
+      </c>
+      <c r="D40">
+        <v>106.5352937</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v>Btlt</v>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v>Led</v>
+      </c>
+      <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
+        <v>12:52:02 12/4/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O40"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O41"/>
   <cols>
     <col min="12" max="12" width="23.33203125" customWidth="1"/>
   </cols>
@@ -2229,7 +2229,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="120" customHeight="1">
+    <row r="40">
       <c r="A40" t="str">
         <v/>
       </c>
@@ -2269,10 +2269,57 @@
       <c r="M40" t="str">
         <v>12:52:02 12/4/2026</v>
       </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="120" customHeight="1">
+      <c r="A41" t="str">
+        <v/>
+      </c>
+      <c r="B41" t="str">
+        <v>Ăn Tây 012_1</v>
+      </c>
+      <c r="C41">
+        <v>11.1317923</v>
+      </c>
+      <c r="D41">
+        <v>106.5176791</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v>BTLT</v>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v>Led</v>
+      </c>
+      <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
+        <v>14:35:31 12/4/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O40"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O41"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O42"/>
   <cols>
     <col min="12" max="12" width="23.33203125" customWidth="1"/>
   </cols>
@@ -2276,7 +2276,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" ht="120" customHeight="1">
+    <row r="41">
       <c r="A41" t="str">
         <v/>
       </c>
@@ -2316,10 +2316,57 @@
       <c r="M41" t="str">
         <v>14:35:31 12/4/2026</v>
       </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="120" customHeight="1">
+      <c r="A42" t="str">
+        <v/>
+      </c>
+      <c r="B42" t="str">
+        <v>An Tây 035_1</v>
+      </c>
+      <c r="C42">
+        <v>11.1045665</v>
+      </c>
+      <c r="D42">
+        <v>106.5354116</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v>BTLT</v>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v>Led</v>
+      </c>
+      <c r="L42" t="str">
+        <v/>
+      </c>
+      <c r="M42" t="str">
+        <v>15:12:08 12/4/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O42"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,10 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O42"/>
-  <cols>
-    <col min="12" max="12" width="23.33203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:O45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2323,7 +2320,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="120" customHeight="1">
+    <row r="42">
       <c r="A42" t="str">
         <v/>
       </c>
@@ -2363,10 +2360,139 @@
       <c r="M42" t="str">
         <v>15:12:08 12/4/2026</v>
       </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v/>
+      </c>
+      <c r="B43" t="str">
+        <v>t1</v>
+      </c>
+      <c r="C43">
+        <v>11.066559678448693</v>
+      </c>
+      <c r="D43">
+        <v>106.59673690795898</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
+        <v>images/t1-2026-04-12T13-09-52-590Z.png</v>
+      </c>
+      <c r="M43" t="str">
+        <v>20:09:22 12/4/2026</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v/>
+      </c>
+      <c r="B44" t="str">
+        <v>t2</v>
+      </c>
+      <c r="C44">
+        <v>11.063369273522982</v>
+      </c>
+      <c r="D44">
+        <v>106.59765958786012</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="L44" t="str">
+        <v>images/t2-2026-04-12T13-09-52-590Z.png</v>
+      </c>
+      <c r="M44" t="str">
+        <v>20:09:37 12/4/2026</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v/>
+      </c>
+      <c r="B45" t="str">
+        <v>t3</v>
+      </c>
+      <c r="C45">
+        <v>11.062253150066383</v>
+      </c>
+      <c r="D45">
+        <v>106.5972948074341</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
+        <v>images/t3-2026-04-12T13-09-52-590Z.png</v>
+      </c>
+      <c r="M45" t="str">
+        <v>20:09:49 12/4/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O42"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O45"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O47"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2407,6 +2407,12 @@
       <c r="M43" t="str">
         <v>20:09:22 12/4/2026</v>
       </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -2448,6 +2454,12 @@
       <c r="M44" t="str">
         <v>20:09:37 12/4/2026</v>
       </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -2489,10 +2501,98 @@
       <c r="M45" t="str">
         <v>20:09:49 12/4/2026</v>
       </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v/>
+      </c>
+      <c r="B46" t="str">
+        <v>tt1</v>
+      </c>
+      <c r="C46">
+        <v>11.105641948035744</v>
+      </c>
+      <c r="D46">
+        <v>106.55982971191408</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
+        <v>images/tt1-2026-04-12T13-19-30-916Z.png</v>
+      </c>
+      <c r="M46" t="str">
+        <v>20:19:16 12/4/2026</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v/>
+      </c>
+      <c r="B47" t="str">
+        <v>tt2</v>
+      </c>
+      <c r="C47">
+        <v>11.104704961235997</v>
+      </c>
+      <c r="D47">
+        <v>106.55982434749605</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
+        <v/>
+      </c>
+      <c r="L47" t="str">
+        <v>images/tt2-2026-04-12T13-19-30-916Z.png</v>
+      </c>
+      <c r="M47" t="str">
+        <v>20:19:24 12/4/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O47"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:O49"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2548,6 +2548,12 @@
       <c r="M46" t="str">
         <v>20:19:16 12/4/2026</v>
       </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -2589,10 +2595,98 @@
       <c r="M47" t="str">
         <v>20:19:24 12/4/2026</v>
       </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v/>
+      </c>
+      <c r="B48" t="str">
+        <v>tttt1</v>
+      </c>
+      <c r="C48">
+        <v>11.10597884143085</v>
+      </c>
+      <c r="D48">
+        <v>106.57253265380861</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="L48" t="str">
+        <v>images/tttt1-2026-04-12T13-26-31-857Z.png</v>
+      </c>
+      <c r="M48" t="str">
+        <v>20:25:47 12/4/2026</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v/>
+      </c>
+      <c r="B49" t="str">
+        <v>tttt2</v>
+      </c>
+      <c r="C49">
+        <v>11.104489138007638</v>
+      </c>
+      <c r="D49">
+        <v>106.57251656055452</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+      <c r="K49" t="str">
+        <v/>
+      </c>
+      <c r="L49" t="str">
+        <v>images/tttt2-2026-04-12T13-26-34-364Z.png</v>
+      </c>
+      <c r="M49" t="str">
+        <v>20:26:03 12/4/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O47"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O49"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O52"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2407,6 +2407,12 @@
       <c r="M43" t="str">
         <v>22:15:39 12/4/2026</v>
       </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -2448,6 +2454,12 @@
       <c r="M44" t="str">
         <v>22:15:46 12/4/2026</v>
       </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -2489,6 +2501,12 @@
       <c r="M45" t="str">
         <v>22:15:49 12/4/2026</v>
       </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -2530,6 +2548,12 @@
       <c r="M46" t="str">
         <v>22:15:53 12/4/2026</v>
       </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -2571,6 +2595,12 @@
       <c r="M47" t="str">
         <v>22:15:55 12/4/2026</v>
       </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -2612,6 +2642,12 @@
       <c r="M48" t="str">
         <v>22:15:57 12/4/2026</v>
       </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -2653,10 +2689,139 @@
       <c r="M49" t="str">
         <v>22:17:02 12/4/2026</v>
       </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v/>
+      </c>
+      <c r="B50" t="str">
+        <v>H1</v>
+      </c>
+      <c r="C50">
+        <v>11.014961254298361</v>
+      </c>
+      <c r="D50">
+        <v>106.67115211486818</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
+        <v/>
+      </c>
+      <c r="L50" t="str">
+        <v>images/h1-2026-04-12T15-34-35-445Z.jpeg</v>
+      </c>
+      <c r="M50" t="str">
+        <v>22:33:02 12/4/2026</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v/>
+      </c>
+      <c r="B51" t="str">
+        <v>H2</v>
+      </c>
+      <c r="C51">
+        <v>11.014081910108642</v>
+      </c>
+      <c r="D51">
+        <v>106.67146374800707</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+      <c r="K51" t="str">
+        <v/>
+      </c>
+      <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v>22:33:08 12/4/2026</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v/>
+      </c>
+      <c r="B52" t="str">
+        <v>H3</v>
+      </c>
+      <c r="C52">
+        <v>11.013511762779267</v>
+      </c>
+      <c r="D52">
+        <v>106.67158434093564</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
+        <v/>
+      </c>
+      <c r="L52" t="str">
+        <v>images/h3-2026-04-12T15-34-37-427Z.jpeg</v>
+      </c>
+      <c r="M52" t="str">
+        <v>22:33:37 12/4/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O49"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O52"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O54"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2736,6 +2736,12 @@
       <c r="M50" t="str">
         <v>22:33:02 12/4/2026</v>
       </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -2777,6 +2783,12 @@
       <c r="M51" t="str">
         <v>22:33:08 12/4/2026</v>
       </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -2818,10 +2830,98 @@
       <c r="M52" t="str">
         <v>22:33:37 12/4/2026</v>
       </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v/>
+      </c>
+      <c r="B53" t="str">
+        <v>Tktq1</v>
+      </c>
+      <c r="C53">
+        <v>10.787959044201465</v>
+      </c>
+      <c r="D53">
+        <v>106.59861445426942</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
+        <v/>
+      </c>
+      <c r="L53" t="str">
+        <v>images/tktq1-2026-04-12T15-40-11-455Z.jpeg</v>
+      </c>
+      <c r="M53" t="str">
+        <v>22:39:10 12/4/2026</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v/>
+      </c>
+      <c r="B54" t="str">
+        <v>Tktq2</v>
+      </c>
+      <c r="C54">
+        <v>10.788396682645603</v>
+      </c>
+      <c r="D54">
+        <v>106.59960749356645</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
+        <v/>
+      </c>
+      <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v>22:39:31 12/4/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O54"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O54"/>
+  <dimension ref="A1:O55"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2877,6 +2877,12 @@
       <c r="M53" t="str">
         <v>22:39:10 12/4/2026</v>
       </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -2918,10 +2924,57 @@
       <c r="M54" t="str">
         <v>22:39:31 12/4/2026</v>
       </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v/>
+      </c>
+      <c r="B55" t="str">
+        <v>An Tây 071_2</v>
+      </c>
+      <c r="C55">
+        <v>11.0740215</v>
+      </c>
+      <c r="D55">
+        <v>106.5577071</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v>BTLT</v>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
+        <v>Led</v>
+      </c>
+      <c r="L55" t="str">
+        <v>images/an-ty-071_2-2026-04-13T01-48-36-691Z.jpeg</v>
+      </c>
+      <c r="M55" t="str">
+        <v>08:48:27 13/4/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O54"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O55"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:O61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2971,10 +2971,262 @@
       <c r="M55" t="str">
         <v>08:48:27 13/4/2026</v>
       </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v/>
+      </c>
+      <c r="B56" t="str">
+        <v>Lvc 1</v>
+      </c>
+      <c r="C56">
+        <v>10.733780035770264</v>
+      </c>
+      <c r="D56">
+        <v>106.64080014956933</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56">
+        <v>2</v>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v>Stk</v>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
+        <v/>
+      </c>
+      <c r="L56" t="str">
+        <v>images/lvc-1-2026-04-13T01-58-04-926Z.jpeg</v>
+      </c>
+      <c r="M56" t="str">
+        <v>08:54:23 13/4/2026</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v/>
+      </c>
+      <c r="B57" t="str">
+        <v>Lvc 2</v>
+      </c>
+      <c r="C57">
+        <v>10.733729965468195</v>
+      </c>
+      <c r="D57">
+        <v>106.64059366537933</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57">
+        <v>2</v>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v>Stk</v>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
+        <v/>
+      </c>
+      <c r="L57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
+        <v>08:54:29 13/4/2026</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v/>
+      </c>
+      <c r="B58" t="str">
+        <v>Lvc 3</v>
+      </c>
+      <c r="C58">
+        <v>10.734056739921558</v>
+      </c>
+      <c r="D58">
+        <v>106.64039246682592</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58">
+        <v>2</v>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v>Stk</v>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
+        <v/>
+      </c>
+      <c r="L58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
+        <v>08:54:36 13/4/2026</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v/>
+      </c>
+      <c r="B59" t="str">
+        <v>Lvc 4</v>
+      </c>
+      <c r="C59">
+        <v>10.734355518903069</v>
+      </c>
+      <c r="D59">
+        <v>106.6402164304159</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59">
+        <v>2</v>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v>Stk</v>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
+        <v/>
+      </c>
+      <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v>08:54:52 13/4/2026</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v/>
+      </c>
+      <c r="B60" t="str">
+        <v>Lvc1 1</v>
+      </c>
+      <c r="C60">
+        <v>10.734773534259206</v>
+      </c>
+      <c r="D60">
+        <v>106.6399552574516</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60">
+        <v>2</v>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v>Stk</v>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
+        <v/>
+      </c>
+      <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v>08:55:19 13/4/2026</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v/>
+      </c>
+      <c r="B61" t="str">
+        <v>Lvc1 2</v>
+      </c>
+      <c r="C61">
+        <v>10.735026520090136</v>
+      </c>
+      <c r="D61">
+        <v>106.63981040265661</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61">
+        <v>6</v>
+      </c>
+      <c r="H61" t="str">
+        <v>Luong van can</v>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61" t="str">
+        <v>images/lvc1-2-2026-04-13T01-58-06-769Z.jpeg</v>
+      </c>
+      <c r="M61" t="str">
+        <v>08:55:52 13/4/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O61"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O64"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3018,6 +3018,12 @@
       <c r="M56" t="str">
         <v>08:54:23 13/4/2026</v>
       </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -3059,6 +3065,12 @@
       <c r="M57" t="str">
         <v>08:54:29 13/4/2026</v>
       </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -3100,6 +3112,12 @@
       <c r="M58" t="str">
         <v>08:54:36 13/4/2026</v>
       </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -3141,6 +3159,12 @@
       <c r="M59" t="str">
         <v>08:54:52 13/4/2026</v>
       </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -3182,6 +3206,12 @@
       <c r="M60" t="str">
         <v>08:55:19 13/4/2026</v>
       </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -3223,10 +3253,139 @@
       <c r="M61" t="str">
         <v>08:55:52 13/4/2026</v>
       </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v/>
+      </c>
+      <c r="B62" t="str">
+        <v>Vvk1</v>
+      </c>
+      <c r="C62">
+        <v>10.738713445297229</v>
+      </c>
+      <c r="D62">
+        <v>106.64069029544257</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62">
+        <v>2</v>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <v>Stk</v>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+      <c r="K62" t="str">
+        <v/>
+      </c>
+      <c r="L62" t="str">
+        <v>images/vvk1-2026-04-13T02-05-32-103Z.jpeg</v>
+      </c>
+      <c r="M62" t="str">
+        <v>09:04:48 13/4/2026</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v/>
+      </c>
+      <c r="B63" t="str">
+        <v>Vvk2</v>
+      </c>
+      <c r="C63">
+        <v>10.739414501411282</v>
+      </c>
+      <c r="D63">
+        <v>106.64024482935218</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63">
+        <v>2</v>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <v>Stk</v>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
+        <v/>
+      </c>
+      <c r="L63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
+        <v>09:05:00 13/4/2026</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v/>
+      </c>
+      <c r="B64" t="str">
+        <v>Vvk3</v>
+      </c>
+      <c r="C64">
+        <v>10.740070466051796</v>
+      </c>
+      <c r="D64">
+        <v>106.63979685304984</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64">
+        <v>2</v>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+      <c r="I64" t="str">
+        <v>Stk</v>
+      </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
+      <c r="K64" t="str">
+        <v/>
+      </c>
+      <c r="L64" t="str">
+        <v/>
+      </c>
+      <c r="M64" t="str">
+        <v>09:05:09 13/4/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O64"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:O86"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3300,6 +3300,12 @@
       <c r="M62" t="str">
         <v>09:04:48 13/4/2026</v>
       </c>
+      <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -3341,6 +3347,12 @@
       <c r="M63" t="str">
         <v>09:05:00 13/4/2026</v>
       </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -3382,10 +3394,918 @@
       <c r="M64" t="str">
         <v>09:05:09 13/4/2026</v>
       </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v/>
+      </c>
+      <c r="B65" t="str">
+        <v>TS1</v>
+      </c>
+      <c r="C65">
+        <v>10.8948406</v>
+      </c>
+      <c r="D65">
+        <v>106.7783216</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65">
+        <v>6</v>
+      </c>
+      <c r="H65" t="str">
+        <v>HHT1</v>
+      </c>
+      <c r="I65" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+      <c r="K65" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L65" t="str">
+        <v/>
+      </c>
+      <c r="M65" t="str">
+        <v>08:56:11 13/4/2026</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v/>
+      </c>
+      <c r="B66" t="str">
+        <v>TS2</v>
+      </c>
+      <c r="C66">
+        <v>10.8950395</v>
+      </c>
+      <c r="D66">
+        <v>106.7787517</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66">
+        <v>6</v>
+      </c>
+      <c r="H66" t="str">
+        <v>HHT1</v>
+      </c>
+      <c r="I66" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+      <c r="K66" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L66" t="str">
+        <v/>
+      </c>
+      <c r="M66" t="str">
+        <v>08:56:40 13/4/2026</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v/>
+      </c>
+      <c r="B67" t="str">
+        <v>TS3</v>
+      </c>
+      <c r="C67">
+        <v>10.8951335</v>
+      </c>
+      <c r="D67">
+        <v>106.7788192</v>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67">
+        <v>6</v>
+      </c>
+      <c r="H67" t="str">
+        <v>HHT1</v>
+      </c>
+      <c r="I67" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+      <c r="K67" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L67" t="str">
+        <v/>
+      </c>
+      <c r="M67" t="str">
+        <v>08:57:02 13/4/2026</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v/>
+      </c>
+      <c r="B68" t="str">
+        <v>TS4</v>
+      </c>
+      <c r="C68">
+        <v>10.8952532</v>
+      </c>
+      <c r="D68">
+        <v>106.7793386</v>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68">
+        <v>6</v>
+      </c>
+      <c r="H68" t="str">
+        <v>HHT1</v>
+      </c>
+      <c r="I68" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+      <c r="K68" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L68" t="str">
+        <v/>
+      </c>
+      <c r="M68" t="str">
+        <v>08:57:18 13/4/2026</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v/>
+      </c>
+      <c r="B69" t="str">
+        <v>TS5</v>
+      </c>
+      <c r="C69">
+        <v>10.8953387</v>
+      </c>
+      <c r="D69">
+        <v>106.7796043</v>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69">
+        <v>6</v>
+      </c>
+      <c r="H69" t="str">
+        <v>HHT1</v>
+      </c>
+      <c r="I69" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+      <c r="K69" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L69" t="str">
+        <v/>
+      </c>
+      <c r="M69" t="str">
+        <v>08:57:35 13/4/2026</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v/>
+      </c>
+      <c r="B70" t="str">
+        <v>TS6</v>
+      </c>
+      <c r="C70">
+        <v>10.8954617</v>
+      </c>
+      <c r="D70">
+        <v>106.7798753</v>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70">
+        <v>6</v>
+      </c>
+      <c r="H70" t="str">
+        <v>HHT1</v>
+      </c>
+      <c r="I70" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
+      <c r="K70" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L70" t="str">
+        <v/>
+      </c>
+      <c r="M70" t="str">
+        <v>08:57:48 13/4/2026</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v/>
+      </c>
+      <c r="B71" t="str">
+        <v>TS7</v>
+      </c>
+      <c r="C71">
+        <v>10.8955236</v>
+      </c>
+      <c r="D71">
+        <v>106.7799418</v>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71">
+        <v>6</v>
+      </c>
+      <c r="H71" t="str">
+        <v>HHT1</v>
+      </c>
+      <c r="I71" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J71" t="str">
+        <v/>
+      </c>
+      <c r="K71" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L71" t="str">
+        <v/>
+      </c>
+      <c r="M71" t="str">
+        <v>08:58:01 13/4/2026</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v/>
+      </c>
+      <c r="B72" t="str">
+        <v>TS8</v>
+      </c>
+      <c r="C72">
+        <v>10.89555</v>
+      </c>
+      <c r="D72">
+        <v>106.7800039</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72">
+        <v>6</v>
+      </c>
+      <c r="H72" t="str">
+        <v>HHT1</v>
+      </c>
+      <c r="I72" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J72" t="str">
+        <v/>
+      </c>
+      <c r="K72" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L72" t="str">
+        <v/>
+      </c>
+      <c r="M72" t="str">
+        <v>08:58:14 13/4/2026</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v/>
+      </c>
+      <c r="B73" t="str">
+        <v>TS9</v>
+      </c>
+      <c r="C73">
+        <v>10.8957475</v>
+      </c>
+      <c r="D73">
+        <v>106.7807345</v>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73">
+        <v>6</v>
+      </c>
+      <c r="H73" t="str">
+        <v>HHT1</v>
+      </c>
+      <c r="I73" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J73" t="str">
+        <v/>
+      </c>
+      <c r="K73" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L73" t="str">
+        <v/>
+      </c>
+      <c r="M73" t="str">
+        <v>08:58:29 13/4/2026</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v/>
+      </c>
+      <c r="B74" t="str">
+        <v>TS10</v>
+      </c>
+      <c r="C74">
+        <v>10.8958495</v>
+      </c>
+      <c r="D74">
+        <v>106.7808881</v>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74">
+        <v>6</v>
+      </c>
+      <c r="H74" t="str">
+        <v>HHT1</v>
+      </c>
+      <c r="I74" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J74" t="str">
+        <v/>
+      </c>
+      <c r="K74" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L74" t="str">
+        <v/>
+      </c>
+      <c r="M74" t="str">
+        <v>08:58:43 13/4/2026</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v/>
+      </c>
+      <c r="B75" t="str">
+        <v>TS11</v>
+      </c>
+      <c r="C75">
+        <v>10.8959922</v>
+      </c>
+      <c r="D75">
+        <v>106.7812883</v>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75">
+        <v>6</v>
+      </c>
+      <c r="H75" t="str">
+        <v>HHT1</v>
+      </c>
+      <c r="I75" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J75" t="str">
+        <v/>
+      </c>
+      <c r="K75" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L75" t="str">
+        <v/>
+      </c>
+      <c r="M75" t="str">
+        <v>08:59:01 13/4/2026</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v/>
+      </c>
+      <c r="B76" t="str">
+        <v>TS12</v>
+      </c>
+      <c r="C76">
+        <v>10.8960035</v>
+      </c>
+      <c r="D76">
+        <v>106.781449</v>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76">
+        <v>6</v>
+      </c>
+      <c r="H76" t="str">
+        <v>HHT1</v>
+      </c>
+      <c r="I76" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J76" t="str">
+        <v/>
+      </c>
+      <c r="K76" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L76" t="str">
+        <v/>
+      </c>
+      <c r="M76" t="str">
+        <v>08:59:15 13/4/2026</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v/>
+      </c>
+      <c r="B77" t="str">
+        <v>TS13</v>
+      </c>
+      <c r="C77">
+        <v>10.8960587</v>
+      </c>
+      <c r="D77">
+        <v>106.7815926</v>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77">
+        <v>6</v>
+      </c>
+      <c r="H77" t="str">
+        <v>HHT1</v>
+      </c>
+      <c r="I77" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+      <c r="K77" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L77" t="str">
+        <v/>
+      </c>
+      <c r="M77" t="str">
+        <v>08:59:31 13/4/2026</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v/>
+      </c>
+      <c r="B78" t="str">
+        <v>TS14</v>
+      </c>
+      <c r="C78">
+        <v>10.8963037</v>
+      </c>
+      <c r="D78">
+        <v>106.7820472</v>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78">
+        <v>6</v>
+      </c>
+      <c r="H78" t="str">
+        <v>HHT1</v>
+      </c>
+      <c r="I78" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J78" t="str">
+        <v/>
+      </c>
+      <c r="K78" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L78" t="str">
+        <v/>
+      </c>
+      <c r="M78" t="str">
+        <v>08:59:42 13/4/2026</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v/>
+      </c>
+      <c r="B79" t="str">
+        <v>TS15</v>
+      </c>
+      <c r="C79">
+        <v>10.8963269</v>
+      </c>
+      <c r="D79">
+        <v>106.7821845</v>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79">
+        <v>6</v>
+      </c>
+      <c r="H79" t="str">
+        <v>HHT1</v>
+      </c>
+      <c r="I79" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J79" t="str">
+        <v/>
+      </c>
+      <c r="K79" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L79" t="str">
+        <v/>
+      </c>
+      <c r="M79" t="str">
+        <v>08:59:58 13/4/2026</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v/>
+      </c>
+      <c r="B80" t="str">
+        <v>TS16</v>
+      </c>
+      <c r="C80">
+        <v>10.8963457</v>
+      </c>
+      <c r="D80">
+        <v>106.782243</v>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80">
+        <v>6</v>
+      </c>
+      <c r="H80" t="str">
+        <v>HHT1</v>
+      </c>
+      <c r="I80" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J80" t="str">
+        <v/>
+      </c>
+      <c r="K80" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L80" t="str">
+        <v/>
+      </c>
+      <c r="M80" t="str">
+        <v>09:00:10 13/4/2026</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v/>
+      </c>
+      <c r="B81" t="str">
+        <v>TS17</v>
+      </c>
+      <c r="C81">
+        <v>10.8965862</v>
+      </c>
+      <c r="D81">
+        <v>106.7827966</v>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81">
+        <v>6</v>
+      </c>
+      <c r="H81" t="str">
+        <v>HHT1</v>
+      </c>
+      <c r="I81" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J81" t="str">
+        <v/>
+      </c>
+      <c r="K81" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L81" t="str">
+        <v/>
+      </c>
+      <c r="M81" t="str">
+        <v>09:00:23 13/4/2026</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v/>
+      </c>
+      <c r="B82" t="str">
+        <v>TS18</v>
+      </c>
+      <c r="C82">
+        <v>10.8966627</v>
+      </c>
+      <c r="D82">
+        <v>106.7831476</v>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82">
+        <v>6</v>
+      </c>
+      <c r="H82" t="str">
+        <v>HHT1</v>
+      </c>
+      <c r="I82" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J82" t="str">
+        <v/>
+      </c>
+      <c r="K82" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L82" t="str">
+        <v/>
+      </c>
+      <c r="M82" t="str">
+        <v>09:00:38 13/4/2026</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v/>
+      </c>
+      <c r="B83" t="str">
+        <v>TS19</v>
+      </c>
+      <c r="C83">
+        <v>10.8967981</v>
+      </c>
+      <c r="D83">
+        <v>106.7834764</v>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83">
+        <v>6</v>
+      </c>
+      <c r="H83" t="str">
+        <v>HHT1</v>
+      </c>
+      <c r="I83" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J83" t="str">
+        <v/>
+      </c>
+      <c r="K83" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L83" t="str">
+        <v/>
+      </c>
+      <c r="M83" t="str">
+        <v>09:00:51 13/4/2026</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v/>
+      </c>
+      <c r="B84" t="str">
+        <v>TS20</v>
+      </c>
+      <c r="C84">
+        <v>10.8968367</v>
+      </c>
+      <c r="D84">
+        <v>106.7837997</v>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84">
+        <v>6</v>
+      </c>
+      <c r="H84" t="str">
+        <v>HHT1</v>
+      </c>
+      <c r="I84" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J84" t="str">
+        <v/>
+      </c>
+      <c r="K84" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L84" t="str">
+        <v/>
+      </c>
+      <c r="M84" t="str">
+        <v>09:01:08 13/4/2026</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v/>
+      </c>
+      <c r="B85" t="str">
+        <v>TS21</v>
+      </c>
+      <c r="C85">
+        <v>10.8972767</v>
+      </c>
+      <c r="D85">
+        <v>106.7834944</v>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85">
+        <v>6</v>
+      </c>
+      <c r="H85" t="str">
+        <v>HHT1</v>
+      </c>
+      <c r="I85" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J85" t="str">
+        <v/>
+      </c>
+      <c r="K85" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L85" t="str">
+        <v/>
+      </c>
+      <c r="M85" t="str">
+        <v>09:01:28 13/4/2026</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v/>
+      </c>
+      <c r="B86" t="str">
+        <v>TS22</v>
+      </c>
+      <c r="C86">
+        <v>10.8969084</v>
+      </c>
+      <c r="D86">
+        <v>106.7834593</v>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86">
+        <v>6</v>
+      </c>
+      <c r="H86" t="str">
+        <v>HHT1</v>
+      </c>
+      <c r="I86" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J86" t="str">
+        <v/>
+      </c>
+      <c r="K86" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L86" t="str">
+        <v/>
+      </c>
+      <c r="M86" t="str">
+        <v>09:01:43 13/4/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O64"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O86"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O98"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3441,6 +3441,12 @@
       <c r="M65" t="str">
         <v>08:56:11 13/4/2026</v>
       </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -3482,6 +3488,12 @@
       <c r="M66" t="str">
         <v>08:56:40 13/4/2026</v>
       </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -3523,6 +3535,12 @@
       <c r="M67" t="str">
         <v>08:57:02 13/4/2026</v>
       </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -3564,6 +3582,12 @@
       <c r="M68" t="str">
         <v>08:57:18 13/4/2026</v>
       </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -3605,6 +3629,12 @@
       <c r="M69" t="str">
         <v>08:57:35 13/4/2026</v>
       </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -3646,6 +3676,12 @@
       <c r="M70" t="str">
         <v>08:57:48 13/4/2026</v>
       </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -3687,6 +3723,12 @@
       <c r="M71" t="str">
         <v>08:58:01 13/4/2026</v>
       </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -3728,6 +3770,12 @@
       <c r="M72" t="str">
         <v>08:58:14 13/4/2026</v>
       </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -3769,6 +3817,12 @@
       <c r="M73" t="str">
         <v>08:58:29 13/4/2026</v>
       </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -3810,6 +3864,12 @@
       <c r="M74" t="str">
         <v>08:58:43 13/4/2026</v>
       </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -3851,6 +3911,12 @@
       <c r="M75" t="str">
         <v>08:59:01 13/4/2026</v>
       </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -3892,6 +3958,12 @@
       <c r="M76" t="str">
         <v>08:59:15 13/4/2026</v>
       </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -3933,6 +4005,12 @@
       <c r="M77" t="str">
         <v>08:59:31 13/4/2026</v>
       </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -3974,6 +4052,12 @@
       <c r="M78" t="str">
         <v>08:59:42 13/4/2026</v>
       </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -4015,6 +4099,12 @@
       <c r="M79" t="str">
         <v>08:59:58 13/4/2026</v>
       </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -4056,6 +4146,12 @@
       <c r="M80" t="str">
         <v>09:00:10 13/4/2026</v>
       </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -4097,6 +4193,12 @@
       <c r="M81" t="str">
         <v>09:00:23 13/4/2026</v>
       </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -4138,6 +4240,12 @@
       <c r="M82" t="str">
         <v>09:00:38 13/4/2026</v>
       </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -4179,6 +4287,12 @@
       <c r="M83" t="str">
         <v>09:00:51 13/4/2026</v>
       </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -4220,6 +4334,12 @@
       <c r="M84" t="str">
         <v>09:01:08 13/4/2026</v>
       </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -4261,6 +4381,12 @@
       <c r="M85" t="str">
         <v>09:01:28 13/4/2026</v>
       </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -4302,10 +4428,508 @@
       <c r="M86" t="str">
         <v>09:01:43 13/4/2026</v>
       </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v/>
+      </c>
+      <c r="B87" t="str">
+        <v>NTU-1</v>
+      </c>
+      <c r="C87">
+        <v>10.8922611</v>
+      </c>
+      <c r="D87">
+        <v>106.7847772</v>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87">
+        <v>6</v>
+      </c>
+      <c r="H87" t="str">
+        <v>NTU</v>
+      </c>
+      <c r="I87" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J87" t="str">
+        <v/>
+      </c>
+      <c r="K87" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L87" t="str">
+        <v/>
+      </c>
+      <c r="M87" t="str">
+        <v>09:16:53 13/4/2026</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v/>
+      </c>
+      <c r="B88" t="str">
+        <v>NTU-2</v>
+      </c>
+      <c r="C88">
+        <v>10.8923432</v>
+      </c>
+      <c r="D88">
+        <v>106.7849759</v>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88">
+        <v>2</v>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+      <c r="I88" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J88" t="str">
+        <v/>
+      </c>
+      <c r="K88" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L88" t="str">
+        <v/>
+      </c>
+      <c r="M88" t="str">
+        <v>09:17:12 13/4/2026</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v/>
+      </c>
+      <c r="B89" t="str">
+        <v>NTU-3</v>
+      </c>
+      <c r="C89">
+        <v>10.9009009009009</v>
+      </c>
+      <c r="D89">
+        <v>106.77349563826016</v>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89">
+        <v>2</v>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+      <c r="I89" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J89" t="str">
+        <v/>
+      </c>
+      <c r="K89" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L89" t="str">
+        <v/>
+      </c>
+      <c r="M89" t="str">
+        <v>09:17:29 13/4/2026</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v/>
+      </c>
+      <c r="B90" t="str">
+        <v>NTU-4</v>
+      </c>
+      <c r="C90">
+        <v>10.8923349</v>
+      </c>
+      <c r="D90">
+        <v>106.7854695</v>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90">
+        <v>2</v>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+      <c r="I90" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J90" t="str">
+        <v/>
+      </c>
+      <c r="K90" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L90" t="str">
+        <v/>
+      </c>
+      <c r="M90" t="str">
+        <v>09:17:41 13/4/2026</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v/>
+      </c>
+      <c r="B91" t="str">
+        <v>NTU-5</v>
+      </c>
+      <c r="C91">
+        <v>10.8924067</v>
+      </c>
+      <c r="D91">
+        <v>106.7855887</v>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91">
+        <v>2</v>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+      <c r="I91" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J91" t="str">
+        <v/>
+      </c>
+      <c r="K91" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L91" t="str">
+        <v/>
+      </c>
+      <c r="M91" t="str">
+        <v>09:17:54 13/4/2026</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v/>
+      </c>
+      <c r="B92" t="str">
+        <v>NTU-6</v>
+      </c>
+      <c r="C92">
+        <v>10.892417</v>
+      </c>
+      <c r="D92">
+        <v>106.7856242</v>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92">
+        <v>2</v>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+      <c r="I92" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J92" t="str">
+        <v/>
+      </c>
+      <c r="K92" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L92" t="str">
+        <v/>
+      </c>
+      <c r="M92" t="str">
+        <v>09:18:09 13/4/2026</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v/>
+      </c>
+      <c r="B93" t="str">
+        <v>NTU-7</v>
+      </c>
+      <c r="C93">
+        <v>10.8922592</v>
+      </c>
+      <c r="D93">
+        <v>106.7863334</v>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93">
+        <v>2</v>
+      </c>
+      <c r="H93" t="str">
+        <v/>
+      </c>
+      <c r="I93" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J93" t="str">
+        <v/>
+      </c>
+      <c r="K93" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L93" t="str">
+        <v/>
+      </c>
+      <c r="M93" t="str">
+        <v>09:18:25 13/4/2026</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v/>
+      </c>
+      <c r="B94" t="str">
+        <v>NTU-8</v>
+      </c>
+      <c r="C94">
+        <v>10.8922394</v>
+      </c>
+      <c r="D94">
+        <v>106.7866072</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94">
+        <v>2</v>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+      <c r="I94" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J94" t="str">
+        <v/>
+      </c>
+      <c r="K94" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L94" t="str">
+        <v/>
+      </c>
+      <c r="M94" t="str">
+        <v>09:18:41 13/4/2026</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v/>
+      </c>
+      <c r="B95" t="str">
+        <v>NTU-9</v>
+      </c>
+      <c r="C95">
+        <v>10.8922696</v>
+      </c>
+      <c r="D95">
+        <v>106.7866821</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95">
+        <v>2</v>
+      </c>
+      <c r="H95" t="str">
+        <v/>
+      </c>
+      <c r="I95" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J95" t="str">
+        <v/>
+      </c>
+      <c r="K95" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L95" t="str">
+        <v/>
+      </c>
+      <c r="M95" t="str">
+        <v>09:18:56 13/4/2026</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v/>
+      </c>
+      <c r="B96" t="str">
+        <v>NTU-10</v>
+      </c>
+      <c r="C96">
+        <v>10.8922965</v>
+      </c>
+      <c r="D96">
+        <v>106.7867306</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96">
+        <v>2</v>
+      </c>
+      <c r="H96" t="str">
+        <v/>
+      </c>
+      <c r="I96" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J96" t="str">
+        <v/>
+      </c>
+      <c r="K96" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L96" t="str">
+        <v/>
+      </c>
+      <c r="M96" t="str">
+        <v>09:19:10 13/4/2026</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v/>
+      </c>
+      <c r="B97" t="str">
+        <v>NTU-11</v>
+      </c>
+      <c r="C97">
+        <v>10.892343</v>
+      </c>
+      <c r="D97">
+        <v>106.787437</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97">
+        <v>2</v>
+      </c>
+      <c r="H97" t="str">
+        <v/>
+      </c>
+      <c r="I97" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J97" t="str">
+        <v/>
+      </c>
+      <c r="K97" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L97" t="str">
+        <v/>
+      </c>
+      <c r="M97" t="str">
+        <v>09:19:26 13/4/2026</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v/>
+      </c>
+      <c r="B98" t="str">
+        <v>NTU-12</v>
+      </c>
+      <c r="C98">
+        <v>10.892395</v>
+      </c>
+      <c r="D98">
+        <v>106.7875626</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98">
+        <v>2</v>
+      </c>
+      <c r="H98" t="str">
+        <v/>
+      </c>
+      <c r="I98" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J98" t="str">
+        <v/>
+      </c>
+      <c r="K98" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L98" t="str">
+        <v/>
+      </c>
+      <c r="M98" t="str">
+        <v>09:19:43 13/4/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O86"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O98"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O121"/>
+  <dimension ref="A1:O128"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3958,6 +3958,12 @@
       <c r="M76" t="str">
         <v>09:35:34 13/4/2026</v>
       </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -3999,6 +4005,12 @@
       <c r="M77" t="str">
         <v>09:35:54 13/4/2026</v>
       </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -4040,6 +4052,12 @@
       <c r="M78" t="str">
         <v>09:36:11 13/4/2026</v>
       </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -4081,6 +4099,12 @@
       <c r="M79" t="str">
         <v>09:36:25 13/4/2026</v>
       </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -4122,6 +4146,12 @@
       <c r="M80" t="str">
         <v>09:36:46 13/4/2026</v>
       </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -4163,6 +4193,12 @@
       <c r="M81" t="str">
         <v>09:37:01 13/4/2026</v>
       </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -4204,6 +4240,12 @@
       <c r="M82" t="str">
         <v>09:37:20 13/4/2026</v>
       </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -4245,6 +4287,12 @@
       <c r="M83" t="str">
         <v>09:37:38 13/4/2026</v>
       </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -4286,6 +4334,12 @@
       <c r="M84" t="str">
         <v>09:37:54 13/4/2026</v>
       </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -4327,6 +4381,12 @@
       <c r="M85" t="str">
         <v>09:38:11 13/4/2026</v>
       </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -4368,6 +4428,12 @@
       <c r="M86" t="str">
         <v>09:38:26 13/4/2026</v>
       </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -4409,6 +4475,12 @@
       <c r="M87" t="str">
         <v>09:38:44 13/4/2026</v>
       </c>
+      <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -4450,6 +4522,12 @@
       <c r="M88" t="str">
         <v>09:39:01 13/4/2026</v>
       </c>
+      <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -4491,6 +4569,12 @@
       <c r="M89" t="str">
         <v>09:39:18 13/4/2026</v>
       </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -4532,6 +4616,12 @@
       <c r="M90" t="str">
         <v>09:39:37 13/4/2026</v>
       </c>
+      <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -4573,6 +4663,12 @@
       <c r="M91" t="str">
         <v>09:40:15 13/4/2026</v>
       </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -4614,6 +4710,12 @@
       <c r="M92" t="str">
         <v>09:40:31 13/4/2026</v>
       </c>
+      <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -4655,6 +4757,12 @@
       <c r="M93" t="str">
         <v>09:40:47 13/4/2026</v>
       </c>
+      <c r="N93" t="str">
+        <v/>
+      </c>
+      <c r="O93" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -4696,6 +4804,12 @@
       <c r="M94" t="str">
         <v>09:41:04 13/4/2026</v>
       </c>
+      <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -4737,6 +4851,12 @@
       <c r="M95" t="str">
         <v>09:41:32 13/4/2026</v>
       </c>
+      <c r="N95" t="str">
+        <v/>
+      </c>
+      <c r="O95" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -4778,6 +4898,12 @@
       <c r="M96" t="str">
         <v>09:41:49 13/4/2026</v>
       </c>
+      <c r="N96" t="str">
+        <v/>
+      </c>
+      <c r="O96" t="str">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -4819,6 +4945,12 @@
       <c r="M97" t="str">
         <v>09:42:06 13/4/2026</v>
       </c>
+      <c r="N97" t="str">
+        <v/>
+      </c>
+      <c r="O97" t="str">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -4860,6 +4992,12 @@
       <c r="M98" t="str">
         <v>09:42:32 13/4/2026</v>
       </c>
+      <c r="N98" t="str">
+        <v/>
+      </c>
+      <c r="O98" t="str">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -4901,6 +5039,12 @@
       <c r="M99" t="str">
         <v>09:42:52 13/4/2026</v>
       </c>
+      <c r="N99" t="str">
+        <v/>
+      </c>
+      <c r="O99" t="str">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -4942,6 +5086,12 @@
       <c r="M100" t="str">
         <v>09:43:14 13/4/2026</v>
       </c>
+      <c r="N100" t="str">
+        <v/>
+      </c>
+      <c r="O100" t="str">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -4983,6 +5133,12 @@
       <c r="M101" t="str">
         <v>09:43:29 13/4/2026</v>
       </c>
+      <c r="N101" t="str">
+        <v/>
+      </c>
+      <c r="O101" t="str">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -5024,6 +5180,12 @@
       <c r="M102" t="str">
         <v>09:43:44 13/4/2026</v>
       </c>
+      <c r="N102" t="str">
+        <v/>
+      </c>
+      <c r="O102" t="str">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -5065,6 +5227,12 @@
       <c r="M103" t="str">
         <v>09:44:02 13/4/2026</v>
       </c>
+      <c r="N103" t="str">
+        <v/>
+      </c>
+      <c r="O103" t="str">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -5106,6 +5274,12 @@
       <c r="M104" t="str">
         <v>09:44:18 13/4/2026</v>
       </c>
+      <c r="N104" t="str">
+        <v/>
+      </c>
+      <c r="O104" t="str">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -5147,6 +5321,12 @@
       <c r="M105" t="str">
         <v>09:44:37 13/4/2026</v>
       </c>
+      <c r="N105" t="str">
+        <v/>
+      </c>
+      <c r="O105" t="str">
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -5188,6 +5368,12 @@
       <c r="M106" t="str">
         <v>09:44:55 13/4/2026</v>
       </c>
+      <c r="N106" t="str">
+        <v/>
+      </c>
+      <c r="O106" t="str">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -5229,6 +5415,12 @@
       <c r="M107" t="str">
         <v>09:45:12 13/4/2026</v>
       </c>
+      <c r="N107" t="str">
+        <v/>
+      </c>
+      <c r="O107" t="str">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -5270,6 +5462,12 @@
       <c r="M108" t="str">
         <v>09:45:28 13/4/2026</v>
       </c>
+      <c r="N108" t="str">
+        <v/>
+      </c>
+      <c r="O108" t="str">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -5311,6 +5509,12 @@
       <c r="M109" t="str">
         <v>09:45:44 13/4/2026</v>
       </c>
+      <c r="N109" t="str">
+        <v/>
+      </c>
+      <c r="O109" t="str">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -5352,6 +5556,12 @@
       <c r="M110" t="str">
         <v>09:46:01 13/4/2026</v>
       </c>
+      <c r="N110" t="str">
+        <v/>
+      </c>
+      <c r="O110" t="str">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -5393,6 +5603,12 @@
       <c r="M111" t="str">
         <v>09:46:22 13/4/2026</v>
       </c>
+      <c r="N111" t="str">
+        <v/>
+      </c>
+      <c r="O111" t="str">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -5434,6 +5650,12 @@
       <c r="M112" t="str">
         <v>09:46:39 13/4/2026</v>
       </c>
+      <c r="N112" t="str">
+        <v/>
+      </c>
+      <c r="O112" t="str">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -5475,6 +5697,12 @@
       <c r="M113" t="str">
         <v>09:46:56 13/4/2026</v>
       </c>
+      <c r="N113" t="str">
+        <v/>
+      </c>
+      <c r="O113" t="str">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -5516,6 +5744,12 @@
       <c r="M114" t="str">
         <v>09:47:13 13/4/2026</v>
       </c>
+      <c r="N114" t="str">
+        <v/>
+      </c>
+      <c r="O114" t="str">
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -5557,6 +5791,12 @@
       <c r="M115" t="str">
         <v>09:47:32 13/4/2026</v>
       </c>
+      <c r="N115" t="str">
+        <v/>
+      </c>
+      <c r="O115" t="str">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -5598,6 +5838,12 @@
       <c r="M116" t="str">
         <v>09:47:49 13/4/2026</v>
       </c>
+      <c r="N116" t="str">
+        <v/>
+      </c>
+      <c r="O116" t="str">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -5639,6 +5885,12 @@
       <c r="M117" t="str">
         <v>09:48:05 13/4/2026</v>
       </c>
+      <c r="N117" t="str">
+        <v/>
+      </c>
+      <c r="O117" t="str">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -5680,6 +5932,12 @@
       <c r="M118" t="str">
         <v>09:48:21 13/4/2026</v>
       </c>
+      <c r="N118" t="str">
+        <v/>
+      </c>
+      <c r="O118" t="str">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -5721,6 +5979,12 @@
       <c r="M119" t="str">
         <v>09:48:39 13/4/2026</v>
       </c>
+      <c r="N119" t="str">
+        <v/>
+      </c>
+      <c r="O119" t="str">
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -5762,6 +6026,12 @@
       <c r="M120" t="str">
         <v>09:48:56 13/4/2026</v>
       </c>
+      <c r="N120" t="str">
+        <v/>
+      </c>
+      <c r="O120" t="str">
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -5803,10 +6073,303 @@
       <c r="M121" t="str">
         <v>09:49:16 13/4/2026</v>
       </c>
+      <c r="N121" t="str">
+        <v/>
+      </c>
+      <c r="O121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v/>
+      </c>
+      <c r="B122" t="str">
+        <v>NVC-1</v>
+      </c>
+      <c r="C122">
+        <v>10.9007677</v>
+      </c>
+      <c r="D122">
+        <v>106.7848408</v>
+      </c>
+      <c r="E122" t="str">
+        <v/>
+      </c>
+      <c r="F122" t="str">
+        <v/>
+      </c>
+      <c r="G122">
+        <v>2</v>
+      </c>
+      <c r="H122" t="str">
+        <v/>
+      </c>
+      <c r="I122" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J122" t="str">
+        <v/>
+      </c>
+      <c r="K122" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L122" t="str">
+        <v/>
+      </c>
+      <c r="M122" t="str">
+        <v>10:00:08 13/4/2026</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v/>
+      </c>
+      <c r="B123" t="str">
+        <v>NVC-2</v>
+      </c>
+      <c r="C123">
+        <v>10.9004119</v>
+      </c>
+      <c r="D123">
+        <v>106.7849756</v>
+      </c>
+      <c r="E123" t="str">
+        <v/>
+      </c>
+      <c r="F123" t="str">
+        <v/>
+      </c>
+      <c r="G123">
+        <v>2</v>
+      </c>
+      <c r="H123" t="str">
+        <v/>
+      </c>
+      <c r="I123" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J123" t="str">
+        <v/>
+      </c>
+      <c r="K123" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L123" t="str">
+        <v/>
+      </c>
+      <c r="M123" t="str">
+        <v>10:00:30 13/4/2026</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v/>
+      </c>
+      <c r="B124" t="str">
+        <v>NVC-3</v>
+      </c>
+      <c r="C124">
+        <v>10.9002838</v>
+      </c>
+      <c r="D124">
+        <v>106.7848604</v>
+      </c>
+      <c r="E124" t="str">
+        <v/>
+      </c>
+      <c r="F124" t="str">
+        <v/>
+      </c>
+      <c r="G124">
+        <v>2</v>
+      </c>
+      <c r="H124" t="str">
+        <v/>
+      </c>
+      <c r="I124" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J124" t="str">
+        <v/>
+      </c>
+      <c r="K124" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L124" t="str">
+        <v/>
+      </c>
+      <c r="M124" t="str">
+        <v>10:00:45 13/4/2026</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v/>
+      </c>
+      <c r="B125" t="str">
+        <v>NVC-4</v>
+      </c>
+      <c r="C125">
+        <v>10.9001442</v>
+      </c>
+      <c r="D125">
+        <v>106.7848551</v>
+      </c>
+      <c r="E125" t="str">
+        <v/>
+      </c>
+      <c r="F125" t="str">
+        <v/>
+      </c>
+      <c r="G125">
+        <v>2</v>
+      </c>
+      <c r="H125" t="str">
+        <v/>
+      </c>
+      <c r="I125" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J125" t="str">
+        <v/>
+      </c>
+      <c r="K125" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L125" t="str">
+        <v/>
+      </c>
+      <c r="M125" t="str">
+        <v>10:01:01 13/4/2026</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v/>
+      </c>
+      <c r="B126" t="str">
+        <v>NVC-5</v>
+      </c>
+      <c r="C126">
+        <v>10.8996704</v>
+      </c>
+      <c r="D126">
+        <v>106.7849199</v>
+      </c>
+      <c r="E126" t="str">
+        <v/>
+      </c>
+      <c r="F126" t="str">
+        <v/>
+      </c>
+      <c r="G126">
+        <v>2</v>
+      </c>
+      <c r="H126" t="str">
+        <v/>
+      </c>
+      <c r="I126" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J126" t="str">
+        <v/>
+      </c>
+      <c r="K126" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L126" t="str">
+        <v/>
+      </c>
+      <c r="M126" t="str">
+        <v>10:01:24 13/4/2026</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v/>
+      </c>
+      <c r="B127" t="str">
+        <v>NVC-6</v>
+      </c>
+      <c r="C127">
+        <v>10.8995594</v>
+      </c>
+      <c r="D127">
+        <v>106.7848668</v>
+      </c>
+      <c r="E127" t="str">
+        <v/>
+      </c>
+      <c r="F127" t="str">
+        <v/>
+      </c>
+      <c r="G127">
+        <v>2</v>
+      </c>
+      <c r="H127" t="str">
+        <v/>
+      </c>
+      <c r="I127" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J127" t="str">
+        <v/>
+      </c>
+      <c r="K127" t="str">
+        <v>HPS 2 đèn</v>
+      </c>
+      <c r="L127" t="str">
+        <v/>
+      </c>
+      <c r="M127" t="str">
+        <v>10:01:46 13/4/2026</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v/>
+      </c>
+      <c r="B128" t="str">
+        <v>NVC-7</v>
+      </c>
+      <c r="C128">
+        <v>10.8991268</v>
+      </c>
+      <c r="D128">
+        <v>106.7849153</v>
+      </c>
+      <c r="E128" t="str">
+        <v/>
+      </c>
+      <c r="F128" t="str">
+        <v/>
+      </c>
+      <c r="G128">
+        <v>2</v>
+      </c>
+      <c r="H128" t="str">
+        <v/>
+      </c>
+      <c r="I128" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J128" t="str">
+        <v/>
+      </c>
+      <c r="K128" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L128" t="str">
+        <v/>
+      </c>
+      <c r="M128" t="str">
+        <v>10:02:02 13/4/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O121"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O128"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O128"/>
+  <dimension ref="A1:O154"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6120,6 +6120,12 @@
       <c r="M122" t="str">
         <v>10:00:08 13/4/2026</v>
       </c>
+      <c r="N122" t="str">
+        <v/>
+      </c>
+      <c r="O122" t="str">
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -6161,6 +6167,12 @@
       <c r="M123" t="str">
         <v>10:00:30 13/4/2026</v>
       </c>
+      <c r="N123" t="str">
+        <v/>
+      </c>
+      <c r="O123" t="str">
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -6202,6 +6214,12 @@
       <c r="M124" t="str">
         <v>10:00:45 13/4/2026</v>
       </c>
+      <c r="N124" t="str">
+        <v/>
+      </c>
+      <c r="O124" t="str">
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -6243,6 +6261,12 @@
       <c r="M125" t="str">
         <v>10:01:01 13/4/2026</v>
       </c>
+      <c r="N125" t="str">
+        <v/>
+      </c>
+      <c r="O125" t="str">
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -6284,6 +6308,12 @@
       <c r="M126" t="str">
         <v>10:01:24 13/4/2026</v>
       </c>
+      <c r="N126" t="str">
+        <v/>
+      </c>
+      <c r="O126" t="str">
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -6325,6 +6355,12 @@
       <c r="M127" t="str">
         <v>10:01:46 13/4/2026</v>
       </c>
+      <c r="N127" t="str">
+        <v/>
+      </c>
+      <c r="O127" t="str">
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -6366,10 +6402,1082 @@
       <c r="M128" t="str">
         <v>10:02:02 13/4/2026</v>
       </c>
+      <c r="N128" t="str">
+        <v/>
+      </c>
+      <c r="O128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v/>
+      </c>
+      <c r="B129" t="str">
+        <v>NĐC-1</v>
+      </c>
+      <c r="C129">
+        <v>10.9004279</v>
+      </c>
+      <c r="D129">
+        <v>106.7822653</v>
+      </c>
+      <c r="E129" t="str">
+        <v/>
+      </c>
+      <c r="F129" t="str">
+        <v/>
+      </c>
+      <c r="G129">
+        <v>2</v>
+      </c>
+      <c r="H129" t="str">
+        <v/>
+      </c>
+      <c r="I129" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J129" t="str">
+        <v/>
+      </c>
+      <c r="K129" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L129" t="str">
+        <v/>
+      </c>
+      <c r="M129" t="str">
+        <v>10:07:02 13/4/2026</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v/>
+      </c>
+      <c r="B130" t="str">
+        <v>NĐC-2</v>
+      </c>
+      <c r="C130">
+        <v>10.9002921</v>
+      </c>
+      <c r="D130">
+        <v>106.7822468</v>
+      </c>
+      <c r="E130" t="str">
+        <v/>
+      </c>
+      <c r="F130" t="str">
+        <v/>
+      </c>
+      <c r="G130">
+        <v>2</v>
+      </c>
+      <c r="H130" t="str">
+        <v/>
+      </c>
+      <c r="I130" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J130" t="str">
+        <v/>
+      </c>
+      <c r="K130" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L130" t="str">
+        <v/>
+      </c>
+      <c r="M130" t="str">
+        <v>10:07:25 13/4/2026</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v/>
+      </c>
+      <c r="B131" t="str">
+        <v>NĐC-3</v>
+      </c>
+      <c r="C131">
+        <v>10.9003095</v>
+      </c>
+      <c r="D131">
+        <v>106.78271</v>
+      </c>
+      <c r="E131" t="str">
+        <v/>
+      </c>
+      <c r="F131" t="str">
+        <v/>
+      </c>
+      <c r="G131">
+        <v>2</v>
+      </c>
+      <c r="H131" t="str">
+        <v/>
+      </c>
+      <c r="I131" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J131" t="str">
+        <v/>
+      </c>
+      <c r="K131" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L131" t="str">
+        <v/>
+      </c>
+      <c r="M131" t="str">
+        <v>10:07:49 13/4/2026</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v/>
+      </c>
+      <c r="B132" t="str">
+        <v>NĐC-4</v>
+      </c>
+      <c r="C132">
+        <v>10.9003686</v>
+      </c>
+      <c r="D132">
+        <v>106.7828058</v>
+      </c>
+      <c r="E132" t="str">
+        <v/>
+      </c>
+      <c r="F132" t="str">
+        <v/>
+      </c>
+      <c r="G132">
+        <v>2</v>
+      </c>
+      <c r="H132" t="str">
+        <v/>
+      </c>
+      <c r="I132" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J132" t="str">
+        <v/>
+      </c>
+      <c r="K132" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L132" t="str">
+        <v/>
+      </c>
+      <c r="M132" t="str">
+        <v>10:08:00 13/4/2026</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v/>
+      </c>
+      <c r="B133" t="str">
+        <v>NĐC-5</v>
+      </c>
+      <c r="C133">
+        <v>10.9004258</v>
+      </c>
+      <c r="D133">
+        <v>106.7830298</v>
+      </c>
+      <c r="E133" t="str">
+        <v/>
+      </c>
+      <c r="F133" t="str">
+        <v/>
+      </c>
+      <c r="G133">
+        <v>2</v>
+      </c>
+      <c r="H133" t="str">
+        <v/>
+      </c>
+      <c r="I133" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J133" t="str">
+        <v/>
+      </c>
+      <c r="K133" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L133" t="str">
+        <v/>
+      </c>
+      <c r="M133" t="str">
+        <v>10:08:14 13/4/2026</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v/>
+      </c>
+      <c r="B134" t="str">
+        <v>NĐC-6</v>
+      </c>
+      <c r="C134">
+        <v>10.9004632</v>
+      </c>
+      <c r="D134">
+        <v>106.7831386</v>
+      </c>
+      <c r="E134" t="str">
+        <v/>
+      </c>
+      <c r="F134" t="str">
+        <v/>
+      </c>
+      <c r="G134">
+        <v>2</v>
+      </c>
+      <c r="H134" t="str">
+        <v/>
+      </c>
+      <c r="I134" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J134" t="str">
+        <v/>
+      </c>
+      <c r="K134" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L134" t="str">
+        <v/>
+      </c>
+      <c r="M134" t="str">
+        <v>10:08:28 13/4/2026</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v/>
+      </c>
+      <c r="B135" t="str">
+        <v>NĐC-7</v>
+      </c>
+      <c r="C135">
+        <v>10.9005003</v>
+      </c>
+      <c r="D135">
+        <v>106.7837046</v>
+      </c>
+      <c r="E135" t="str">
+        <v/>
+      </c>
+      <c r="F135" t="str">
+        <v/>
+      </c>
+      <c r="G135">
+        <v>2</v>
+      </c>
+      <c r="H135" t="str">
+        <v/>
+      </c>
+      <c r="I135" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J135" t="str">
+        <v/>
+      </c>
+      <c r="K135" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L135" t="str">
+        <v/>
+      </c>
+      <c r="M135" t="str">
+        <v>10:08:48 13/4/2026</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v/>
+      </c>
+      <c r="B136" t="str">
+        <v>Tủ</v>
+      </c>
+      <c r="C136">
+        <v>10.9005176</v>
+      </c>
+      <c r="D136">
+        <v>106.7837164</v>
+      </c>
+      <c r="E136" t="str">
+        <v/>
+      </c>
+      <c r="F136" t="str">
+        <v/>
+      </c>
+      <c r="G136">
+        <v>6</v>
+      </c>
+      <c r="H136" t="str">
+        <v>NĐC 1</v>
+      </c>
+      <c r="I136" t="str">
+        <v/>
+      </c>
+      <c r="J136" t="str">
+        <v/>
+      </c>
+      <c r="K136" t="str">
+        <v/>
+      </c>
+      <c r="L136" t="str">
+        <v/>
+      </c>
+      <c r="M136" t="str">
+        <v>10:09:27 13/4/2026</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v/>
+      </c>
+      <c r="B137" t="str">
+        <v>Tủ điều khiển</v>
+      </c>
+      <c r="C137">
+        <v>10.9006067</v>
+      </c>
+      <c r="D137">
+        <v>106.783782</v>
+      </c>
+      <c r="E137" t="str">
+        <v/>
+      </c>
+      <c r="F137" t="str">
+        <v/>
+      </c>
+      <c r="G137">
+        <v>6</v>
+      </c>
+      <c r="H137" t="str">
+        <v>NĐC 1</v>
+      </c>
+      <c r="I137" t="str">
+        <v/>
+      </c>
+      <c r="J137" t="str">
+        <v/>
+      </c>
+      <c r="K137" t="str">
+        <v/>
+      </c>
+      <c r="L137" t="str">
+        <v>images/t-iu-khin-2026-04-13T03-19-05-674Z.jpeg</v>
+      </c>
+      <c r="M137" t="str">
+        <v>10:10:28 13/4/2026</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v/>
+      </c>
+      <c r="B138" t="str">
+        <v>NĐC-8</v>
+      </c>
+      <c r="C138">
+        <v>10.9004101</v>
+      </c>
+      <c r="D138">
+        <v>106.7838991</v>
+      </c>
+      <c r="E138" t="str">
+        <v/>
+      </c>
+      <c r="F138" t="str">
+        <v/>
+      </c>
+      <c r="G138">
+        <v>2</v>
+      </c>
+      <c r="H138" t="str">
+        <v/>
+      </c>
+      <c r="I138" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J138" t="str">
+        <v/>
+      </c>
+      <c r="K138" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L138" t="str">
+        <v/>
+      </c>
+      <c r="M138" t="str">
+        <v>10:12:27 13/4/2026</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v/>
+      </c>
+      <c r="B139" t="str">
+        <v>NĐC-9</v>
+      </c>
+      <c r="C139">
+        <v>10.900733</v>
+      </c>
+      <c r="D139">
+        <v>106.7842548</v>
+      </c>
+      <c r="E139" t="str">
+        <v/>
+      </c>
+      <c r="F139" t="str">
+        <v/>
+      </c>
+      <c r="G139">
+        <v>2</v>
+      </c>
+      <c r="H139" t="str">
+        <v/>
+      </c>
+      <c r="I139" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J139" t="str">
+        <v/>
+      </c>
+      <c r="K139" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L139" t="str">
+        <v/>
+      </c>
+      <c r="M139" t="str">
+        <v>10:12:46 13/4/2026</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v/>
+      </c>
+      <c r="B140" t="str">
+        <v>NĐC-10</v>
+      </c>
+      <c r="C140">
+        <v>10.9007563</v>
+      </c>
+      <c r="D140">
+        <v>106.7845458</v>
+      </c>
+      <c r="E140" t="str">
+        <v/>
+      </c>
+      <c r="F140" t="str">
+        <v/>
+      </c>
+      <c r="G140">
+        <v>2</v>
+      </c>
+      <c r="H140" t="str">
+        <v/>
+      </c>
+      <c r="I140" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J140" t="str">
+        <v/>
+      </c>
+      <c r="K140" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L140" t="str">
+        <v/>
+      </c>
+      <c r="M140" t="str">
+        <v>10:13:01 13/4/2026</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v/>
+      </c>
+      <c r="B141" t="str">
+        <v>NĐC-11</v>
+      </c>
+      <c r="C141">
+        <v>10.9008199</v>
+      </c>
+      <c r="D141">
+        <v>106.784711</v>
+      </c>
+      <c r="E141" t="str">
+        <v/>
+      </c>
+      <c r="F141" t="str">
+        <v/>
+      </c>
+      <c r="G141">
+        <v>2</v>
+      </c>
+      <c r="H141" t="str">
+        <v/>
+      </c>
+      <c r="I141" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J141" t="str">
+        <v/>
+      </c>
+      <c r="K141" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L141" t="str">
+        <v/>
+      </c>
+      <c r="M141" t="str">
+        <v>10:13:20 13/4/2026</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v/>
+      </c>
+      <c r="B142" t="str">
+        <v>NĐC-12</v>
+      </c>
+      <c r="C142">
+        <v>10.9011718</v>
+      </c>
+      <c r="D142">
+        <v>106.7852974</v>
+      </c>
+      <c r="E142" t="str">
+        <v/>
+      </c>
+      <c r="F142" t="str">
+        <v/>
+      </c>
+      <c r="G142">
+        <v>2</v>
+      </c>
+      <c r="H142" t="str">
+        <v/>
+      </c>
+      <c r="I142" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J142" t="str">
+        <v/>
+      </c>
+      <c r="K142" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L142" t="str">
+        <v/>
+      </c>
+      <c r="M142" t="str">
+        <v>10:13:38 13/4/2026</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v/>
+      </c>
+      <c r="B143" t="str">
+        <v>NĐC-13</v>
+      </c>
+      <c r="C143">
+        <v>10.901436</v>
+      </c>
+      <c r="D143">
+        <v>106.7856748</v>
+      </c>
+      <c r="E143" t="str">
+        <v/>
+      </c>
+      <c r="F143" t="str">
+        <v/>
+      </c>
+      <c r="G143">
+        <v>2</v>
+      </c>
+      <c r="H143" t="str">
+        <v/>
+      </c>
+      <c r="I143" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J143" t="str">
+        <v/>
+      </c>
+      <c r="K143" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L143" t="str">
+        <v/>
+      </c>
+      <c r="M143" t="str">
+        <v>10:13:57 13/4/2026</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v/>
+      </c>
+      <c r="B144" t="str">
+        <v>NĐC-14</v>
+      </c>
+      <c r="C144">
+        <v>10.9014676</v>
+      </c>
+      <c r="D144">
+        <v>106.7857237</v>
+      </c>
+      <c r="E144" t="str">
+        <v/>
+      </c>
+      <c r="F144" t="str">
+        <v/>
+      </c>
+      <c r="G144">
+        <v>2</v>
+      </c>
+      <c r="H144" t="str">
+        <v/>
+      </c>
+      <c r="I144" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J144" t="str">
+        <v/>
+      </c>
+      <c r="K144" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L144" t="str">
+        <v/>
+      </c>
+      <c r="M144" t="str">
+        <v>10:14:17 13/4/2026</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v/>
+      </c>
+      <c r="B145" t="str">
+        <v>NĐC-15</v>
+      </c>
+      <c r="C145">
+        <v>10.9014891</v>
+      </c>
+      <c r="D145">
+        <v>106.7857964</v>
+      </c>
+      <c r="E145" t="str">
+        <v/>
+      </c>
+      <c r="F145" t="str">
+        <v/>
+      </c>
+      <c r="G145">
+        <v>2</v>
+      </c>
+      <c r="H145" t="str">
+        <v/>
+      </c>
+      <c r="I145" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J145" t="str">
+        <v/>
+      </c>
+      <c r="K145" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L145" t="str">
+        <v/>
+      </c>
+      <c r="M145" t="str">
+        <v>10:14:35 13/4/2026</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v/>
+      </c>
+      <c r="B146" t="str">
+        <v>NĐC-16</v>
+      </c>
+      <c r="C146">
+        <v>10.9018521</v>
+      </c>
+      <c r="D146">
+        <v>106.7864466</v>
+      </c>
+      <c r="E146" t="str">
+        <v/>
+      </c>
+      <c r="F146" t="str">
+        <v/>
+      </c>
+      <c r="G146">
+        <v>2</v>
+      </c>
+      <c r="H146" t="str">
+        <v/>
+      </c>
+      <c r="I146" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J146" t="str">
+        <v/>
+      </c>
+      <c r="K146" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L146" t="str">
+        <v/>
+      </c>
+      <c r="M146" t="str">
+        <v>10:14:50 13/4/2026</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v/>
+      </c>
+      <c r="B147" t="str">
+        <v>NĐC-17</v>
+      </c>
+      <c r="C147">
+        <v>10.9019683</v>
+      </c>
+      <c r="D147">
+        <v>106.7866976</v>
+      </c>
+      <c r="E147" t="str">
+        <v/>
+      </c>
+      <c r="F147" t="str">
+        <v/>
+      </c>
+      <c r="G147">
+        <v>2</v>
+      </c>
+      <c r="H147" t="str">
+        <v/>
+      </c>
+      <c r="I147" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J147" t="str">
+        <v/>
+      </c>
+      <c r="K147" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L147" t="str">
+        <v/>
+      </c>
+      <c r="M147" t="str">
+        <v>10:15:08 13/4/2026</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v/>
+      </c>
+      <c r="B148" t="str">
+        <v>NĐC-18</v>
+      </c>
+      <c r="C148">
+        <v>10.9020083</v>
+      </c>
+      <c r="D148">
+        <v>106.7868692</v>
+      </c>
+      <c r="E148" t="str">
+        <v/>
+      </c>
+      <c r="F148" t="str">
+        <v/>
+      </c>
+      <c r="G148">
+        <v>2</v>
+      </c>
+      <c r="H148" t="str">
+        <v/>
+      </c>
+      <c r="I148" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J148" t="str">
+        <v/>
+      </c>
+      <c r="K148" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L148" t="str">
+        <v/>
+      </c>
+      <c r="M148" t="str">
+        <v>10:15:28 13/4/2026</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v/>
+      </c>
+      <c r="B149" t="str">
+        <v>NĐC-19</v>
+      </c>
+      <c r="C149">
+        <v>10.9020121</v>
+      </c>
+      <c r="D149">
+        <v>106.7869148</v>
+      </c>
+      <c r="E149" t="str">
+        <v/>
+      </c>
+      <c r="F149" t="str">
+        <v/>
+      </c>
+      <c r="G149">
+        <v>2</v>
+      </c>
+      <c r="H149" t="str">
+        <v/>
+      </c>
+      <c r="I149" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J149" t="str">
+        <v/>
+      </c>
+      <c r="K149" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L149" t="str">
+        <v/>
+      </c>
+      <c r="M149" t="str">
+        <v>10:15:43 13/4/2026</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v/>
+      </c>
+      <c r="B150" t="str">
+        <v>NĐC-20</v>
+      </c>
+      <c r="C150">
+        <v>10.9020246</v>
+      </c>
+      <c r="D150">
+        <v>106.7869185</v>
+      </c>
+      <c r="E150" t="str">
+        <v/>
+      </c>
+      <c r="F150" t="str">
+        <v/>
+      </c>
+      <c r="G150">
+        <v>2</v>
+      </c>
+      <c r="H150" t="str">
+        <v/>
+      </c>
+      <c r="I150" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J150" t="str">
+        <v/>
+      </c>
+      <c r="K150" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L150" t="str">
+        <v/>
+      </c>
+      <c r="M150" t="str">
+        <v>10:16:00 13/4/2026</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v/>
+      </c>
+      <c r="B151" t="str">
+        <v>NĐC-21</v>
+      </c>
+      <c r="C151">
+        <v>10.9020268</v>
+      </c>
+      <c r="D151">
+        <v>106.7869653</v>
+      </c>
+      <c r="E151" t="str">
+        <v/>
+      </c>
+      <c r="F151" t="str">
+        <v/>
+      </c>
+      <c r="G151">
+        <v>2</v>
+      </c>
+      <c r="H151" t="str">
+        <v/>
+      </c>
+      <c r="I151" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J151" t="str">
+        <v/>
+      </c>
+      <c r="K151" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L151" t="str">
+        <v/>
+      </c>
+      <c r="M151" t="str">
+        <v>10:16:17 13/4/2026</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v/>
+      </c>
+      <c r="B152" t="str">
+        <v>NĐC-22</v>
+      </c>
+      <c r="C152">
+        <v>10.9020919</v>
+      </c>
+      <c r="D152">
+        <v>106.7877141</v>
+      </c>
+      <c r="E152" t="str">
+        <v/>
+      </c>
+      <c r="F152" t="str">
+        <v/>
+      </c>
+      <c r="G152">
+        <v>2</v>
+      </c>
+      <c r="H152" t="str">
+        <v/>
+      </c>
+      <c r="I152" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J152" t="str">
+        <v/>
+      </c>
+      <c r="K152" t="str">
+        <v>HPS</v>
+      </c>
+      <c r="L152" t="str">
+        <v/>
+      </c>
+      <c r="M152" t="str">
+        <v>10:16:32 13/4/2026</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v/>
+      </c>
+      <c r="B153" t="str">
+        <v>NĐC-23</v>
+      </c>
+      <c r="C153">
+        <v>10.901698</v>
+      </c>
+      <c r="D153">
+        <v>106.7886023</v>
+      </c>
+      <c r="E153" t="str">
+        <v/>
+      </c>
+      <c r="F153" t="str">
+        <v/>
+      </c>
+      <c r="G153">
+        <v>2</v>
+      </c>
+      <c r="H153" t="str">
+        <v/>
+      </c>
+      <c r="I153" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J153" t="str">
+        <v/>
+      </c>
+      <c r="K153" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L153" t="str">
+        <v/>
+      </c>
+      <c r="M153" t="str">
+        <v>10:18:29 13/4/2026</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v/>
+      </c>
+      <c r="B154" t="str">
+        <v>NĐC-24</v>
+      </c>
+      <c r="C154">
+        <v>10.9016085</v>
+      </c>
+      <c r="D154">
+        <v>106.789027</v>
+      </c>
+      <c r="E154" t="str">
+        <v/>
+      </c>
+      <c r="F154" t="str">
+        <v/>
+      </c>
+      <c r="G154">
+        <v>2</v>
+      </c>
+      <c r="H154" t="str">
+        <v/>
+      </c>
+      <c r="I154" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J154" t="str">
+        <v/>
+      </c>
+      <c r="K154" t="str">
+        <v>LED</v>
+      </c>
+      <c r="L154" t="str">
+        <v/>
+      </c>
+      <c r="M154" t="str">
+        <v>10:18:48 13/4/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O128"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O154"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O154"/>
+  <dimension ref="A1:O159"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6449,6 +6449,12 @@
       <c r="M129" t="str">
         <v>10:07:02 13/4/2026</v>
       </c>
+      <c r="N129" t="str">
+        <v/>
+      </c>
+      <c r="O129" t="str">
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -6490,6 +6496,12 @@
       <c r="M130" t="str">
         <v>10:07:25 13/4/2026</v>
       </c>
+      <c r="N130" t="str">
+        <v/>
+      </c>
+      <c r="O130" t="str">
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -6531,6 +6543,12 @@
       <c r="M131" t="str">
         <v>10:07:49 13/4/2026</v>
       </c>
+      <c r="N131" t="str">
+        <v/>
+      </c>
+      <c r="O131" t="str">
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -6572,6 +6590,12 @@
       <c r="M132" t="str">
         <v>10:08:00 13/4/2026</v>
       </c>
+      <c r="N132" t="str">
+        <v/>
+      </c>
+      <c r="O132" t="str">
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -6613,6 +6637,12 @@
       <c r="M133" t="str">
         <v>10:08:14 13/4/2026</v>
       </c>
+      <c r="N133" t="str">
+        <v/>
+      </c>
+      <c r="O133" t="str">
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -6654,6 +6684,12 @@
       <c r="M134" t="str">
         <v>10:08:28 13/4/2026</v>
       </c>
+      <c r="N134" t="str">
+        <v/>
+      </c>
+      <c r="O134" t="str">
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -6695,6 +6731,12 @@
       <c r="M135" t="str">
         <v>10:08:48 13/4/2026</v>
       </c>
+      <c r="N135" t="str">
+        <v/>
+      </c>
+      <c r="O135" t="str">
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -6736,6 +6778,12 @@
       <c r="M136" t="str">
         <v>10:09:27 13/4/2026</v>
       </c>
+      <c r="N136" t="str">
+        <v/>
+      </c>
+      <c r="O136" t="str">
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -6777,6 +6825,12 @@
       <c r="M137" t="str">
         <v>10:10:28 13/4/2026</v>
       </c>
+      <c r="N137" t="str">
+        <v/>
+      </c>
+      <c r="O137" t="str">
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -6818,6 +6872,12 @@
       <c r="M138" t="str">
         <v>10:12:27 13/4/2026</v>
       </c>
+      <c r="N138" t="str">
+        <v/>
+      </c>
+      <c r="O138" t="str">
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -6859,6 +6919,12 @@
       <c r="M139" t="str">
         <v>10:12:46 13/4/2026</v>
       </c>
+      <c r="N139" t="str">
+        <v/>
+      </c>
+      <c r="O139" t="str">
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -6900,6 +6966,12 @@
       <c r="M140" t="str">
         <v>10:13:01 13/4/2026</v>
       </c>
+      <c r="N140" t="str">
+        <v/>
+      </c>
+      <c r="O140" t="str">
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -6941,6 +7013,12 @@
       <c r="M141" t="str">
         <v>10:13:20 13/4/2026</v>
       </c>
+      <c r="N141" t="str">
+        <v/>
+      </c>
+      <c r="O141" t="str">
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -6982,6 +7060,12 @@
       <c r="M142" t="str">
         <v>10:13:38 13/4/2026</v>
       </c>
+      <c r="N142" t="str">
+        <v/>
+      </c>
+      <c r="O142" t="str">
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
@@ -7023,6 +7107,12 @@
       <c r="M143" t="str">
         <v>10:13:57 13/4/2026</v>
       </c>
+      <c r="N143" t="str">
+        <v/>
+      </c>
+      <c r="O143" t="str">
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -7064,6 +7154,12 @@
       <c r="M144" t="str">
         <v>10:14:17 13/4/2026</v>
       </c>
+      <c r="N144" t="str">
+        <v/>
+      </c>
+      <c r="O144" t="str">
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -7105,6 +7201,12 @@
       <c r="M145" t="str">
         <v>10:14:35 13/4/2026</v>
       </c>
+      <c r="N145" t="str">
+        <v/>
+      </c>
+      <c r="O145" t="str">
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -7146,6 +7248,12 @@
       <c r="M146" t="str">
         <v>10:14:50 13/4/2026</v>
       </c>
+      <c r="N146" t="str">
+        <v/>
+      </c>
+      <c r="O146" t="str">
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
@@ -7187,6 +7295,12 @@
       <c r="M147" t="str">
         <v>10:15:08 13/4/2026</v>
       </c>
+      <c r="N147" t="str">
+        <v/>
+      </c>
+      <c r="O147" t="str">
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -7228,6 +7342,12 @@
       <c r="M148" t="str">
         <v>10:15:28 13/4/2026</v>
       </c>
+      <c r="N148" t="str">
+        <v/>
+      </c>
+      <c r="O148" t="str">
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -7269,6 +7389,12 @@
       <c r="M149" t="str">
         <v>10:15:43 13/4/2026</v>
       </c>
+      <c r="N149" t="str">
+        <v/>
+      </c>
+      <c r="O149" t="str">
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
@@ -7310,6 +7436,12 @@
       <c r="M150" t="str">
         <v>10:16:00 13/4/2026</v>
       </c>
+      <c r="N150" t="str">
+        <v/>
+      </c>
+      <c r="O150" t="str">
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
@@ -7351,6 +7483,12 @@
       <c r="M151" t="str">
         <v>10:16:17 13/4/2026</v>
       </c>
+      <c r="N151" t="str">
+        <v/>
+      </c>
+      <c r="O151" t="str">
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
@@ -7392,6 +7530,12 @@
       <c r="M152" t="str">
         <v>10:16:32 13/4/2026</v>
       </c>
+      <c r="N152" t="str">
+        <v/>
+      </c>
+      <c r="O152" t="str">
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -7433,6 +7577,12 @@
       <c r="M153" t="str">
         <v>10:18:29 13/4/2026</v>
       </c>
+      <c r="N153" t="str">
+        <v/>
+      </c>
+      <c r="O153" t="str">
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -7474,10 +7624,251 @@
       <c r="M154" t="str">
         <v>10:18:48 13/4/2026</v>
       </c>
+      <c r="N154" t="str">
+        <v/>
+      </c>
+      <c r="O154" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v/>
+      </c>
+      <c r="B155" t="str">
+        <v>T1</v>
+      </c>
+      <c r="C155">
+        <v>10.734346984855224</v>
+      </c>
+      <c r="D155">
+        <v>106.64088338613512</v>
+      </c>
+      <c r="E155" t="str">
+        <v/>
+      </c>
+      <c r="F155" t="str">
+        <v/>
+      </c>
+      <c r="G155">
+        <v>1</v>
+      </c>
+      <c r="H155" t="str">
+        <v/>
+      </c>
+      <c r="I155" t="str">
+        <v/>
+      </c>
+      <c r="J155" t="str">
+        <v/>
+      </c>
+      <c r="K155" t="str">
+        <v/>
+      </c>
+      <c r="L155" t="str">
+        <v/>
+      </c>
+      <c r="M155" t="str">
+        <v>11:02:36 15/4/2026</v>
+      </c>
+      <c r="N155" t="str">
+        <v/>
+      </c>
+      <c r="O155" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v/>
+      </c>
+      <c r="B156" t="str">
+        <v>T2</v>
+      </c>
+      <c r="C156">
+        <v>10.7341242</v>
+      </c>
+      <c r="D156">
+        <v>106.6409775</v>
+      </c>
+      <c r="E156" t="str">
+        <v/>
+      </c>
+      <c r="F156" t="str">
+        <v/>
+      </c>
+      <c r="G156">
+        <v>1</v>
+      </c>
+      <c r="H156" t="str">
+        <v/>
+      </c>
+      <c r="I156" t="str">
+        <v/>
+      </c>
+      <c r="J156" t="str">
+        <v/>
+      </c>
+      <c r="K156" t="str">
+        <v/>
+      </c>
+      <c r="L156" t="str">
+        <v/>
+      </c>
+      <c r="M156" t="str">
+        <v>11:02:54 15/4/2026</v>
+      </c>
+      <c r="N156" t="str">
+        <v>T1</v>
+      </c>
+      <c r="O156">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v/>
+      </c>
+      <c r="B157" t="str">
+        <v>T3</v>
+      </c>
+      <c r="C157">
+        <v>10.7339148581693</v>
+      </c>
+      <c r="D157">
+        <v>106.64117574691774</v>
+      </c>
+      <c r="E157" t="str">
+        <v/>
+      </c>
+      <c r="F157" t="str">
+        <v/>
+      </c>
+      <c r="G157">
+        <v>1</v>
+      </c>
+      <c r="H157" t="str">
+        <v/>
+      </c>
+      <c r="I157" t="str">
+        <v/>
+      </c>
+      <c r="J157" t="str">
+        <v/>
+      </c>
+      <c r="K157" t="str">
+        <v/>
+      </c>
+      <c r="L157" t="str">
+        <v/>
+      </c>
+      <c r="M157" t="str">
+        <v>11:06:55 15/4/2026</v>
+      </c>
+      <c r="N157" t="str">
+        <v>T2</v>
+      </c>
+      <c r="O157">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v/>
+      </c>
+      <c r="B158" t="str">
+        <v>B1</v>
+      </c>
+      <c r="C158">
+        <v>10.733852390755871</v>
+      </c>
+      <c r="D158">
+        <v>106.64058722554275</v>
+      </c>
+      <c r="E158" t="str">
+        <v/>
+      </c>
+      <c r="F158" t="str">
+        <v/>
+      </c>
+      <c r="G158">
+        <v>1</v>
+      </c>
+      <c r="H158" t="str">
+        <v/>
+      </c>
+      <c r="I158" t="str">
+        <v/>
+      </c>
+      <c r="J158" t="str">
+        <v/>
+      </c>
+      <c r="K158" t="str">
+        <v/>
+      </c>
+      <c r="L158" t="str">
+        <v/>
+      </c>
+      <c r="M158" t="str">
+        <v>11:07:53 15/4/2026</v>
+      </c>
+      <c r="N158" t="str">
+        <v/>
+      </c>
+      <c r="O158" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v/>
+      </c>
+      <c r="B159" t="str">
+        <v>B2</v>
+      </c>
+      <c r="C159">
+        <v>10.7338</v>
+      </c>
+      <c r="D159">
+        <v>106.6411133</v>
+      </c>
+      <c r="E159" t="str">
+        <v/>
+      </c>
+      <c r="F159" t="str">
+        <v/>
+      </c>
+      <c r="G159">
+        <v>1</v>
+      </c>
+      <c r="H159" t="str">
+        <v/>
+      </c>
+      <c r="I159" t="str">
+        <v/>
+      </c>
+      <c r="J159" t="str">
+        <v/>
+      </c>
+      <c r="K159" t="str">
+        <v/>
+      </c>
+      <c r="L159" t="str">
+        <v/>
+      </c>
+      <c r="M159" t="str">
+        <v>11:09:39 15/4/2026</v>
+      </c>
+      <c r="N159" t="str">
+        <v>B1</v>
+      </c>
+      <c r="O159">
+        <v>58</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O154"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O159"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O159"/>
+  <dimension ref="A1:O161"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7866,9 +7866,103 @@
         <v>58</v>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v/>
+      </c>
+      <c r="B160" t="str">
+        <v>t1</v>
+      </c>
+      <c r="C160">
+        <v>10.826688279850183</v>
+      </c>
+      <c r="D160">
+        <v>106.68615102767946</v>
+      </c>
+      <c r="E160" t="str">
+        <v/>
+      </c>
+      <c r="F160" t="str">
+        <v/>
+      </c>
+      <c r="G160">
+        <v>1</v>
+      </c>
+      <c r="H160" t="str">
+        <v/>
+      </c>
+      <c r="I160" t="str">
+        <v/>
+      </c>
+      <c r="J160" t="str">
+        <v/>
+      </c>
+      <c r="K160" t="str">
+        <v/>
+      </c>
+      <c r="L160" t="str">
+        <v/>
+      </c>
+      <c r="M160" t="str">
+        <v>21:26:39 23/4/2026</v>
+      </c>
+      <c r="N160" t="str">
+        <v>T3</v>
+      </c>
+      <c r="O160">
+        <v>11426</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v/>
+      </c>
+      <c r="B161" t="str">
+        <v>t2</v>
+      </c>
+      <c r="C161">
+        <v>10.760187010447785</v>
+      </c>
+      <c r="D161">
+        <v>106.6135221719742</v>
+      </c>
+      <c r="E161" t="str">
+        <v/>
+      </c>
+      <c r="F161" t="str">
+        <v/>
+      </c>
+      <c r="G161">
+        <v>1</v>
+      </c>
+      <c r="H161" t="str">
+        <v/>
+      </c>
+      <c r="I161" t="str">
+        <v/>
+      </c>
+      <c r="J161" t="str">
+        <v/>
+      </c>
+      <c r="K161" t="str">
+        <v/>
+      </c>
+      <c r="L161" t="str">
+        <v/>
+      </c>
+      <c r="M161" t="str">
+        <v>21:26:59 23/4/2026</v>
+      </c>
+      <c r="N161" t="str">
+        <v>t1</v>
+      </c>
+      <c r="O161">
+        <v>10845</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O159"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O161"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O161"/>
+  <dimension ref="A1:O162"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7960,9 +7960,56 @@
         <v>10845</v>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v/>
+      </c>
+      <c r="B162" t="str">
+        <v>t1</v>
+      </c>
+      <c r="C162">
+        <v>10.760213705654916</v>
+      </c>
+      <c r="D162">
+        <v>106.61354710952482</v>
+      </c>
+      <c r="E162" t="str">
+        <v/>
+      </c>
+      <c r="F162" t="str">
+        <v/>
+      </c>
+      <c r="G162">
+        <v>1</v>
+      </c>
+      <c r="H162" t="str">
+        <v/>
+      </c>
+      <c r="I162" t="str">
+        <v/>
+      </c>
+      <c r="J162" t="str">
+        <v/>
+      </c>
+      <c r="K162" t="str">
+        <v/>
+      </c>
+      <c r="L162" t="str">
+        <v/>
+      </c>
+      <c r="M162" t="str">
+        <v>21:32:07 23/4/2026</v>
+      </c>
+      <c r="N162" t="str">
+        <v>T3</v>
+      </c>
+      <c r="O162">
+        <v>4203</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O161"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O162"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O162"/>
+  <dimension ref="A1:O163"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8007,9 +8007,56 @@
         <v>4203</v>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v/>
+      </c>
+      <c r="B163" t="str">
+        <v>sdafsad</v>
+      </c>
+      <c r="C163">
+        <v>11.03758152522604</v>
+      </c>
+      <c r="D163">
+        <v>106.49734497070314</v>
+      </c>
+      <c r="E163" t="str">
+        <v/>
+      </c>
+      <c r="F163" t="str">
+        <v/>
+      </c>
+      <c r="G163">
+        <v>1</v>
+      </c>
+      <c r="H163" t="str">
+        <v/>
+      </c>
+      <c r="I163" t="str">
+        <v/>
+      </c>
+      <c r="J163" t="str">
+        <v/>
+      </c>
+      <c r="K163" t="str">
+        <v/>
+      </c>
+      <c r="L163" t="str">
+        <v/>
+      </c>
+      <c r="M163" t="str">
+        <v>21:55:40 23/4/2026</v>
+      </c>
+      <c r="N163" t="str">
+        <v/>
+      </c>
+      <c r="O163" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O162"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O163"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O163"/>
+  <dimension ref="A1:O164"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8054,9 +8054,56 @@
         <v/>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v/>
+      </c>
+      <c r="B164" t="str">
+        <v>My home</v>
+      </c>
+      <c r="C164">
+        <v>10.76024525</v>
+      </c>
+      <c r="D164">
+        <v>106.6134465</v>
+      </c>
+      <c r="E164" t="str">
+        <v/>
+      </c>
+      <c r="F164" t="str">
+        <v/>
+      </c>
+      <c r="G164">
+        <v>1</v>
+      </c>
+      <c r="H164" t="str">
+        <v/>
+      </c>
+      <c r="I164" t="str">
+        <v/>
+      </c>
+      <c r="J164" t="str">
+        <v/>
+      </c>
+      <c r="K164" t="str">
+        <v/>
+      </c>
+      <c r="L164" t="str">
+        <v/>
+      </c>
+      <c r="M164" t="str">
+        <v>21:58:13 23/4/2026</v>
+      </c>
+      <c r="N164" t="str">
+        <v/>
+      </c>
+      <c r="O164" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O163"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O164"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O164"/>
+  <dimension ref="A1:O204"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8101,9 +8101,1889 @@
         <v/>
       </c>
     </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v/>
+      </c>
+      <c r="B165" t="str">
+        <v>Trụ sở 1</v>
+      </c>
+      <c r="C165">
+        <v>10.73418806484744</v>
+      </c>
+      <c r="D165">
+        <v>106.64022535085681</v>
+      </c>
+      <c r="E165" t="str">
+        <v/>
+      </c>
+      <c r="F165" t="str">
+        <v/>
+      </c>
+      <c r="G165">
+        <v>1</v>
+      </c>
+      <c r="H165" t="str">
+        <v/>
+      </c>
+      <c r="I165" t="str">
+        <v/>
+      </c>
+      <c r="J165" t="str">
+        <v/>
+      </c>
+      <c r="K165" t="str">
+        <v/>
+      </c>
+      <c r="L165" t="str">
+        <v/>
+      </c>
+      <c r="M165" t="str">
+        <v>07:05:51 24/4/2026</v>
+      </c>
+      <c r="N165" t="str">
+        <v/>
+      </c>
+      <c r="O165" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v/>
+      </c>
+      <c r="B166" t="str">
+        <v>Trụ sở 2</v>
+      </c>
+      <c r="C166">
+        <v>10.734042684602663</v>
+      </c>
+      <c r="D166">
+        <v>106.64034157991411</v>
+      </c>
+      <c r="E166" t="str">
+        <v/>
+      </c>
+      <c r="F166" t="str">
+        <v/>
+      </c>
+      <c r="G166">
+        <v>1</v>
+      </c>
+      <c r="H166" t="str">
+        <v/>
+      </c>
+      <c r="I166" t="str">
+        <v/>
+      </c>
+      <c r="J166" t="str">
+        <v/>
+      </c>
+      <c r="K166" t="str">
+        <v/>
+      </c>
+      <c r="L166" t="str">
+        <v/>
+      </c>
+      <c r="M166" t="str">
+        <v>07:06:15 24/4/2026</v>
+      </c>
+      <c r="N166" t="str">
+        <v>Trụ sở 1</v>
+      </c>
+      <c r="O166">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v/>
+      </c>
+      <c r="B167" t="str">
+        <v>Trụ sở 3</v>
+      </c>
+      <c r="C167">
+        <v>10.733834568648254</v>
+      </c>
+      <c r="D167">
+        <v>106.64046707457399</v>
+      </c>
+      <c r="E167" t="str">
+        <v/>
+      </c>
+      <c r="F167" t="str">
+        <v/>
+      </c>
+      <c r="G167">
+        <v>1</v>
+      </c>
+      <c r="H167" t="str">
+        <v/>
+      </c>
+      <c r="I167" t="str">
+        <v/>
+      </c>
+      <c r="J167" t="str">
+        <v/>
+      </c>
+      <c r="K167" t="str">
+        <v/>
+      </c>
+      <c r="L167" t="str">
+        <v/>
+      </c>
+      <c r="M167" t="str">
+        <v>07:07:45 24/4/2026</v>
+      </c>
+      <c r="N167" t="str">
+        <v>Trụ sở 2</v>
+      </c>
+      <c r="O167">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v/>
+      </c>
+      <c r="B168" t="str">
+        <v>Trụ sở 4</v>
+      </c>
+      <c r="C168">
+        <v>10.733634722156264</v>
+      </c>
+      <c r="D168">
+        <v>106.64062447161123</v>
+      </c>
+      <c r="E168" t="str">
+        <v/>
+      </c>
+      <c r="F168" t="str">
+        <v/>
+      </c>
+      <c r="G168">
+        <v>1</v>
+      </c>
+      <c r="H168" t="str">
+        <v/>
+      </c>
+      <c r="I168" t="str">
+        <v/>
+      </c>
+      <c r="J168" t="str">
+        <v/>
+      </c>
+      <c r="K168" t="str">
+        <v/>
+      </c>
+      <c r="L168" t="str">
+        <v/>
+      </c>
+      <c r="M168" t="str">
+        <v>07:08:08 24/4/2026</v>
+      </c>
+      <c r="N168" t="str">
+        <v>Trụ sở 3</v>
+      </c>
+      <c r="O168">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v/>
+      </c>
+      <c r="B169" t="str">
+        <v>Trụ sở 5</v>
+      </c>
+      <c r="C169">
+        <v>10.73339914508806</v>
+      </c>
+      <c r="D169">
+        <v>106.64076640558676</v>
+      </c>
+      <c r="E169" t="str">
+        <v/>
+      </c>
+      <c r="F169" t="str">
+        <v/>
+      </c>
+      <c r="G169">
+        <v>1</v>
+      </c>
+      <c r="H169" t="str">
+        <v/>
+      </c>
+      <c r="I169" t="str">
+        <v/>
+      </c>
+      <c r="J169" t="str">
+        <v/>
+      </c>
+      <c r="K169" t="str">
+        <v/>
+      </c>
+      <c r="L169" t="str">
+        <v/>
+      </c>
+      <c r="M169" t="str">
+        <v>07:08:28 24/4/2026</v>
+      </c>
+      <c r="N169" t="str">
+        <v>Trụ sở 4</v>
+      </c>
+      <c r="O169">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v/>
+      </c>
+      <c r="B170" t="str">
+        <v>Trụ sở 6</v>
+      </c>
+      <c r="C170">
+        <v>10.733293827023235</v>
+      </c>
+      <c r="D170">
+        <v>106.64069697260857</v>
+      </c>
+      <c r="E170" t="str">
+        <v/>
+      </c>
+      <c r="F170" t="str">
+        <v/>
+      </c>
+      <c r="G170">
+        <v>1</v>
+      </c>
+      <c r="H170" t="str">
+        <v/>
+      </c>
+      <c r="I170" t="str">
+        <v/>
+      </c>
+      <c r="J170" t="str">
+        <v/>
+      </c>
+      <c r="K170" t="str">
+        <v/>
+      </c>
+      <c r="L170" t="str">
+        <v/>
+      </c>
+      <c r="M170" t="str">
+        <v>07:08:47 24/4/2026</v>
+      </c>
+      <c r="N170" t="str">
+        <v>Trụ sở 5</v>
+      </c>
+      <c r="O170">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v/>
+      </c>
+      <c r="B171" t="str">
+        <v>Trụ sở 7</v>
+      </c>
+      <c r="C171">
+        <v>10.732862919066434</v>
+      </c>
+      <c r="D171">
+        <v>106.64114482645647</v>
+      </c>
+      <c r="E171" t="str">
+        <v/>
+      </c>
+      <c r="F171" t="str">
+        <v/>
+      </c>
+      <c r="G171">
+        <v>1</v>
+      </c>
+      <c r="H171" t="str">
+        <v/>
+      </c>
+      <c r="I171" t="str">
+        <v/>
+      </c>
+      <c r="J171" t="str">
+        <v/>
+      </c>
+      <c r="K171" t="str">
+        <v/>
+      </c>
+      <c r="L171" t="str">
+        <v/>
+      </c>
+      <c r="M171" t="str">
+        <v>07:10:01 24/4/2026</v>
+      </c>
+      <c r="N171" t="str">
+        <v>Trụ sở 6</v>
+      </c>
+      <c r="O171">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v/>
+      </c>
+      <c r="B172" t="str">
+        <v>Trụ sở 8</v>
+      </c>
+      <c r="C172">
+        <v>10.733140540400864</v>
+      </c>
+      <c r="D172">
+        <v>106.64050340652466</v>
+      </c>
+      <c r="E172" t="str">
+        <v/>
+      </c>
+      <c r="F172" t="str">
+        <v/>
+      </c>
+      <c r="G172">
+        <v>1</v>
+      </c>
+      <c r="H172" t="str">
+        <v/>
+      </c>
+      <c r="I172" t="str">
+        <v/>
+      </c>
+      <c r="J172" t="str">
+        <v/>
+      </c>
+      <c r="K172" t="str">
+        <v/>
+      </c>
+      <c r="L172" t="str">
+        <v/>
+      </c>
+      <c r="M172" t="str">
+        <v>07:10:23 24/4/2026</v>
+      </c>
+      <c r="N172" t="str">
+        <v>Trụ sở 7</v>
+      </c>
+      <c r="O172">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v/>
+      </c>
+      <c r="B173" t="str">
+        <v>Trụ sở 9</v>
+      </c>
+      <c r="C173">
+        <v>10.733003944943965</v>
+      </c>
+      <c r="D173">
+        <v>106.64032727479938</v>
+      </c>
+      <c r="E173" t="str">
+        <v/>
+      </c>
+      <c r="F173" t="str">
+        <v/>
+      </c>
+      <c r="G173">
+        <v>1</v>
+      </c>
+      <c r="H173" t="str">
+        <v/>
+      </c>
+      <c r="I173" t="str">
+        <v/>
+      </c>
+      <c r="J173" t="str">
+        <v/>
+      </c>
+      <c r="K173" t="str">
+        <v/>
+      </c>
+      <c r="L173" t="str">
+        <v/>
+      </c>
+      <c r="M173" t="str">
+        <v>07:11:31 24/4/2026</v>
+      </c>
+      <c r="N173" t="str">
+        <v>Trụ sở 8</v>
+      </c>
+      <c r="O173">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v/>
+      </c>
+      <c r="B174" t="str">
+        <v>Trụ sở 10</v>
+      </c>
+      <c r="C174">
+        <v>10.732949043363861</v>
+      </c>
+      <c r="D174">
+        <v>106.64026737213135</v>
+      </c>
+      <c r="E174" t="str">
+        <v/>
+      </c>
+      <c r="F174" t="str">
+        <v/>
+      </c>
+      <c r="G174">
+        <v>1</v>
+      </c>
+      <c r="H174" t="str">
+        <v/>
+      </c>
+      <c r="I174" t="str">
+        <v/>
+      </c>
+      <c r="J174" t="str">
+        <v/>
+      </c>
+      <c r="K174" t="str">
+        <v/>
+      </c>
+      <c r="L174" t="str">
+        <v/>
+      </c>
+      <c r="M174" t="str">
+        <v>07:12:24 24/4/2026</v>
+      </c>
+      <c r="N174" t="str">
+        <v>Trụ sở 9</v>
+      </c>
+      <c r="O174">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v/>
+      </c>
+      <c r="B175" t="str">
+        <v>Trụ sở 11</v>
+      </c>
+      <c r="C175">
+        <v>10.732791803811988</v>
+      </c>
+      <c r="D175">
+        <v>106.64008157625214</v>
+      </c>
+      <c r="E175" t="str">
+        <v/>
+      </c>
+      <c r="F175" t="str">
+        <v/>
+      </c>
+      <c r="G175">
+        <v>1</v>
+      </c>
+      <c r="H175" t="str">
+        <v/>
+      </c>
+      <c r="I175" t="str">
+        <v/>
+      </c>
+      <c r="J175" t="str">
+        <v/>
+      </c>
+      <c r="K175" t="str">
+        <v/>
+      </c>
+      <c r="L175" t="str">
+        <v/>
+      </c>
+      <c r="M175" t="str">
+        <v>07:13:41 24/4/2026</v>
+      </c>
+      <c r="N175" t="str">
+        <v>Trụ sở 10</v>
+      </c>
+      <c r="O175">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v/>
+      </c>
+      <c r="B176" t="str">
+        <v>Trụ sở 12</v>
+      </c>
+      <c r="C176">
+        <v>10.732578233513125</v>
+      </c>
+      <c r="D176">
+        <v>106.63981164058531</v>
+      </c>
+      <c r="E176" t="str">
+        <v/>
+      </c>
+      <c r="F176" t="str">
+        <v/>
+      </c>
+      <c r="G176">
+        <v>1</v>
+      </c>
+      <c r="H176" t="str">
+        <v/>
+      </c>
+      <c r="I176" t="str">
+        <v/>
+      </c>
+      <c r="J176" t="str">
+        <v/>
+      </c>
+      <c r="K176" t="str">
+        <v/>
+      </c>
+      <c r="L176" t="str">
+        <v/>
+      </c>
+      <c r="M176" t="str">
+        <v>07:13:57 24/4/2026</v>
+      </c>
+      <c r="N176" t="str">
+        <v>Trụ sở 11</v>
+      </c>
+      <c r="O176">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v/>
+      </c>
+      <c r="B177" t="str">
+        <v>Trụ sở 13</v>
+      </c>
+      <c r="C177">
+        <v>10.732407052648785</v>
+      </c>
+      <c r="D177">
+        <v>106.63955390453339</v>
+      </c>
+      <c r="E177" t="str">
+        <v/>
+      </c>
+      <c r="F177" t="str">
+        <v/>
+      </c>
+      <c r="G177">
+        <v>1</v>
+      </c>
+      <c r="H177" t="str">
+        <v/>
+      </c>
+      <c r="I177" t="str">
+        <v/>
+      </c>
+      <c r="J177" t="str">
+        <v/>
+      </c>
+      <c r="K177" t="str">
+        <v/>
+      </c>
+      <c r="L177" t="str">
+        <v/>
+      </c>
+      <c r="M177" t="str">
+        <v>07:14:14 24/4/2026</v>
+      </c>
+      <c r="N177" t="str">
+        <v>Trụ sở 12</v>
+      </c>
+      <c r="O177">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v/>
+      </c>
+      <c r="B178" t="str">
+        <v>Trụ sở 14</v>
+      </c>
+      <c r="C178">
+        <v>10.732147692696113</v>
+      </c>
+      <c r="D178">
+        <v>106.63926414233413</v>
+      </c>
+      <c r="E178" t="str">
+        <v/>
+      </c>
+      <c r="F178" t="str">
+        <v/>
+      </c>
+      <c r="G178">
+        <v>1</v>
+      </c>
+      <c r="H178" t="str">
+        <v/>
+      </c>
+      <c r="I178" t="str">
+        <v/>
+      </c>
+      <c r="J178" t="str">
+        <v/>
+      </c>
+      <c r="K178" t="str">
+        <v/>
+      </c>
+      <c r="L178" t="str">
+        <v/>
+      </c>
+      <c r="M178" t="str">
+        <v>07:15:16 24/4/2026</v>
+      </c>
+      <c r="N178" t="str">
+        <v>Trụ sở 13</v>
+      </c>
+      <c r="O178">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v/>
+      </c>
+      <c r="B179" t="str">
+        <v>Trụ sở 15</v>
+      </c>
+      <c r="C179">
+        <v>10.732079921603217</v>
+      </c>
+      <c r="D179">
+        <v>106.63918670205805</v>
+      </c>
+      <c r="E179" t="str">
+        <v/>
+      </c>
+      <c r="F179" t="str">
+        <v/>
+      </c>
+      <c r="G179">
+        <v>6</v>
+      </c>
+      <c r="H179" t="str">
+        <v>Lưu hữu Phước 3</v>
+      </c>
+      <c r="I179" t="str">
+        <v/>
+      </c>
+      <c r="J179" t="str">
+        <v/>
+      </c>
+      <c r="K179" t="str">
+        <v/>
+      </c>
+      <c r="L179" t="str">
+        <v/>
+      </c>
+      <c r="M179" t="str">
+        <v>07:15:48 24/4/2026</v>
+      </c>
+      <c r="N179" t="str">
+        <v>Trụ sở 14</v>
+      </c>
+      <c r="O179">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v/>
+      </c>
+      <c r="B180" t="str">
+        <v>Lhp3 4</v>
+      </c>
+      <c r="C180">
+        <v>10.731900660805241</v>
+      </c>
+      <c r="D180">
+        <v>106.63896634770524</v>
+      </c>
+      <c r="E180" t="str">
+        <v/>
+      </c>
+      <c r="F180" t="str">
+        <v/>
+      </c>
+      <c r="G180">
+        <v>1</v>
+      </c>
+      <c r="H180" t="str">
+        <v/>
+      </c>
+      <c r="I180" t="str">
+        <v/>
+      </c>
+      <c r="J180" t="str">
+        <v/>
+      </c>
+      <c r="K180" t="str">
+        <v/>
+      </c>
+      <c r="L180" t="str">
+        <v/>
+      </c>
+      <c r="M180" t="str">
+        <v>07:16:52 24/4/2026</v>
+      </c>
+      <c r="N180" t="str">
+        <v/>
+      </c>
+      <c r="O180" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v/>
+      </c>
+      <c r="B181" t="str">
+        <v>Lhp3 5</v>
+      </c>
+      <c r="C181">
+        <v>10.73157975661064</v>
+      </c>
+      <c r="D181">
+        <v>106.63867265821465</v>
+      </c>
+      <c r="E181" t="str">
+        <v/>
+      </c>
+      <c r="F181" t="str">
+        <v/>
+      </c>
+      <c r="G181">
+        <v>1</v>
+      </c>
+      <c r="H181" t="str">
+        <v/>
+      </c>
+      <c r="I181" t="str">
+        <v/>
+      </c>
+      <c r="J181" t="str">
+        <v/>
+      </c>
+      <c r="K181" t="str">
+        <v/>
+      </c>
+      <c r="L181" t="str">
+        <v/>
+      </c>
+      <c r="M181" t="str">
+        <v>07:17:20 24/4/2026</v>
+      </c>
+      <c r="N181" t="str">
+        <v>Lhp3 4</v>
+      </c>
+      <c r="O181">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v/>
+      </c>
+      <c r="B182" t="str">
+        <v>Lhp3 6</v>
+      </c>
+      <c r="C182">
+        <v>10.731262173477234</v>
+      </c>
+      <c r="D182">
+        <v>106.63841669302035</v>
+      </c>
+      <c r="E182" t="str">
+        <v/>
+      </c>
+      <c r="F182" t="str">
+        <v/>
+      </c>
+      <c r="G182">
+        <v>1</v>
+      </c>
+      <c r="H182" t="str">
+        <v/>
+      </c>
+      <c r="I182" t="str">
+        <v/>
+      </c>
+      <c r="J182" t="str">
+        <v/>
+      </c>
+      <c r="K182" t="str">
+        <v/>
+      </c>
+      <c r="L182" t="str">
+        <v/>
+      </c>
+      <c r="M182" t="str">
+        <v>07:17:42 24/4/2026</v>
+      </c>
+      <c r="N182" t="str">
+        <v>Lhp3 5</v>
+      </c>
+      <c r="O182">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v/>
+      </c>
+      <c r="B183" t="str">
+        <v>Lhp3 7</v>
+      </c>
+      <c r="C183">
+        <v>10.731036034471483</v>
+      </c>
+      <c r="D183">
+        <v>106.63823499224384</v>
+      </c>
+      <c r="E183" t="str">
+        <v/>
+      </c>
+      <c r="F183" t="str">
+        <v/>
+      </c>
+      <c r="G183">
+        <v>1</v>
+      </c>
+      <c r="H183" t="str">
+        <v/>
+      </c>
+      <c r="I183" t="str">
+        <v/>
+      </c>
+      <c r="J183" t="str">
+        <v/>
+      </c>
+      <c r="K183" t="str">
+        <v/>
+      </c>
+      <c r="L183" t="str">
+        <v/>
+      </c>
+      <c r="M183" t="str">
+        <v>07:18:03 24/4/2026</v>
+      </c>
+      <c r="N183" t="str">
+        <v>Lhp3 6</v>
+      </c>
+      <c r="O183">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v/>
+      </c>
+      <c r="B184" t="str">
+        <v>Lhp3 8</v>
+      </c>
+      <c r="C184">
+        <v>10.730776469268562</v>
+      </c>
+      <c r="D184">
+        <v>106.63802605324184</v>
+      </c>
+      <c r="E184" t="str">
+        <v/>
+      </c>
+      <c r="F184" t="str">
+        <v/>
+      </c>
+      <c r="G184">
+        <v>1</v>
+      </c>
+      <c r="H184" t="str">
+        <v/>
+      </c>
+      <c r="I184" t="str">
+        <v/>
+      </c>
+      <c r="J184" t="str">
+        <v/>
+      </c>
+      <c r="K184" t="str">
+        <v/>
+      </c>
+      <c r="L184" t="str">
+        <v/>
+      </c>
+      <c r="M184" t="str">
+        <v>07:18:21 24/4/2026</v>
+      </c>
+      <c r="N184" t="str">
+        <v>Lhp3 7</v>
+      </c>
+      <c r="O184">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v/>
+      </c>
+      <c r="B185" t="str">
+        <v>Lhp3 9</v>
+      </c>
+      <c r="C185">
+        <v>10.730565083599975</v>
+      </c>
+      <c r="D185">
+        <v>106.63786451401099</v>
+      </c>
+      <c r="E185" t="str">
+        <v/>
+      </c>
+      <c r="F185" t="str">
+        <v/>
+      </c>
+      <c r="G185">
+        <v>1</v>
+      </c>
+      <c r="H185" t="str">
+        <v/>
+      </c>
+      <c r="I185" t="str">
+        <v/>
+      </c>
+      <c r="J185" t="str">
+        <v/>
+      </c>
+      <c r="K185" t="str">
+        <v/>
+      </c>
+      <c r="L185" t="str">
+        <v/>
+      </c>
+      <c r="M185" t="str">
+        <v>07:18:40 24/4/2026</v>
+      </c>
+      <c r="N185" t="str">
+        <v>Lhp3 8</v>
+      </c>
+      <c r="O185">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v/>
+      </c>
+      <c r="B186" t="str">
+        <v>Lhp3 10</v>
+      </c>
+      <c r="C186">
+        <v>10.730233206245876</v>
+      </c>
+      <c r="D186">
+        <v>106.63760907798991</v>
+      </c>
+      <c r="E186" t="str">
+        <v/>
+      </c>
+      <c r="F186" t="str">
+        <v/>
+      </c>
+      <c r="G186">
+        <v>1</v>
+      </c>
+      <c r="H186" t="str">
+        <v/>
+      </c>
+      <c r="I186" t="str">
+        <v/>
+      </c>
+      <c r="J186" t="str">
+        <v/>
+      </c>
+      <c r="K186" t="str">
+        <v/>
+      </c>
+      <c r="L186" t="str">
+        <v/>
+      </c>
+      <c r="M186" t="str">
+        <v>07:19:01 24/4/2026</v>
+      </c>
+      <c r="N186" t="str">
+        <v>Lhp3 9</v>
+      </c>
+      <c r="O186">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v/>
+      </c>
+      <c r="B187" t="str">
+        <v>Lhp3 11</v>
+      </c>
+      <c r="C187">
+        <v>10.729968166746497</v>
+      </c>
+      <c r="D187">
+        <v>106.63741683541531</v>
+      </c>
+      <c r="E187" t="str">
+        <v/>
+      </c>
+      <c r="F187" t="str">
+        <v/>
+      </c>
+      <c r="G187">
+        <v>1</v>
+      </c>
+      <c r="H187" t="str">
+        <v/>
+      </c>
+      <c r="I187" t="str">
+        <v/>
+      </c>
+      <c r="J187" t="str">
+        <v/>
+      </c>
+      <c r="K187" t="str">
+        <v/>
+      </c>
+      <c r="L187" t="str">
+        <v/>
+      </c>
+      <c r="M187" t="str">
+        <v>07:19:24 24/4/2026</v>
+      </c>
+      <c r="N187" t="str">
+        <v>Lhp3 10</v>
+      </c>
+      <c r="O187">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v/>
+      </c>
+      <c r="B188" t="str">
+        <v>Lhp3 12</v>
+      </c>
+      <c r="C188">
+        <v>10.729749335254786</v>
+      </c>
+      <c r="D188">
+        <v>106.63725344191897</v>
+      </c>
+      <c r="E188" t="str">
+        <v/>
+      </c>
+      <c r="F188" t="str">
+        <v/>
+      </c>
+      <c r="G188">
+        <v>1</v>
+      </c>
+      <c r="H188" t="str">
+        <v/>
+      </c>
+      <c r="I188" t="str">
+        <v/>
+      </c>
+      <c r="J188" t="str">
+        <v/>
+      </c>
+      <c r="K188" t="str">
+        <v/>
+      </c>
+      <c r="L188" t="str">
+        <v/>
+      </c>
+      <c r="M188" t="str">
+        <v>07:19:39 24/4/2026</v>
+      </c>
+      <c r="N188" t="str">
+        <v>Lhp3 11</v>
+      </c>
+      <c r="O188">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v/>
+      </c>
+      <c r="B189" t="str">
+        <v>Lhp3 13</v>
+      </c>
+      <c r="C189">
+        <v>10.7294986606813</v>
+      </c>
+      <c r="D189">
+        <v>106.63706020351471</v>
+      </c>
+      <c r="E189" t="str">
+        <v/>
+      </c>
+      <c r="F189" t="str">
+        <v/>
+      </c>
+      <c r="G189">
+        <v>1</v>
+      </c>
+      <c r="H189" t="str">
+        <v/>
+      </c>
+      <c r="I189" t="str">
+        <v/>
+      </c>
+      <c r="J189" t="str">
+        <v/>
+      </c>
+      <c r="K189" t="str">
+        <v/>
+      </c>
+      <c r="L189" t="str">
+        <v/>
+      </c>
+      <c r="M189" t="str">
+        <v>07:19:56 24/4/2026</v>
+      </c>
+      <c r="N189" t="str">
+        <v>Lhp3 12</v>
+      </c>
+      <c r="O189">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v/>
+      </c>
+      <c r="B190" t="str">
+        <v>Lhp3 14</v>
+      </c>
+      <c r="C190">
+        <v>10.72922425821812</v>
+      </c>
+      <c r="D190">
+        <v>106.63689456558379</v>
+      </c>
+      <c r="E190" t="str">
+        <v/>
+      </c>
+      <c r="F190" t="str">
+        <v/>
+      </c>
+      <c r="G190">
+        <v>1</v>
+      </c>
+      <c r="H190" t="str">
+        <v/>
+      </c>
+      <c r="I190" t="str">
+        <v/>
+      </c>
+      <c r="J190" t="str">
+        <v/>
+      </c>
+      <c r="K190" t="str">
+        <v/>
+      </c>
+      <c r="L190" t="str">
+        <v/>
+      </c>
+      <c r="M190" t="str">
+        <v>07:20:11 24/4/2026</v>
+      </c>
+      <c r="N190" t="str">
+        <v>Lhp3 13</v>
+      </c>
+      <c r="O190">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v/>
+      </c>
+      <c r="B191" t="str">
+        <v>Lhp4 1</v>
+      </c>
+      <c r="C191">
+        <v>10.728956569074574</v>
+      </c>
+      <c r="D191">
+        <v>106.63671815046261</v>
+      </c>
+      <c r="E191" t="str">
+        <v/>
+      </c>
+      <c r="F191" t="str">
+        <v/>
+      </c>
+      <c r="G191">
+        <v>1</v>
+      </c>
+      <c r="H191" t="str">
+        <v/>
+      </c>
+      <c r="I191" t="str">
+        <v/>
+      </c>
+      <c r="J191" t="str">
+        <v/>
+      </c>
+      <c r="K191" t="str">
+        <v/>
+      </c>
+      <c r="L191" t="str">
+        <v/>
+      </c>
+      <c r="M191" t="str">
+        <v>07:20:41 24/4/2026</v>
+      </c>
+      <c r="N191" t="str">
+        <v/>
+      </c>
+      <c r="O191" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v/>
+      </c>
+      <c r="B192" t="str">
+        <v>Lhp4 2</v>
+      </c>
+      <c r="C192">
+        <v>10.728433991283097</v>
+      </c>
+      <c r="D192">
+        <v>106.63639439104661</v>
+      </c>
+      <c r="E192" t="str">
+        <v/>
+      </c>
+      <c r="F192" t="str">
+        <v/>
+      </c>
+      <c r="G192">
+        <v>1</v>
+      </c>
+      <c r="H192" t="str">
+        <v/>
+      </c>
+      <c r="I192" t="str">
+        <v/>
+      </c>
+      <c r="J192" t="str">
+        <v/>
+      </c>
+      <c r="K192" t="str">
+        <v/>
+      </c>
+      <c r="L192" t="str">
+        <v/>
+      </c>
+      <c r="M192" t="str">
+        <v>07:21:06 24/4/2026</v>
+      </c>
+      <c r="N192" t="str">
+        <v>Lhp4 1</v>
+      </c>
+      <c r="O192">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v/>
+      </c>
+      <c r="B193" t="str">
+        <v>Lhp4 3</v>
+      </c>
+      <c r="C193">
+        <v>10.728032438695292</v>
+      </c>
+      <c r="D193">
+        <v>106.63612425327302</v>
+      </c>
+      <c r="E193" t="str">
+        <v/>
+      </c>
+      <c r="F193" t="str">
+        <v/>
+      </c>
+      <c r="G193">
+        <v>1</v>
+      </c>
+      <c r="H193" t="str">
+        <v/>
+      </c>
+      <c r="I193" t="str">
+        <v/>
+      </c>
+      <c r="J193" t="str">
+        <v/>
+      </c>
+      <c r="K193" t="str">
+        <v/>
+      </c>
+      <c r="L193" t="str">
+        <v/>
+      </c>
+      <c r="M193" t="str">
+        <v>07:21:30 24/4/2026</v>
+      </c>
+      <c r="N193" t="str">
+        <v>Lhp4 2</v>
+      </c>
+      <c r="O193">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v/>
+      </c>
+      <c r="B194" t="str">
+        <v>Lhp4 4</v>
+      </c>
+      <c r="C194">
+        <v>10.72765799926532</v>
+      </c>
+      <c r="D194">
+        <v>106.63599060812777</v>
+      </c>
+      <c r="E194" t="str">
+        <v/>
+      </c>
+      <c r="F194" t="str">
+        <v/>
+      </c>
+      <c r="G194">
+        <v>1</v>
+      </c>
+      <c r="H194" t="str">
+        <v/>
+      </c>
+      <c r="I194" t="str">
+        <v/>
+      </c>
+      <c r="J194" t="str">
+        <v/>
+      </c>
+      <c r="K194" t="str">
+        <v/>
+      </c>
+      <c r="L194" t="str">
+        <v/>
+      </c>
+      <c r="M194" t="str">
+        <v>07:22:03 24/4/2026</v>
+      </c>
+      <c r="N194" t="str">
+        <v>Lhp4 3</v>
+      </c>
+      <c r="O194">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v/>
+      </c>
+      <c r="B195" t="str">
+        <v>Lhp4 5</v>
+      </c>
+      <c r="C195">
+        <v>10.727225192787394</v>
+      </c>
+      <c r="D195">
+        <v>106.63579346418851</v>
+      </c>
+      <c r="E195" t="str">
+        <v/>
+      </c>
+      <c r="F195" t="str">
+        <v/>
+      </c>
+      <c r="G195">
+        <v>1</v>
+      </c>
+      <c r="H195" t="str">
+        <v/>
+      </c>
+      <c r="I195" t="str">
+        <v/>
+      </c>
+      <c r="J195" t="str">
+        <v/>
+      </c>
+      <c r="K195" t="str">
+        <v/>
+      </c>
+      <c r="L195" t="str">
+        <v/>
+      </c>
+      <c r="M195" t="str">
+        <v>07:22:39 24/4/2026</v>
+      </c>
+      <c r="N195" t="str">
+        <v>Lhp4 4</v>
+      </c>
+      <c r="O195">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v/>
+      </c>
+      <c r="B196" t="str">
+        <v>Lhp4 6</v>
+      </c>
+      <c r="C196">
+        <v>10.726682332799339</v>
+      </c>
+      <c r="D196">
+        <v>106.63552302384392</v>
+      </c>
+      <c r="E196" t="str">
+        <v/>
+      </c>
+      <c r="F196" t="str">
+        <v/>
+      </c>
+      <c r="G196">
+        <v>1</v>
+      </c>
+      <c r="H196" t="str">
+        <v/>
+      </c>
+      <c r="I196" t="str">
+        <v/>
+      </c>
+      <c r="J196" t="str">
+        <v/>
+      </c>
+      <c r="K196" t="str">
+        <v/>
+      </c>
+      <c r="L196" t="str">
+        <v/>
+      </c>
+      <c r="M196" t="str">
+        <v>07:23:00 24/4/2026</v>
+      </c>
+      <c r="N196" t="str">
+        <v>Lhp4 5</v>
+      </c>
+      <c r="O196">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v/>
+      </c>
+      <c r="B197" t="str">
+        <v>Lhp4 7</v>
+      </c>
+      <c r="C197">
+        <v>10.72638474486691</v>
+      </c>
+      <c r="D197">
+        <v>106.6353979979832</v>
+      </c>
+      <c r="E197" t="str">
+        <v/>
+      </c>
+      <c r="F197" t="str">
+        <v/>
+      </c>
+      <c r="G197">
+        <v>1</v>
+      </c>
+      <c r="H197" t="str">
+        <v/>
+      </c>
+      <c r="I197" t="str">
+        <v/>
+      </c>
+      <c r="J197" t="str">
+        <v/>
+      </c>
+      <c r="K197" t="str">
+        <v/>
+      </c>
+      <c r="L197" t="str">
+        <v/>
+      </c>
+      <c r="M197" t="str">
+        <v>07:23:24 24/4/2026</v>
+      </c>
+      <c r="N197" t="str">
+        <v>Lhp4 6</v>
+      </c>
+      <c r="O197">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v/>
+      </c>
+      <c r="B198" t="str">
+        <v>Lhp4 8</v>
+      </c>
+      <c r="C198">
+        <v>10.726176381627283</v>
+      </c>
+      <c r="D198">
+        <v>106.63526777644427</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v/>
+      </c>
+      <c r="G198">
+        <v>1</v>
+      </c>
+      <c r="H198" t="str">
+        <v/>
+      </c>
+      <c r="I198" t="str">
+        <v/>
+      </c>
+      <c r="J198" t="str">
+        <v/>
+      </c>
+      <c r="K198" t="str">
+        <v/>
+      </c>
+      <c r="L198" t="str">
+        <v/>
+      </c>
+      <c r="M198" t="str">
+        <v>07:23:39 24/4/2026</v>
+      </c>
+      <c r="N198" t="str">
+        <v>Lhp4 7</v>
+      </c>
+      <c r="O198">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v/>
+      </c>
+      <c r="B199" t="str">
+        <v>Lhp4 9</v>
+      </c>
+      <c r="C199">
+        <v>10.725657117978926</v>
+      </c>
+      <c r="D199">
+        <v>106.63502848535511</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v/>
+      </c>
+      <c r="G199">
+        <v>1</v>
+      </c>
+      <c r="H199" t="str">
+        <v/>
+      </c>
+      <c r="I199" t="str">
+        <v/>
+      </c>
+      <c r="J199" t="str">
+        <v/>
+      </c>
+      <c r="K199" t="str">
+        <v/>
+      </c>
+      <c r="L199" t="str">
+        <v/>
+      </c>
+      <c r="M199" t="str">
+        <v>07:24:09 24/4/2026</v>
+      </c>
+      <c r="N199" t="str">
+        <v>Lhp4 8</v>
+      </c>
+      <c r="O199">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v/>
+      </c>
+      <c r="B200" t="str">
+        <v>NSC 2</v>
+      </c>
+      <c r="C200">
+        <v>10.725428104566276</v>
+      </c>
+      <c r="D200">
+        <v>106.63492125445588</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v/>
+      </c>
+      <c r="G200">
+        <v>1</v>
+      </c>
+      <c r="H200" t="str">
+        <v/>
+      </c>
+      <c r="I200" t="str">
+        <v/>
+      </c>
+      <c r="J200" t="str">
+        <v/>
+      </c>
+      <c r="K200" t="str">
+        <v/>
+      </c>
+      <c r="L200" t="str">
+        <v/>
+      </c>
+      <c r="M200" t="str">
+        <v>07:25:01 24/4/2026</v>
+      </c>
+      <c r="N200" t="str">
+        <v/>
+      </c>
+      <c r="O200" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v/>
+      </c>
+      <c r="B201" t="str">
+        <v>NSC 3</v>
+      </c>
+      <c r="C201">
+        <v>10.725230321779414</v>
+      </c>
+      <c r="D201">
+        <v>106.63482384013228</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v/>
+      </c>
+      <c r="G201">
+        <v>1</v>
+      </c>
+      <c r="H201" t="str">
+        <v/>
+      </c>
+      <c r="I201" t="str">
+        <v/>
+      </c>
+      <c r="J201" t="str">
+        <v/>
+      </c>
+      <c r="K201" t="str">
+        <v/>
+      </c>
+      <c r="L201" t="str">
+        <v/>
+      </c>
+      <c r="M201" t="str">
+        <v>07:25:17 24/4/2026</v>
+      </c>
+      <c r="N201" t="str">
+        <v>NSC 2</v>
+      </c>
+      <c r="O201">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v/>
+      </c>
+      <c r="B202" t="str">
+        <v>NSC 4</v>
+      </c>
+      <c r="C202">
+        <v>10.724941161112362</v>
+      </c>
+      <c r="D202">
+        <v>106.63459628820421</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v/>
+      </c>
+      <c r="G202">
+        <v>1</v>
+      </c>
+      <c r="H202" t="str">
+        <v/>
+      </c>
+      <c r="I202" t="str">
+        <v/>
+      </c>
+      <c r="J202" t="str">
+        <v/>
+      </c>
+      <c r="K202" t="str">
+        <v/>
+      </c>
+      <c r="L202" t="str">
+        <v/>
+      </c>
+      <c r="M202" t="str">
+        <v>07:25:32 24/4/2026</v>
+      </c>
+      <c r="N202" t="str">
+        <v>NSC 3</v>
+      </c>
+      <c r="O202">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v/>
+      </c>
+      <c r="B203" t="str">
+        <v>NSC 5</v>
+      </c>
+      <c r="C203">
+        <v>10.724346485400824</v>
+      </c>
+      <c r="D203">
+        <v>106.63435904155283</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v/>
+      </c>
+      <c r="G203">
+        <v>1</v>
+      </c>
+      <c r="H203" t="str">
+        <v/>
+      </c>
+      <c r="I203" t="str">
+        <v/>
+      </c>
+      <c r="J203" t="str">
+        <v/>
+      </c>
+      <c r="K203" t="str">
+        <v/>
+      </c>
+      <c r="L203" t="str">
+        <v/>
+      </c>
+      <c r="M203" t="str">
+        <v>07:26:04 24/4/2026</v>
+      </c>
+      <c r="N203" t="str">
+        <v>NSC 4</v>
+      </c>
+      <c r="O203">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v/>
+      </c>
+      <c r="B204" t="str">
+        <v>NSC 6</v>
+      </c>
+      <c r="C204">
+        <v>10.724071999302733</v>
+      </c>
+      <c r="D204">
+        <v>106.63426955540508</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v/>
+      </c>
+      <c r="G204">
+        <v>1</v>
+      </c>
+      <c r="H204" t="str">
+        <v/>
+      </c>
+      <c r="I204" t="str">
+        <v/>
+      </c>
+      <c r="J204" t="str">
+        <v/>
+      </c>
+      <c r="K204" t="str">
+        <v/>
+      </c>
+      <c r="L204" t="str">
+        <v>images/nsc-6-2026-04-24T00-33-31-828Z.jpeg</v>
+      </c>
+      <c r="M204" t="str">
+        <v>07:26:33 24/4/2026</v>
+      </c>
+      <c r="N204" t="str">
+        <v>NSC 5</v>
+      </c>
+      <c r="O204">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O164"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O204"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O204"/>
+  <dimension ref="A1:O205"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9981,9 +9981,56 @@
         <v>32</v>
       </c>
     </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v/>
+      </c>
+      <c r="B205" t="str">
+        <v>gdfg</v>
+      </c>
+      <c r="C205">
+        <v>11.001186307149458</v>
+      </c>
+      <c r="D205">
+        <v>106.50695800781251</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v/>
+      </c>
+      <c r="G205">
+        <v>1</v>
+      </c>
+      <c r="H205" t="str">
+        <v/>
+      </c>
+      <c r="I205" t="str">
+        <v/>
+      </c>
+      <c r="J205" t="str">
+        <v/>
+      </c>
+      <c r="K205" t="str">
+        <v/>
+      </c>
+      <c r="L205" t="str">
+        <v/>
+      </c>
+      <c r="M205" t="str">
+        <v>01:47:39 10/5/2026</v>
+      </c>
+      <c r="N205" t="str">
+        <v/>
+      </c>
+      <c r="O205" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O204"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O205"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O205"/>
+  <dimension ref="A1:O206"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10028,9 +10028,56 @@
         <v/>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v/>
+      </c>
+      <c r="B206" t="str">
+        <v>fsd</v>
+      </c>
+      <c r="C206">
+        <v>10.945236749955251</v>
+      </c>
+      <c r="D206">
+        <v>106.48223876953125</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v/>
+      </c>
+      <c r="G206">
+        <v>1</v>
+      </c>
+      <c r="H206" t="str">
+        <v/>
+      </c>
+      <c r="I206" t="str">
+        <v/>
+      </c>
+      <c r="J206" t="str">
+        <v/>
+      </c>
+      <c r="K206" t="str">
+        <v/>
+      </c>
+      <c r="L206" t="str">
+        <v/>
+      </c>
+      <c r="M206" t="str">
+        <v>01:49:31 10/5/2026</v>
+      </c>
+      <c r="N206" t="str">
+        <v/>
+      </c>
+      <c r="O206" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O205"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O206"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/khaosat.xlsx
+++ b/data/khaosat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O206"/>
+  <dimension ref="A1:O207"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10075,9 +10075,56 @@
         <v/>
       </c>
     </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>37</v>
+      </c>
+      <c r="B207" t="str">
+        <v>My home</v>
+      </c>
+      <c r="C207">
+        <v>10.760205044059195</v>
+      </c>
+      <c r="D207">
+        <v>106.61352565046401</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
+        <v/>
+      </c>
+      <c r="G207">
+        <v>6</v>
+      </c>
+      <c r="H207" t="str">
+        <v>Lê Minh Nhật</v>
+      </c>
+      <c r="I207" t="str">
+        <v>STK</v>
+      </c>
+      <c r="J207" t="str">
+        <v/>
+      </c>
+      <c r="K207" t="str">
+        <v>LED 100W</v>
+      </c>
+      <c r="L207" t="str">
+        <v>images/my-home-2026-05-09T23-57-09-315Z.jpeg</v>
+      </c>
+      <c r="M207" t="str">
+        <v>06:56:45 10/5/2026</v>
+      </c>
+      <c r="N207" t="str">
+        <v>My home</v>
+      </c>
+      <c r="O207">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O206"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O207"/>
   </ignoredErrors>
 </worksheet>
 </file>